--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25750</v>
+        <v>25300</v>
       </c>
       <c r="F2" t="n">
-        <v>1165</v>
+        <v>1186</v>
       </c>
       <c r="G2" t="n">
-        <v>29998750</v>
+        <v>30005800</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>32050</v>
+        <v>32000</v>
       </c>
       <c r="F3" t="n">
-        <v>936.0624</v>
+        <v>938</v>
       </c>
       <c r="G3" t="n">
-        <v>30000800</v>
+        <v>30016000</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25300</v>
+        <v>25900</v>
       </c>
       <c r="F2" t="n">
         <v>1186</v>
       </c>
       <c r="G2" t="n">
-        <v>30005800</v>
+        <v>30717400</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>32000</v>
+        <v>32100</v>
       </c>
       <c r="F3" t="n">
         <v>938</v>
       </c>
       <c r="G3" t="n">
-        <v>30016000</v>
+        <v>30109800</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25900</v>
+        <v>25300</v>
       </c>
       <c r="F2" t="n">
         <v>1186</v>
       </c>
       <c r="G2" t="n">
-        <v>30717400</v>
+        <v>30005800</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>32100</v>
+        <v>32000</v>
       </c>
       <c r="F3" t="n">
         <v>938</v>
       </c>
       <c r="G3" t="n">
-        <v>30109800</v>
+        <v>30016000</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,66 +473,226 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>25300</v>
+        <v>28850</v>
       </c>
       <c r="F2" t="n">
-        <v>1186</v>
+        <v>1038.0221</v>
       </c>
       <c r="G2" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>126340</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>76400</v>
+      </c>
+      <c r="F3" t="n">
+        <v>391.9756</v>
+      </c>
+      <c r="G3" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>21650</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1383.2304</v>
+      </c>
+      <c r="G4" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F5" t="n">
+        <v>921.4443</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F6" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G6" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G7" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E8" t="n">
         <v>32000</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F8" t="n">
         <v>938</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G8" t="n">
         <v>30016000</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,66 +473,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>28850</v>
+        <v>33150</v>
       </c>
       <c r="F2" t="n">
-        <v>1038.0221</v>
+        <v>921.4443</v>
       </c>
       <c r="G2" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>76400</v>
+        <v>38050</v>
       </c>
       <c r="F3" t="n">
-        <v>391.9756</v>
+        <v>790.1567</v>
       </c>
       <c r="G3" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -542,24 +546,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>21650</v>
+        <v>28850</v>
       </c>
       <c r="F4" t="n">
-        <v>1383.2304</v>
+        <v>1038.0221</v>
       </c>
       <c r="G4" t="n">
         <v>29946939</v>
@@ -574,12 +578,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,10 +592,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>32500</v>
+        <v>76400</v>
       </c>
       <c r="F5" t="n">
-        <v>921.4443</v>
+        <v>391.9756</v>
       </c>
       <c r="G5" t="n">
         <v>29946939</v>
@@ -606,12 +610,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -620,10 +624,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>37900</v>
+        <v>21650</v>
       </c>
       <c r="F6" t="n">
-        <v>790.1567</v>
+        <v>1383.2304</v>
       </c>
       <c r="G6" t="n">
         <v>29946939</v>
@@ -633,17 +637,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,47 +656,111 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25300</v>
+        <v>32500</v>
       </c>
       <c r="F7" t="n">
-        <v>1186</v>
+        <v>921.4443</v>
       </c>
       <c r="G7" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F8" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G8" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G9" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E10" t="n">
         <v>32000</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F10" t="n">
         <v>938</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G10" t="n">
         <v>30016000</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,31 +478,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>33150</v>
+        <v>22750</v>
       </c>
       <c r="F2" t="n">
-        <v>921.4443</v>
+        <v>2200.9656</v>
       </c>
       <c r="G2" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
+        <v>50071968.5</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,12 +510,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -526,49 +524,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>38050</v>
+        <v>33150</v>
       </c>
       <c r="F3" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G3" t="n">
-        <v>30065462.5</v>
+        <v>30545877.8</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>28850</v>
+        <v>38050</v>
       </c>
       <c r="F4" t="n">
-        <v>1038.0221</v>
+        <v>790.1567</v>
       </c>
       <c r="G4" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -578,24 +578,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>76400</v>
+        <v>28850</v>
       </c>
       <c r="F5" t="n">
-        <v>391.9756</v>
+        <v>1038.0221</v>
       </c>
       <c r="G5" t="n">
         <v>29946939</v>
@@ -610,12 +610,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -624,10 +624,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21650</v>
+        <v>76400</v>
       </c>
       <c r="F6" t="n">
-        <v>1383.2304</v>
+        <v>391.9756</v>
       </c>
       <c r="G6" t="n">
         <v>29946939</v>
@@ -642,12 +642,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -656,10 +656,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>32500</v>
+        <v>21650</v>
       </c>
       <c r="F7" t="n">
-        <v>921.4443</v>
+        <v>1383.2304</v>
       </c>
       <c r="G7" t="n">
         <v>29946939</v>
@@ -674,12 +674,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>37900</v>
+        <v>32500</v>
       </c>
       <c r="F8" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G8" t="n">
         <v>29946939</v>
@@ -701,17 +701,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>25300</v>
+        <v>37900</v>
       </c>
       <c r="F9" t="n">
-        <v>1186</v>
+        <v>790.1567</v>
       </c>
       <c r="G9" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -738,29 +738,61 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G10" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E11" t="n">
         <v>32000</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F11" t="n">
         <v>938</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G11" t="n">
         <v>30016000</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,32 +473,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22750</v>
+        <v>21950</v>
       </c>
       <c r="F2" t="n">
-        <v>2200.9656</v>
+        <v>1378.9564</v>
       </c>
       <c r="G2" t="n">
-        <v>50071968.5</v>
+        <v>30268092.9</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -510,31 +510,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>33150</v>
+        <v>22750</v>
       </c>
       <c r="F3" t="n">
-        <v>921.4443</v>
+        <v>2200.9656</v>
       </c>
       <c r="G3" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
+        <v>50071968.5</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,12 +542,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -558,49 +556,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38050</v>
+        <v>33150</v>
       </c>
       <c r="F4" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G4" t="n">
-        <v>30065462.5</v>
+        <v>30545877.8</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>28850</v>
+        <v>38050</v>
       </c>
       <c r="F5" t="n">
-        <v>1038.0221</v>
+        <v>790.1567</v>
       </c>
       <c r="G5" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -610,24 +610,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>76400</v>
+        <v>28850</v>
       </c>
       <c r="F6" t="n">
-        <v>391.9756</v>
+        <v>1038.0221</v>
       </c>
       <c r="G6" t="n">
         <v>29946939</v>
@@ -642,12 +642,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -656,10 +656,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>21650</v>
+        <v>76400</v>
       </c>
       <c r="F7" t="n">
-        <v>1383.2304</v>
+        <v>391.9756</v>
       </c>
       <c r="G7" t="n">
         <v>29946939</v>
@@ -674,12 +674,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>32500</v>
+        <v>21650</v>
       </c>
       <c r="F8" t="n">
-        <v>921.4443</v>
+        <v>1383.2304</v>
       </c>
       <c r="G8" t="n">
         <v>29946939</v>
@@ -706,12 +706,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>37900</v>
+        <v>32500</v>
       </c>
       <c r="F9" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G9" t="n">
         <v>29946939</v>
@@ -733,17 +733,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>25300</v>
+        <v>37900</v>
       </c>
       <c r="F10" t="n">
-        <v>1186</v>
+        <v>790.1567</v>
       </c>
       <c r="G10" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -770,29 +770,61 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G11" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>32000</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>938</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G12" t="n">
         <v>30016000</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,24 +478,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>21950</v>
+        <v>8080</v>
       </c>
       <c r="F2" t="n">
-        <v>1378.9564</v>
+        <v>3746.0511</v>
       </c>
       <c r="G2" t="n">
         <v>30268092.9</v>
@@ -505,32 +505,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>22750</v>
+        <v>21950</v>
       </c>
       <c r="F3" t="n">
-        <v>2200.9656</v>
+        <v>1378.9564</v>
       </c>
       <c r="G3" t="n">
-        <v>50071968.5</v>
+        <v>30268092.9</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -542,31 +542,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>33150</v>
+        <v>22750</v>
       </c>
       <c r="F4" t="n">
-        <v>921.4443</v>
+        <v>2200.9656</v>
       </c>
       <c r="G4" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
+        <v>50071968.5</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -576,12 +574,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -590,49 +588,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>38050</v>
+        <v>33150</v>
       </c>
       <c r="F5" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G5" t="n">
-        <v>30065462.5</v>
+        <v>30545877.8</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28850</v>
+        <v>38050</v>
       </c>
       <c r="F6" t="n">
-        <v>1038.0221</v>
+        <v>790.1567</v>
       </c>
       <c r="G6" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -642,24 +642,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>76400</v>
+        <v>28850</v>
       </c>
       <c r="F7" t="n">
-        <v>391.9756</v>
+        <v>1038.0221</v>
       </c>
       <c r="G7" t="n">
         <v>29946939</v>
@@ -674,12 +674,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21650</v>
+        <v>76400</v>
       </c>
       <c r="F8" t="n">
-        <v>1383.2304</v>
+        <v>391.9756</v>
       </c>
       <c r="G8" t="n">
         <v>29946939</v>
@@ -706,12 +706,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>32500</v>
+        <v>21650</v>
       </c>
       <c r="F9" t="n">
-        <v>921.4443</v>
+        <v>1383.2304</v>
       </c>
       <c r="G9" t="n">
         <v>29946939</v>
@@ -738,12 +738,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>37900</v>
+        <v>32500</v>
       </c>
       <c r="F10" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G10" t="n">
         <v>29946939</v>
@@ -765,17 +765,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -784,13 +784,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>25300</v>
+        <v>37900</v>
       </c>
       <c r="F11" t="n">
-        <v>1186</v>
+        <v>790.1567</v>
       </c>
       <c r="G11" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -802,29 +802,61 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G12" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E13" t="n">
         <v>32000</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F13" t="n">
         <v>938</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G13" t="n">
         <v>30016000</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,34 +488,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8080</v>
+        <v>7520</v>
       </c>
       <c r="F2" t="n">
-        <v>3746.0511</v>
+        <v>4087.0231</v>
       </c>
       <c r="G2" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,30 +524,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>21950</v>
+        <v>83000</v>
       </c>
       <c r="F3" t="n">
-        <v>1378.9564</v>
+        <v>370.2941</v>
       </c>
       <c r="G3" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,49 +556,47 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22750</v>
+        <v>8080</v>
       </c>
       <c r="F4" t="n">
-        <v>2200.9656</v>
+        <v>3746.0511</v>
       </c>
       <c r="G4" t="n">
-        <v>50071968.5</v>
+        <v>30268092.9</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>33150</v>
+        <v>21950</v>
       </c>
       <c r="F5" t="n">
-        <v>921.4443</v>
+        <v>1378.9564</v>
       </c>
       <c r="G5" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
+        <v>30268092.9</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -608,95 +606,97 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>38050</v>
+        <v>22750</v>
       </c>
       <c r="F6" t="n">
-        <v>790.1567</v>
+        <v>2200.9656</v>
       </c>
       <c r="G6" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.4</v>
-      </c>
+        <v>50071968.5</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>28850</v>
+        <v>33150</v>
       </c>
       <c r="F7" t="n">
-        <v>1038.0221</v>
+        <v>921.4443</v>
       </c>
       <c r="G7" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>76400</v>
+        <v>38050</v>
       </c>
       <c r="F8" t="n">
-        <v>391.9756</v>
+        <v>790.1567</v>
       </c>
       <c r="G8" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>21650</v>
+        <v>28850</v>
       </c>
       <c r="F9" t="n">
-        <v>1383.2304</v>
+        <v>1038.0221</v>
       </c>
       <c r="G9" t="n">
         <v>29946939</v>
@@ -738,12 +738,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>32500</v>
+        <v>76400</v>
       </c>
       <c r="F10" t="n">
-        <v>921.4443</v>
+        <v>391.9756</v>
       </c>
       <c r="G10" t="n">
         <v>29946939</v>
@@ -770,12 +770,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>37900</v>
+        <v>21650</v>
       </c>
       <c r="F11" t="n">
-        <v>790.1567</v>
+        <v>1383.2304</v>
       </c>
       <c r="G11" t="n">
         <v>29946939</v>
@@ -797,17 +797,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -816,47 +816,111 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>25300</v>
+        <v>32500</v>
       </c>
       <c r="F12" t="n">
-        <v>1186</v>
+        <v>921.4443</v>
       </c>
       <c r="G12" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F13" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G13" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G14" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E15" t="n">
         <v>32000</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F15" t="n">
         <v>938</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G15" t="n">
         <v>30016000</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,17 +537,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,13 +556,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8080</v>
+        <v>47750</v>
       </c>
       <c r="F4" t="n">
-        <v>3746.0511</v>
+        <v>643.6526</v>
       </c>
       <c r="G4" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -574,24 +574,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21950</v>
+        <v>8080</v>
       </c>
       <c r="F5" t="n">
-        <v>1378.9564</v>
+        <v>3746.0511</v>
       </c>
       <c r="G5" t="n">
         <v>30268092.9</v>
@@ -601,32 +601,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>22750</v>
+        <v>21950</v>
       </c>
       <c r="F6" t="n">
-        <v>2200.9656</v>
+        <v>1378.9564</v>
       </c>
       <c r="G6" t="n">
-        <v>50071968.5</v>
+        <v>30268092.9</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -638,31 +638,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>33150</v>
+        <v>22750</v>
       </c>
       <c r="F7" t="n">
-        <v>921.4443</v>
+        <v>2200.9656</v>
       </c>
       <c r="G7" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
+        <v>50071968.5</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -672,12 +670,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -686,49 +684,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>38050</v>
+        <v>33150</v>
       </c>
       <c r="F8" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G8" t="n">
-        <v>30065462.5</v>
+        <v>30545877.8</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>28850</v>
+        <v>38050</v>
       </c>
       <c r="F9" t="n">
-        <v>1038.0221</v>
+        <v>790.1567</v>
       </c>
       <c r="G9" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -738,24 +738,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>76400</v>
+        <v>28850</v>
       </c>
       <c r="F10" t="n">
-        <v>391.9756</v>
+        <v>1038.0221</v>
       </c>
       <c r="G10" t="n">
         <v>29946939</v>
@@ -770,12 +770,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>21650</v>
+        <v>76400</v>
       </c>
       <c r="F11" t="n">
-        <v>1383.2304</v>
+        <v>391.9756</v>
       </c>
       <c r="G11" t="n">
         <v>29946939</v>
@@ -802,12 +802,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>32500</v>
+        <v>21650</v>
       </c>
       <c r="F12" t="n">
-        <v>921.4443</v>
+        <v>1383.2304</v>
       </c>
       <c r="G12" t="n">
         <v>29946939</v>
@@ -834,12 +834,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>37900</v>
+        <v>32500</v>
       </c>
       <c r="F13" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G13" t="n">
         <v>29946939</v>
@@ -861,17 +861,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,13 +880,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25300</v>
+        <v>37900</v>
       </c>
       <c r="F14" t="n">
-        <v>1186</v>
+        <v>790.1567</v>
       </c>
       <c r="G14" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -898,29 +898,61 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G15" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E16" t="n">
         <v>32000</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F16" t="n">
         <v>938</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G16" t="n">
         <v>30016000</v>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,30 +492,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7520</v>
+        <v>8490</v>
       </c>
       <c r="F2" t="n">
-        <v>4087.0231</v>
+        <v>3672.3539</v>
       </c>
       <c r="G2" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>83000</v>
+        <v>45500</v>
       </c>
       <c r="F3" t="n">
-        <v>370.2941</v>
+        <v>685.237</v>
       </c>
       <c r="G3" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -542,24 +542,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>47750</v>
+        <v>7520</v>
       </c>
       <c r="F4" t="n">
-        <v>643.6526</v>
+        <v>4087.0231</v>
       </c>
       <c r="G4" t="n">
         <v>30734413.9</v>
@@ -569,81 +569,81 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8080</v>
+        <v>83000</v>
       </c>
       <c r="F5" t="n">
-        <v>3746.0511</v>
+        <v>370.2941</v>
       </c>
       <c r="G5" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21950</v>
+        <v>47750</v>
       </c>
       <c r="F6" t="n">
-        <v>1378.9564</v>
+        <v>643.6526</v>
       </c>
       <c r="G6" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,49 +652,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>22750</v>
+        <v>8080</v>
       </c>
       <c r="F7" t="n">
-        <v>2200.9656</v>
+        <v>3746.0511</v>
       </c>
       <c r="G7" t="n">
-        <v>50071968.5</v>
+        <v>30268092.9</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>33150</v>
+        <v>21950</v>
       </c>
       <c r="F8" t="n">
-        <v>921.4443</v>
+        <v>1378.9564</v>
       </c>
       <c r="G8" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
+        <v>30268092.9</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -704,95 +702,97 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38050</v>
+        <v>22750</v>
       </c>
       <c r="F9" t="n">
-        <v>790.1567</v>
+        <v>2200.9656</v>
       </c>
       <c r="G9" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.4</v>
-      </c>
+        <v>50071968.5</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>28850</v>
+        <v>33150</v>
       </c>
       <c r="F10" t="n">
-        <v>1038.0221</v>
+        <v>921.4443</v>
       </c>
       <c r="G10" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>76400</v>
+        <v>38050</v>
       </c>
       <c r="F11" t="n">
-        <v>391.9756</v>
+        <v>790.1567</v>
       </c>
       <c r="G11" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -802,24 +802,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>21650</v>
+        <v>28850</v>
       </c>
       <c r="F12" t="n">
-        <v>1383.2304</v>
+        <v>1038.0221</v>
       </c>
       <c r="G12" t="n">
         <v>29946939</v>
@@ -834,12 +834,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>32500</v>
+        <v>76400</v>
       </c>
       <c r="F13" t="n">
-        <v>921.4443</v>
+        <v>391.9756</v>
       </c>
       <c r="G13" t="n">
         <v>29946939</v>
@@ -866,12 +866,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>37900</v>
+        <v>21650</v>
       </c>
       <c r="F14" t="n">
-        <v>790.1567</v>
+        <v>1383.2304</v>
       </c>
       <c r="G14" t="n">
         <v>29946939</v>
@@ -893,17 +893,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -912,47 +912,111 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>25300</v>
+        <v>32500</v>
       </c>
       <c r="F15" t="n">
-        <v>1186</v>
+        <v>921.4443</v>
       </c>
       <c r="G15" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F16" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G16" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G17" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E18" t="n">
         <v>32000</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F18" t="n">
         <v>938</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G18" t="n">
         <v>30016000</v>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8490</v>
+        <v>86300</v>
       </c>
       <c r="F2" t="n">
-        <v>3672.3539</v>
+        <v>366.4646</v>
       </c>
       <c r="G2" t="n">
-        <v>31178284.6</v>
+        <v>31625898.5</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -510,12 +510,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>45500</v>
+        <v>8490</v>
       </c>
       <c r="F3" t="n">
-        <v>685.237</v>
+        <v>3672.3539</v>
       </c>
       <c r="G3" t="n">
         <v>31178284.6</v>
@@ -537,17 +537,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,13 +556,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7520</v>
+        <v>45500</v>
       </c>
       <c r="F4" t="n">
-        <v>4087.0231</v>
+        <v>685.237</v>
       </c>
       <c r="G4" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -574,12 +574,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>83000</v>
+        <v>7520</v>
       </c>
       <c r="F5" t="n">
-        <v>370.2941</v>
+        <v>4087.0231</v>
       </c>
       <c r="G5" t="n">
         <v>30734413.9</v>
@@ -606,24 +606,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>47750</v>
+        <v>83000</v>
       </c>
       <c r="F6" t="n">
-        <v>643.6526</v>
+        <v>370.2941</v>
       </c>
       <c r="G6" t="n">
         <v>30734413.9</v>
@@ -633,17 +633,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8080</v>
+        <v>47750</v>
       </c>
       <c r="F7" t="n">
-        <v>3746.0511</v>
+        <v>643.6526</v>
       </c>
       <c r="G7" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -670,24 +670,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21950</v>
+        <v>8080</v>
       </c>
       <c r="F8" t="n">
-        <v>1378.9564</v>
+        <v>3746.0511</v>
       </c>
       <c r="G8" t="n">
         <v>30268092.9</v>
@@ -697,32 +697,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>22750</v>
+        <v>21950</v>
       </c>
       <c r="F9" t="n">
-        <v>2200.9656</v>
+        <v>1378.9564</v>
       </c>
       <c r="G9" t="n">
-        <v>50071968.5</v>
+        <v>30268092.9</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -734,31 +734,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>33150</v>
+        <v>22750</v>
       </c>
       <c r="F10" t="n">
-        <v>921.4443</v>
+        <v>2200.9656</v>
       </c>
       <c r="G10" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
+        <v>50071968.5</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -768,12 +766,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -782,49 +780,51 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>38050</v>
+        <v>33150</v>
       </c>
       <c r="F11" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G11" t="n">
-        <v>30065462.5</v>
+        <v>30545877.8</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>28850</v>
+        <v>38050</v>
       </c>
       <c r="F12" t="n">
-        <v>1038.0221</v>
+        <v>790.1567</v>
       </c>
       <c r="G12" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -834,24 +834,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>76400</v>
+        <v>28850</v>
       </c>
       <c r="F13" t="n">
-        <v>391.9756</v>
+        <v>1038.0221</v>
       </c>
       <c r="G13" t="n">
         <v>29946939</v>
@@ -866,12 +866,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>21650</v>
+        <v>76400</v>
       </c>
       <c r="F14" t="n">
-        <v>1383.2304</v>
+        <v>391.9756</v>
       </c>
       <c r="G14" t="n">
         <v>29946939</v>
@@ -898,12 +898,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>32500</v>
+        <v>21650</v>
       </c>
       <c r="F15" t="n">
-        <v>921.4443</v>
+        <v>1383.2304</v>
       </c>
       <c r="G15" t="n">
         <v>29946939</v>
@@ -930,12 +930,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>37900</v>
+        <v>32500</v>
       </c>
       <c r="F16" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G16" t="n">
         <v>29946939</v>
@@ -957,17 +957,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>25300</v>
+        <v>37900</v>
       </c>
       <c r="F17" t="n">
-        <v>1186</v>
+        <v>790.1567</v>
       </c>
       <c r="G17" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -994,29 +994,61 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G18" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E19" t="n">
         <v>32000</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F19" t="n">
         <v>938</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G19" t="n">
         <v>30016000</v>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,94 +492,96 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86300</v>
+        <v>35050</v>
       </c>
       <c r="F2" t="n">
-        <v>366.4646</v>
+        <v>941.2811</v>
       </c>
       <c r="G2" t="n">
-        <v>31625898.5</v>
+        <v>32991903.3</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8490</v>
+        <v>29100</v>
       </c>
       <c r="F3" t="n">
-        <v>3672.3539</v>
+        <v>1976.0221</v>
       </c>
       <c r="G3" t="n">
-        <v>31178284.6</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>45500</v>
+        <v>43700</v>
       </c>
       <c r="F4" t="n">
-        <v>685.237</v>
+        <v>1509.9269</v>
       </c>
       <c r="G4" t="n">
-        <v>31178284.6</v>
+        <v>65983806.6</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,20 +590,20 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7520</v>
+        <v>49500</v>
       </c>
       <c r="F5" t="n">
-        <v>4087.0231</v>
+        <v>1333.0062</v>
       </c>
       <c r="G5" t="n">
-        <v>30734413.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -620,94 +622,94 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>83000</v>
+        <v>86300</v>
       </c>
       <c r="F6" t="n">
-        <v>370.2941</v>
+        <v>366.4646</v>
       </c>
       <c r="G6" t="n">
-        <v>30734413.9</v>
+        <v>31625898.5</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>47750</v>
+        <v>8490</v>
       </c>
       <c r="F7" t="n">
-        <v>643.6526</v>
+        <v>3672.3539</v>
       </c>
       <c r="G7" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8080</v>
+        <v>45500</v>
       </c>
       <c r="F8" t="n">
-        <v>3746.0511</v>
+        <v>685.237</v>
       </c>
       <c r="G8" t="n">
-        <v>30268092.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -716,130 +718,126 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>21950</v>
+        <v>7520</v>
       </c>
       <c r="F9" t="n">
-        <v>1378.9564</v>
+        <v>4087.0231</v>
       </c>
       <c r="G9" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22750</v>
+        <v>83000</v>
       </c>
       <c r="F10" t="n">
-        <v>2200.9656</v>
+        <v>370.2941</v>
       </c>
       <c r="G10" t="n">
-        <v>50071968.5</v>
+        <v>30734413.9</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>33150</v>
+        <v>47750</v>
       </c>
       <c r="F11" t="n">
-        <v>921.4443</v>
+        <v>643.6526</v>
       </c>
       <c r="G11" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2</v>
-      </c>
+        <v>30734413.9</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>38050</v>
+        <v>8080</v>
       </c>
       <c r="F12" t="n">
-        <v>790.1567</v>
+        <v>3746.0511</v>
       </c>
       <c r="G12" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.4</v>
-      </c>
+        <v>30268092.9</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -848,30 +846,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>28850</v>
+        <v>21950</v>
       </c>
       <c r="F13" t="n">
-        <v>1038.0221</v>
+        <v>1378.9564</v>
       </c>
       <c r="G13" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,79 +878,83 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>76400</v>
+        <v>22750</v>
       </c>
       <c r="F14" t="n">
-        <v>391.9756</v>
+        <v>2200.9656</v>
       </c>
       <c r="G14" t="n">
-        <v>29946939</v>
+        <v>50071968.5</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>21650</v>
+        <v>33150</v>
       </c>
       <c r="F15" t="n">
-        <v>1383.2304</v>
+        <v>921.4443</v>
       </c>
       <c r="G15" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>32500</v>
+        <v>38050</v>
       </c>
       <c r="F16" t="n">
-        <v>921.4443</v>
+        <v>790.1567</v>
       </c>
       <c r="G16" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -962,24 +964,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>37900</v>
+        <v>28850</v>
       </c>
       <c r="F17" t="n">
-        <v>790.1567</v>
+        <v>1038.0221</v>
       </c>
       <c r="G17" t="n">
         <v>29946939</v>
@@ -989,17 +991,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1008,47 +1010,175 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>25300</v>
+        <v>76400</v>
       </c>
       <c r="F18" t="n">
-        <v>1186</v>
+        <v>391.9756</v>
       </c>
       <c r="G18" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>21650</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1383.2304</v>
+      </c>
+      <c r="G19" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F20" t="n">
+        <v>921.4443</v>
+      </c>
+      <c r="G20" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F21" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G21" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G22" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E23" t="n">
         <v>32000</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F23" t="n">
         <v>938</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G23" t="n">
         <v>30016000</v>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,68 +473,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>35050</v>
+        <v>10090</v>
       </c>
       <c r="F2" t="n">
-        <v>941.2811</v>
+        <v>3333.5276</v>
       </c>
       <c r="G2" t="n">
-        <v>32991903.3</v>
+        <v>33635293.3</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>29100</v>
+        <v>53200</v>
       </c>
       <c r="F3" t="n">
-        <v>1976.0221</v>
+        <v>632.2424</v>
       </c>
       <c r="G3" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>33635293.3</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,27 +542,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>43700</v>
+        <v>35050</v>
       </c>
       <c r="F4" t="n">
-        <v>1509.9269</v>
+        <v>941.2811</v>
       </c>
       <c r="G4" t="n">
-        <v>65983806.6</v>
+        <v>32991903.3</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -576,76 +574,78 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49500</v>
+        <v>29100</v>
       </c>
       <c r="F5" t="n">
-        <v>1333.0062</v>
+        <v>1976.0221</v>
       </c>
       <c r="G5" t="n">
-        <v>65983806.6</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>86300</v>
+        <v>43700</v>
       </c>
       <c r="F6" t="n">
-        <v>366.4646</v>
+        <v>1509.9269</v>
       </c>
       <c r="G6" t="n">
-        <v>31625898.5</v>
+        <v>65983806.6</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -654,30 +654,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8490</v>
+        <v>49500</v>
       </c>
       <c r="F7" t="n">
-        <v>3672.3539</v>
+        <v>1333.0062</v>
       </c>
       <c r="G7" t="n">
-        <v>31178284.6</v>
+        <v>65983806.6</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -686,20 +686,20 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>45500</v>
+        <v>86300</v>
       </c>
       <c r="F8" t="n">
-        <v>685.237</v>
+        <v>366.4646</v>
       </c>
       <c r="G8" t="n">
-        <v>31178284.6</v>
+        <v>31625898.5</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -718,30 +718,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7520</v>
+        <v>8490</v>
       </c>
       <c r="F9" t="n">
-        <v>4087.0231</v>
+        <v>3672.3539</v>
       </c>
       <c r="G9" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>83000</v>
+        <v>45500</v>
       </c>
       <c r="F10" t="n">
-        <v>370.2941</v>
+        <v>685.237</v>
       </c>
       <c r="G10" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -768,24 +768,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>47750</v>
+        <v>7520</v>
       </c>
       <c r="F11" t="n">
-        <v>643.6526</v>
+        <v>4087.0231</v>
       </c>
       <c r="G11" t="n">
         <v>30734413.9</v>
@@ -795,81 +795,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8080</v>
+        <v>83000</v>
       </c>
       <c r="F12" t="n">
-        <v>3746.0511</v>
+        <v>370.2941</v>
       </c>
       <c r="G12" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>21950</v>
+        <v>47750</v>
       </c>
       <c r="F13" t="n">
-        <v>1378.9564</v>
+        <v>643.6526</v>
       </c>
       <c r="G13" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -878,49 +878,47 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>22750</v>
+        <v>8080</v>
       </c>
       <c r="F14" t="n">
-        <v>2200.9656</v>
+        <v>3746.0511</v>
       </c>
       <c r="G14" t="n">
-        <v>50071968.5</v>
+        <v>30268092.9</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>33150</v>
+        <v>21950</v>
       </c>
       <c r="F15" t="n">
-        <v>921.4443</v>
+        <v>1378.9564</v>
       </c>
       <c r="G15" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2</v>
-      </c>
+        <v>30268092.9</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -930,95 +928,97 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>38050</v>
+        <v>22750</v>
       </c>
       <c r="F16" t="n">
-        <v>790.1567</v>
+        <v>2200.9656</v>
       </c>
       <c r="G16" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.4</v>
-      </c>
+        <v>50071968.5</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>28850</v>
+        <v>33150</v>
       </c>
       <c r="F17" t="n">
-        <v>1038.0221</v>
+        <v>921.4443</v>
       </c>
       <c r="G17" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>76400</v>
+        <v>38050</v>
       </c>
       <c r="F18" t="n">
-        <v>391.9756</v>
+        <v>790.1567</v>
       </c>
       <c r="G18" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1028,24 +1028,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>21650</v>
+        <v>28850</v>
       </c>
       <c r="F19" t="n">
-        <v>1383.2304</v>
+        <v>1038.0221</v>
       </c>
       <c r="G19" t="n">
         <v>29946939</v>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>32500</v>
+        <v>76400</v>
       </c>
       <c r="F20" t="n">
-        <v>921.4443</v>
+        <v>391.9756</v>
       </c>
       <c r="G20" t="n">
         <v>29946939</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>37900</v>
+        <v>21650</v>
       </c>
       <c r="F21" t="n">
-        <v>790.1567</v>
+        <v>1383.2304</v>
       </c>
       <c r="G21" t="n">
         <v>29946939</v>
@@ -1119,17 +1119,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1138,47 +1138,111 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>25300</v>
+        <v>32500</v>
       </c>
       <c r="F22" t="n">
-        <v>1186</v>
+        <v>921.4443</v>
       </c>
       <c r="G22" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F23" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G23" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G24" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E25" t="n">
         <v>32000</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F25" t="n">
         <v>938</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G25" t="n">
         <v>30016000</v>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10090</v>
+        <v>10250</v>
       </c>
       <c r="F2" t="n">
-        <v>3333.5276</v>
+        <v>3328.756</v>
       </c>
       <c r="G2" t="n">
-        <v>33635293.3</v>
+        <v>34119749</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -510,12 +510,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53200</v>
+        <v>10090</v>
       </c>
       <c r="F3" t="n">
-        <v>632.2424</v>
+        <v>3333.5276</v>
       </c>
       <c r="G3" t="n">
         <v>33635293.3</v>
@@ -537,32 +537,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>35050</v>
+        <v>53200</v>
       </c>
       <c r="F4" t="n">
-        <v>941.2811</v>
+        <v>632.2424</v>
       </c>
       <c r="G4" t="n">
-        <v>32991903.3</v>
+        <v>33635293.3</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -574,31 +574,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>29100</v>
+        <v>35050</v>
       </c>
       <c r="F5" t="n">
-        <v>1976.0221</v>
+        <v>941.2811</v>
       </c>
       <c r="G5" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>32991903.3</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -608,29 +606,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>43700</v>
+        <v>29100</v>
       </c>
       <c r="F6" t="n">
-        <v>1509.9269</v>
+        <v>1976.0221</v>
       </c>
       <c r="G6" t="n">
-        <v>65983806.6</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -640,24 +640,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49500</v>
+        <v>43700</v>
       </c>
       <c r="F7" t="n">
-        <v>1333.0062</v>
+        <v>1509.9269</v>
       </c>
       <c r="G7" t="n">
         <v>65983806.6</v>
@@ -667,17 +667,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -686,30 +686,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>86300</v>
+        <v>49500</v>
       </c>
       <c r="F8" t="n">
-        <v>366.4646</v>
+        <v>1333.0062</v>
       </c>
       <c r="G8" t="n">
-        <v>31625898.5</v>
+        <v>65983806.6</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8490</v>
+        <v>86300</v>
       </c>
       <c r="F9" t="n">
-        <v>3672.3539</v>
+        <v>366.4646</v>
       </c>
       <c r="G9" t="n">
-        <v>31178284.6</v>
+        <v>31625898.5</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>45500</v>
+        <v>8490</v>
       </c>
       <c r="F10" t="n">
-        <v>685.237</v>
+        <v>3672.3539</v>
       </c>
       <c r="G10" t="n">
         <v>31178284.6</v>
@@ -763,17 +763,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7520</v>
+        <v>45500</v>
       </c>
       <c r="F11" t="n">
-        <v>4087.0231</v>
+        <v>685.237</v>
       </c>
       <c r="G11" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>83000</v>
+        <v>7520</v>
       </c>
       <c r="F12" t="n">
-        <v>370.2941</v>
+        <v>4087.0231</v>
       </c>
       <c r="G12" t="n">
         <v>30734413.9</v>
@@ -832,24 +832,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>47750</v>
+        <v>83000</v>
       </c>
       <c r="F13" t="n">
-        <v>643.6526</v>
+        <v>370.2941</v>
       </c>
       <c r="G13" t="n">
         <v>30734413.9</v>
@@ -859,17 +859,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>8080</v>
+        <v>47750</v>
       </c>
       <c r="F14" t="n">
-        <v>3746.0511</v>
+        <v>643.6526</v>
       </c>
       <c r="G14" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -896,24 +896,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>21950</v>
+        <v>8080</v>
       </c>
       <c r="F15" t="n">
-        <v>1378.9564</v>
+        <v>3746.0511</v>
       </c>
       <c r="G15" t="n">
         <v>30268092.9</v>
@@ -923,32 +923,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>22750</v>
+        <v>21950</v>
       </c>
       <c r="F16" t="n">
-        <v>2200.9656</v>
+        <v>1378.9564</v>
       </c>
       <c r="G16" t="n">
-        <v>50071968.5</v>
+        <v>30268092.9</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -960,31 +960,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>33150</v>
+        <v>22750</v>
       </c>
       <c r="F17" t="n">
-        <v>921.4443</v>
+        <v>2200.9656</v>
       </c>
       <c r="G17" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2</v>
-      </c>
+        <v>50071968.5</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -994,12 +992,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1008,49 +1006,51 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>38050</v>
+        <v>33150</v>
       </c>
       <c r="F18" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G18" t="n">
-        <v>30065462.5</v>
+        <v>30545877.8</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>28850</v>
+        <v>38050</v>
       </c>
       <c r="F19" t="n">
-        <v>1038.0221</v>
+        <v>790.1567</v>
       </c>
       <c r="G19" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1060,24 +1060,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>76400</v>
+        <v>28850</v>
       </c>
       <c r="F20" t="n">
-        <v>391.9756</v>
+        <v>1038.0221</v>
       </c>
       <c r="G20" t="n">
         <v>29946939</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>21650</v>
+        <v>76400</v>
       </c>
       <c r="F21" t="n">
-        <v>1383.2304</v>
+        <v>391.9756</v>
       </c>
       <c r="G21" t="n">
         <v>29946939</v>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>32500</v>
+        <v>21650</v>
       </c>
       <c r="F22" t="n">
-        <v>921.4443</v>
+        <v>1383.2304</v>
       </c>
       <c r="G22" t="n">
         <v>29946939</v>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>37900</v>
+        <v>32500</v>
       </c>
       <c r="F23" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G23" t="n">
         <v>29946939</v>
@@ -1183,17 +1183,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>25300</v>
+        <v>37900</v>
       </c>
       <c r="F24" t="n">
-        <v>1186</v>
+        <v>790.1567</v>
       </c>
       <c r="G24" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1220,29 +1220,61 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G25" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E26" t="n">
         <v>32000</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>938</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G26" t="n">
         <v>30016000</v>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,39 +473,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10250</v>
+        <v>52400</v>
       </c>
       <c r="F2" t="n">
-        <v>3328.756</v>
+        <v>636.0417</v>
       </c>
       <c r="G2" t="n">
-        <v>34119749</v>
+        <v>33328583.4</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10090</v>
+        <v>10250</v>
       </c>
       <c r="F3" t="n">
-        <v>3333.5276</v>
+        <v>3328.756</v>
       </c>
       <c r="G3" t="n">
-        <v>33635293.3</v>
+        <v>34119749</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -542,12 +542,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53200</v>
+        <v>10090</v>
       </c>
       <c r="F4" t="n">
-        <v>632.2424</v>
+        <v>3333.5276</v>
       </c>
       <c r="G4" t="n">
         <v>33635293.3</v>
@@ -569,32 +569,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>35050</v>
+        <v>53200</v>
       </c>
       <c r="F5" t="n">
-        <v>941.2811</v>
+        <v>632.2424</v>
       </c>
       <c r="G5" t="n">
-        <v>32991903.3</v>
+        <v>33635293.3</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -606,31 +606,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>29100</v>
+        <v>35050</v>
       </c>
       <c r="F6" t="n">
-        <v>1976.0221</v>
+        <v>941.2811</v>
       </c>
       <c r="G6" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>32991903.3</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -640,29 +638,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>43700</v>
+        <v>29100</v>
       </c>
       <c r="F7" t="n">
-        <v>1509.9269</v>
+        <v>1976.0221</v>
       </c>
       <c r="G7" t="n">
-        <v>65983806.6</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -672,24 +672,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>49500</v>
+        <v>43700</v>
       </c>
       <c r="F8" t="n">
-        <v>1333.0062</v>
+        <v>1509.9269</v>
       </c>
       <c r="G8" t="n">
         <v>65983806.6</v>
@@ -699,17 +699,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -718,30 +718,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>86300</v>
+        <v>49500</v>
       </c>
       <c r="F9" t="n">
-        <v>366.4646</v>
+        <v>1333.0062</v>
       </c>
       <c r="G9" t="n">
-        <v>31625898.5</v>
+        <v>65983806.6</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8490</v>
+        <v>86300</v>
       </c>
       <c r="F10" t="n">
-        <v>3672.3539</v>
+        <v>366.4646</v>
       </c>
       <c r="G10" t="n">
-        <v>31178284.6</v>
+        <v>31625898.5</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>45500</v>
+        <v>8490</v>
       </c>
       <c r="F11" t="n">
-        <v>685.237</v>
+        <v>3672.3539</v>
       </c>
       <c r="G11" t="n">
         <v>31178284.6</v>
@@ -795,17 +795,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7520</v>
+        <v>45500</v>
       </c>
       <c r="F12" t="n">
-        <v>4087.0231</v>
+        <v>685.237</v>
       </c>
       <c r="G12" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>83000</v>
+        <v>7520</v>
       </c>
       <c r="F13" t="n">
-        <v>370.2941</v>
+        <v>4087.0231</v>
       </c>
       <c r="G13" t="n">
         <v>30734413.9</v>
@@ -864,24 +864,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>47750</v>
+        <v>83000</v>
       </c>
       <c r="F14" t="n">
-        <v>643.6526</v>
+        <v>370.2941</v>
       </c>
       <c r="G14" t="n">
         <v>30734413.9</v>
@@ -891,17 +891,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -910,13 +910,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8080</v>
+        <v>47750</v>
       </c>
       <c r="F15" t="n">
-        <v>3746.0511</v>
+        <v>643.6526</v>
       </c>
       <c r="G15" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -928,24 +928,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>21950</v>
+        <v>8080</v>
       </c>
       <c r="F16" t="n">
-        <v>1378.9564</v>
+        <v>3746.0511</v>
       </c>
       <c r="G16" t="n">
         <v>30268092.9</v>
@@ -955,32 +955,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>22750</v>
+        <v>21950</v>
       </c>
       <c r="F17" t="n">
-        <v>2200.9656</v>
+        <v>1378.9564</v>
       </c>
       <c r="G17" t="n">
-        <v>50071968.5</v>
+        <v>30268092.9</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -992,31 +992,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>33150</v>
+        <v>22750</v>
       </c>
       <c r="F18" t="n">
-        <v>921.4443</v>
+        <v>2200.9656</v>
       </c>
       <c r="G18" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
+        <v>50071968.5</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1026,12 +1024,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1040,49 +1038,51 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>38050</v>
+        <v>33150</v>
       </c>
       <c r="F19" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G19" t="n">
-        <v>30065462.5</v>
+        <v>30545877.8</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>28850</v>
+        <v>38050</v>
       </c>
       <c r="F20" t="n">
-        <v>1038.0221</v>
+        <v>790.1567</v>
       </c>
       <c r="G20" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1092,24 +1092,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>76400</v>
+        <v>28850</v>
       </c>
       <c r="F21" t="n">
-        <v>391.9756</v>
+        <v>1038.0221</v>
       </c>
       <c r="G21" t="n">
         <v>29946939</v>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>21650</v>
+        <v>76400</v>
       </c>
       <c r="F22" t="n">
-        <v>1383.2304</v>
+        <v>391.9756</v>
       </c>
       <c r="G22" t="n">
         <v>29946939</v>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>32500</v>
+        <v>21650</v>
       </c>
       <c r="F23" t="n">
-        <v>921.4443</v>
+        <v>1383.2304</v>
       </c>
       <c r="G23" t="n">
         <v>29946939</v>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>37900</v>
+        <v>32500</v>
       </c>
       <c r="F24" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G24" t="n">
         <v>29946939</v>
@@ -1215,17 +1215,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1234,13 +1234,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>25300</v>
+        <v>37900</v>
       </c>
       <c r="F25" t="n">
-        <v>1186</v>
+        <v>790.1567</v>
       </c>
       <c r="G25" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1252,29 +1252,61 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G26" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E27" t="n">
         <v>32000</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>938</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G27" t="n">
         <v>30016000</v>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,52 +492,52 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>52400</v>
+        <v>87800</v>
       </c>
       <c r="F2" t="n">
-        <v>636.0417</v>
+        <v>384.5603</v>
       </c>
       <c r="G2" t="n">
-        <v>33328583.4</v>
+        <v>33764396.5</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>10250</v>
+        <v>52400</v>
       </c>
       <c r="F3" t="n">
-        <v>3328.756</v>
+        <v>636.0417</v>
       </c>
       <c r="G3" t="n">
-        <v>34119749</v>
+        <v>33328583.4</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -556,13 +556,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10090</v>
+        <v>10250</v>
       </c>
       <c r="F4" t="n">
-        <v>3333.5276</v>
+        <v>3328.756</v>
       </c>
       <c r="G4" t="n">
-        <v>33635293.3</v>
+        <v>34119749</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -574,12 +574,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53200</v>
+        <v>10090</v>
       </c>
       <c r="F5" t="n">
-        <v>632.2424</v>
+        <v>3333.5276</v>
       </c>
       <c r="G5" t="n">
         <v>33635293.3</v>
@@ -601,32 +601,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>35050</v>
+        <v>53200</v>
       </c>
       <c r="F6" t="n">
-        <v>941.2811</v>
+        <v>632.2424</v>
       </c>
       <c r="G6" t="n">
-        <v>32991903.3</v>
+        <v>33635293.3</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -638,31 +638,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29100</v>
+        <v>35050</v>
       </c>
       <c r="F7" t="n">
-        <v>1976.0221</v>
+        <v>941.2811</v>
       </c>
       <c r="G7" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>32991903.3</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -672,29 +670,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>43700</v>
+        <v>29100</v>
       </c>
       <c r="F8" t="n">
-        <v>1509.9269</v>
+        <v>1976.0221</v>
       </c>
       <c r="G8" t="n">
-        <v>65983806.6</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -704,24 +704,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>49500</v>
+        <v>43700</v>
       </c>
       <c r="F9" t="n">
-        <v>1333.0062</v>
+        <v>1509.9269</v>
       </c>
       <c r="G9" t="n">
         <v>65983806.6</v>
@@ -731,17 +731,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -750,30 +750,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>86300</v>
+        <v>49500</v>
       </c>
       <c r="F10" t="n">
-        <v>366.4646</v>
+        <v>1333.0062</v>
       </c>
       <c r="G10" t="n">
-        <v>31625898.5</v>
+        <v>65983806.6</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8490</v>
+        <v>86300</v>
       </c>
       <c r="F11" t="n">
-        <v>3672.3539</v>
+        <v>366.4646</v>
       </c>
       <c r="G11" t="n">
-        <v>31178284.6</v>
+        <v>31625898.5</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>45500</v>
+        <v>8490</v>
       </c>
       <c r="F12" t="n">
-        <v>685.237</v>
+        <v>3672.3539</v>
       </c>
       <c r="G12" t="n">
         <v>31178284.6</v>
@@ -827,17 +827,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7520</v>
+        <v>45500</v>
       </c>
       <c r="F13" t="n">
-        <v>4087.0231</v>
+        <v>685.237</v>
       </c>
       <c r="G13" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>83000</v>
+        <v>7520</v>
       </c>
       <c r="F14" t="n">
-        <v>370.2941</v>
+        <v>4087.0231</v>
       </c>
       <c r="G14" t="n">
         <v>30734413.9</v>
@@ -896,24 +896,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>47750</v>
+        <v>83000</v>
       </c>
       <c r="F15" t="n">
-        <v>643.6526</v>
+        <v>370.2941</v>
       </c>
       <c r="G15" t="n">
         <v>30734413.9</v>
@@ -923,17 +923,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8080</v>
+        <v>47750</v>
       </c>
       <c r="F16" t="n">
-        <v>3746.0511</v>
+        <v>643.6526</v>
       </c>
       <c r="G16" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -960,24 +960,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>21950</v>
+        <v>8080</v>
       </c>
       <c r="F17" t="n">
-        <v>1378.9564</v>
+        <v>3746.0511</v>
       </c>
       <c r="G17" t="n">
         <v>30268092.9</v>
@@ -987,32 +987,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>22750</v>
+        <v>21950</v>
       </c>
       <c r="F18" t="n">
-        <v>2200.9656</v>
+        <v>1378.9564</v>
       </c>
       <c r="G18" t="n">
-        <v>50071968.5</v>
+        <v>30268092.9</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1024,31 +1024,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>33150</v>
+        <v>22750</v>
       </c>
       <c r="F19" t="n">
-        <v>921.4443</v>
+        <v>2200.9656</v>
       </c>
       <c r="G19" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
+        <v>50071968.5</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1058,12 +1056,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1072,49 +1070,51 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>38050</v>
+        <v>33150</v>
       </c>
       <c r="F20" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G20" t="n">
-        <v>30065462.5</v>
+        <v>30545877.8</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>28850</v>
+        <v>38050</v>
       </c>
       <c r="F21" t="n">
-        <v>1038.0221</v>
+        <v>790.1567</v>
       </c>
       <c r="G21" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1124,24 +1124,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>76400</v>
+        <v>28850</v>
       </c>
       <c r="F22" t="n">
-        <v>391.9756</v>
+        <v>1038.0221</v>
       </c>
       <c r="G22" t="n">
         <v>29946939</v>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>21650</v>
+        <v>76400</v>
       </c>
       <c r="F23" t="n">
-        <v>1383.2304</v>
+        <v>391.9756</v>
       </c>
       <c r="G23" t="n">
         <v>29946939</v>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>32500</v>
+        <v>21650</v>
       </c>
       <c r="F24" t="n">
-        <v>921.4443</v>
+        <v>1383.2304</v>
       </c>
       <c r="G24" t="n">
         <v>29946939</v>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1234,10 +1234,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>37900</v>
+        <v>32500</v>
       </c>
       <c r="F25" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G25" t="n">
         <v>29946939</v>
@@ -1247,17 +1247,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>25300</v>
+        <v>37900</v>
       </c>
       <c r="F26" t="n">
-        <v>1186</v>
+        <v>790.1567</v>
       </c>
       <c r="G26" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1284,29 +1284,61 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G27" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E28" t="n">
         <v>32000</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F28" t="n">
         <v>938</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G28" t="n">
         <v>30016000</v>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,158 +492,160 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>87800</v>
+        <v>9990</v>
       </c>
       <c r="F2" t="n">
-        <v>384.5603</v>
+        <v>3271.9446</v>
       </c>
       <c r="G2" t="n">
-        <v>33764396.5</v>
+        <v>32686726.8</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>52400</v>
+        <v>32000</v>
       </c>
       <c r="F3" t="n">
-        <v>636.0417</v>
+        <v>2127.2811</v>
       </c>
       <c r="G3" t="n">
-        <v>33328583.4</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>68072995.90000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10250</v>
+        <v>19830</v>
       </c>
       <c r="F4" t="n">
-        <v>3328.756</v>
+        <v>2747.2455</v>
       </c>
       <c r="G4" t="n">
-        <v>34119749</v>
+        <v>54477878.1</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10090</v>
+        <v>37100</v>
       </c>
       <c r="F5" t="n">
-        <v>3333.5276</v>
+        <v>293.6813</v>
       </c>
       <c r="G5" t="n">
-        <v>33635293.3</v>
+        <v>10895575.6</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53200</v>
+        <v>80200</v>
       </c>
       <c r="F6" t="n">
-        <v>632.2424</v>
+        <v>407.5652</v>
       </c>
       <c r="G6" t="n">
-        <v>33635293.3</v>
+        <v>32686726.8</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,86 +654,84 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>35050</v>
+        <v>31600</v>
       </c>
       <c r="F7" t="n">
-        <v>941.2811</v>
+        <v>344.7967</v>
       </c>
       <c r="G7" t="n">
-        <v>32991903.3</v>
+        <v>10895575.6</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>29100</v>
+        <v>38200</v>
       </c>
       <c r="F8" t="n">
-        <v>1976.0221</v>
+        <v>855.6735</v>
       </c>
       <c r="G8" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>32686726.8</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>43700</v>
+        <v>87800</v>
       </c>
       <c r="F9" t="n">
-        <v>1509.9269</v>
+        <v>384.5603</v>
       </c>
       <c r="G9" t="n">
-        <v>65983806.6</v>
+        <v>33764396.5</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -750,52 +750,52 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>49500</v>
+        <v>52400</v>
       </c>
       <c r="F10" t="n">
-        <v>1333.0062</v>
+        <v>636.0417</v>
       </c>
       <c r="G10" t="n">
-        <v>65983806.6</v>
+        <v>33328583.4</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>86300</v>
+        <v>10250</v>
       </c>
       <c r="F11" t="n">
-        <v>366.4646</v>
+        <v>3328.756</v>
       </c>
       <c r="G11" t="n">
-        <v>31625898.5</v>
+        <v>34119749</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -810,24 +810,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8490</v>
+        <v>10090</v>
       </c>
       <c r="F12" t="n">
-        <v>3672.3539</v>
+        <v>3333.5276</v>
       </c>
       <c r="G12" t="n">
-        <v>31178284.6</v>
+        <v>33635293.3</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -842,34 +842,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>45500</v>
+        <v>53200</v>
       </c>
       <c r="F13" t="n">
-        <v>685.237</v>
+        <v>632.2424</v>
       </c>
       <c r="G13" t="n">
-        <v>31178284.6</v>
+        <v>33635293.3</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -878,62 +878,64 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7520</v>
+        <v>35050</v>
       </c>
       <c r="F14" t="n">
-        <v>4087.0231</v>
+        <v>941.2811</v>
       </c>
       <c r="G14" t="n">
-        <v>30734413.9</v>
+        <v>32991903.3</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>83000</v>
+        <v>29100</v>
       </c>
       <c r="F15" t="n">
-        <v>370.2941</v>
+        <v>1976.0221</v>
       </c>
       <c r="G15" t="n">
-        <v>30734413.9</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -942,62 +944,62 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>47750</v>
+        <v>43700</v>
       </c>
       <c r="F16" t="n">
-        <v>643.6526</v>
+        <v>1509.9269</v>
       </c>
       <c r="G16" t="n">
-        <v>30734413.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>8080</v>
+        <v>49500</v>
       </c>
       <c r="F17" t="n">
-        <v>3746.0511</v>
+        <v>1333.0062</v>
       </c>
       <c r="G17" t="n">
-        <v>30268092.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1006,130 +1008,126 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>21950</v>
+        <v>86300</v>
       </c>
       <c r="F18" t="n">
-        <v>1378.9564</v>
+        <v>366.4646</v>
       </c>
       <c r="G18" t="n">
-        <v>30268092.9</v>
+        <v>31625898.5</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>22750</v>
+        <v>8490</v>
       </c>
       <c r="F19" t="n">
-        <v>2200.9656</v>
+        <v>3672.3539</v>
       </c>
       <c r="G19" t="n">
-        <v>50071968.5</v>
+        <v>31178284.6</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>33150</v>
+        <v>45500</v>
       </c>
       <c r="F20" t="n">
-        <v>921.4443</v>
+        <v>685.237</v>
       </c>
       <c r="G20" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2</v>
-      </c>
+        <v>31178284.6</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>38050</v>
+        <v>7520</v>
       </c>
       <c r="F21" t="n">
-        <v>790.1567</v>
+        <v>4087.0231</v>
       </c>
       <c r="G21" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.4</v>
-      </c>
+        <v>30734413.9</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1138,30 +1136,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>28850</v>
+        <v>83000</v>
       </c>
       <c r="F22" t="n">
-        <v>1038.0221</v>
+        <v>370.2941</v>
       </c>
       <c r="G22" t="n">
-        <v>29946939</v>
+        <v>30734413.9</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1170,30 +1168,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>76400</v>
+        <v>47750</v>
       </c>
       <c r="F23" t="n">
-        <v>391.9756</v>
+        <v>643.6526</v>
       </c>
       <c r="G23" t="n">
-        <v>29946939</v>
+        <v>30734413.9</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1202,62 +1200,62 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>21650</v>
+        <v>8080</v>
       </c>
       <c r="F24" t="n">
-        <v>1383.2304</v>
+        <v>3746.0511</v>
       </c>
       <c r="G24" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>32500</v>
+        <v>21950</v>
       </c>
       <c r="F25" t="n">
-        <v>921.4443</v>
+        <v>1378.9564</v>
       </c>
       <c r="G25" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1266,79 +1264,307 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>37900</v>
+        <v>22750</v>
       </c>
       <c r="F26" t="n">
-        <v>790.1567</v>
+        <v>2200.9656</v>
       </c>
       <c r="G26" t="n">
-        <v>29946939</v>
+        <v>50071968.5</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>25300</v>
+        <v>33150</v>
       </c>
       <c r="F27" t="n">
-        <v>1186</v>
+        <v>921.4443</v>
       </c>
       <c r="G27" t="n">
-        <v>30005800</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>38050</v>
+      </c>
+      <c r="F28" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G28" t="n">
+        <v>30065462.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>아이티센글로벌</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>124500</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>28850</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1038.0221</v>
+      </c>
+      <c r="G29" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>126340</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>76400</v>
+      </c>
+      <c r="F30" t="n">
+        <v>391.9756</v>
+      </c>
+      <c r="G30" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>21650</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1383.2304</v>
+      </c>
+      <c r="G31" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F32" t="n">
+        <v>921.4443</v>
+      </c>
+      <c r="G32" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F33" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G33" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G34" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E35" t="n">
         <v>32000</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F35" t="n">
         <v>938</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G35" t="n">
         <v>30016000</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,96 +492,94 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9990</v>
+        <v>9520</v>
       </c>
       <c r="F2" t="n">
-        <v>3271.9446</v>
+        <v>1132.5399</v>
       </c>
       <c r="G2" t="n">
-        <v>32686726.8</v>
+        <v>10781779.8</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>32000</v>
+        <v>38400</v>
       </c>
       <c r="F3" t="n">
-        <v>2127.2811</v>
+        <v>561.551</v>
       </c>
       <c r="G3" t="n">
-        <v>68072995.90000001</v>
-      </c>
-      <c r="H3" t="n">
-        <v>8.06</v>
-      </c>
+        <v>21563559.7</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>19830</v>
+        <v>79400</v>
       </c>
       <c r="F4" t="n">
-        <v>2747.2455</v>
+        <v>135.7907</v>
       </c>
       <c r="G4" t="n">
-        <v>54477878.1</v>
+        <v>10781779.8</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -590,30 +588,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>37100</v>
+        <v>31050</v>
       </c>
       <c r="F5" t="n">
-        <v>293.6813</v>
+        <v>347.2393</v>
       </c>
       <c r="G5" t="n">
-        <v>10895575.6</v>
+        <v>10781779.8</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -622,30 +620,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>80200</v>
+        <v>38500</v>
       </c>
       <c r="F6" t="n">
-        <v>407.5652</v>
+        <v>280.0462</v>
       </c>
       <c r="G6" t="n">
-        <v>32686726.8</v>
+        <v>10781779.8</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -654,13 +652,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>31600</v>
+        <v>50100</v>
       </c>
       <c r="F7" t="n">
-        <v>344.7967</v>
+        <v>645.6156</v>
       </c>
       <c r="G7" t="n">
-        <v>10895575.6</v>
+        <v>32345339.5</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -672,12 +670,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -686,10 +684,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>38200</v>
+        <v>9990</v>
       </c>
       <c r="F8" t="n">
-        <v>855.6735</v>
+        <v>3271.9446</v>
       </c>
       <c r="G8" t="n">
         <v>32686726.8</v>
@@ -699,177 +697,179 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>87800</v>
+        <v>32000</v>
       </c>
       <c r="F9" t="n">
-        <v>384.5603</v>
+        <v>2127.2811</v>
       </c>
       <c r="G9" t="n">
-        <v>33764396.5</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>68072995.90000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>52400</v>
+        <v>19830</v>
       </c>
       <c r="F10" t="n">
-        <v>636.0417</v>
+        <v>2747.2455</v>
       </c>
       <c r="G10" t="n">
-        <v>33328583.4</v>
+        <v>54477878.1</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10250</v>
+        <v>37100</v>
       </c>
       <c r="F11" t="n">
-        <v>3328.756</v>
+        <v>293.6813</v>
       </c>
       <c r="G11" t="n">
-        <v>34119749</v>
+        <v>10895575.6</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10090</v>
+        <v>80200</v>
       </c>
       <c r="F12" t="n">
-        <v>3333.5276</v>
+        <v>407.5652</v>
       </c>
       <c r="G12" t="n">
-        <v>33635293.3</v>
+        <v>32686726.8</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53200</v>
+        <v>31600</v>
       </c>
       <c r="F13" t="n">
-        <v>632.2424</v>
+        <v>344.7967</v>
       </c>
       <c r="G13" t="n">
-        <v>33635293.3</v>
+        <v>10895575.6</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -878,192 +878,190 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>35050</v>
+        <v>38200</v>
       </c>
       <c r="F14" t="n">
-        <v>941.2811</v>
+        <v>855.6735</v>
       </c>
       <c r="G14" t="n">
-        <v>32991903.3</v>
+        <v>32686726.8</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>29100</v>
+        <v>87800</v>
       </c>
       <c r="F15" t="n">
-        <v>1976.0221</v>
+        <v>384.5603</v>
       </c>
       <c r="G15" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>33764396.5</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>43700</v>
+        <v>52400</v>
       </c>
       <c r="F16" t="n">
-        <v>1509.9269</v>
+        <v>636.0417</v>
       </c>
       <c r="G16" t="n">
-        <v>65983806.6</v>
+        <v>33328583.4</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>49500</v>
+        <v>10250</v>
       </c>
       <c r="F17" t="n">
-        <v>1333.0062</v>
+        <v>3328.756</v>
       </c>
       <c r="G17" t="n">
-        <v>65983806.6</v>
+        <v>34119749</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>86300</v>
+        <v>10090</v>
       </c>
       <c r="F18" t="n">
-        <v>366.4646</v>
+        <v>3333.5276</v>
       </c>
       <c r="G18" t="n">
-        <v>31625898.5</v>
+        <v>33635293.3</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8490</v>
+        <v>53200</v>
       </c>
       <c r="F19" t="n">
-        <v>3672.3539</v>
+        <v>632.2424</v>
       </c>
       <c r="G19" t="n">
-        <v>31178284.6</v>
+        <v>33635293.3</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1072,84 +1070,86 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>45500</v>
+        <v>35050</v>
       </c>
       <c r="F20" t="n">
-        <v>685.237</v>
+        <v>941.2811</v>
       </c>
       <c r="G20" t="n">
-        <v>31178284.6</v>
+        <v>32991903.3</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>7520</v>
+        <v>29100</v>
       </c>
       <c r="F21" t="n">
-        <v>4087.0231</v>
+        <v>1976.0221</v>
       </c>
       <c r="G21" t="n">
-        <v>30734413.9</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>83000</v>
+        <v>43700</v>
       </c>
       <c r="F22" t="n">
-        <v>370.2941</v>
+        <v>1509.9269</v>
       </c>
       <c r="G22" t="n">
-        <v>30734413.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1164,66 +1164,66 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>47750</v>
+        <v>49500</v>
       </c>
       <c r="F23" t="n">
-        <v>643.6526</v>
+        <v>1333.0062</v>
       </c>
       <c r="G23" t="n">
-        <v>30734413.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>8080</v>
+        <v>86300</v>
       </c>
       <c r="F24" t="n">
-        <v>3746.0511</v>
+        <v>366.4646</v>
       </c>
       <c r="G24" t="n">
-        <v>30268092.9</v>
+        <v>31625898.5</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1232,162 +1232,158 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>21950</v>
+        <v>8490</v>
       </c>
       <c r="F25" t="n">
-        <v>1378.9564</v>
+        <v>3672.3539</v>
       </c>
       <c r="G25" t="n">
-        <v>30268092.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>22750</v>
+        <v>45500</v>
       </c>
       <c r="F26" t="n">
-        <v>2200.9656</v>
+        <v>685.237</v>
       </c>
       <c r="G26" t="n">
-        <v>50071968.5</v>
+        <v>31178284.6</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>33150</v>
+        <v>7520</v>
       </c>
       <c r="F27" t="n">
-        <v>921.4443</v>
+        <v>4087.0231</v>
       </c>
       <c r="G27" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2</v>
-      </c>
+        <v>30734413.9</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>38050</v>
+        <v>83000</v>
       </c>
       <c r="F28" t="n">
-        <v>790.1567</v>
+        <v>370.2941</v>
       </c>
       <c r="G28" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.4</v>
-      </c>
+        <v>30734413.9</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>28850</v>
+        <v>47750</v>
       </c>
       <c r="F29" t="n">
-        <v>1038.0221</v>
+        <v>643.6526</v>
       </c>
       <c r="G29" t="n">
-        <v>29946939</v>
+        <v>30734413.9</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1396,20 +1392,20 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>76400</v>
+        <v>8080</v>
       </c>
       <c r="F30" t="n">
-        <v>391.9756</v>
+        <v>3746.0511</v>
       </c>
       <c r="G30" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1424,34 +1420,34 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>21650</v>
+        <v>21950</v>
       </c>
       <c r="F31" t="n">
-        <v>1383.2304</v>
+        <v>1378.9564</v>
       </c>
       <c r="G31" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1460,111 +1456,307 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>32500</v>
+        <v>22750</v>
       </c>
       <c r="F32" t="n">
-        <v>921.4443</v>
+        <v>2200.9656</v>
       </c>
       <c r="G32" t="n">
-        <v>29946939</v>
+        <v>50071968.5</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>37900</v>
+        <v>33150</v>
       </c>
       <c r="F33" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G33" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>25300</v>
+        <v>38050</v>
       </c>
       <c r="F34" t="n">
-        <v>1186</v>
+        <v>790.1567</v>
       </c>
       <c r="G34" t="n">
-        <v>30005800</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>아이티센글로벌</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>124500</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>28850</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1038.0221</v>
+      </c>
+      <c r="G35" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>126340</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>76400</v>
+      </c>
+      <c r="F36" t="n">
+        <v>391.9756</v>
+      </c>
+      <c r="G36" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>21650</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1383.2304</v>
+      </c>
+      <c r="G37" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F38" t="n">
+        <v>921.4443</v>
+      </c>
+      <c r="G38" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F39" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G39" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G40" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E41" t="n">
         <v>32000</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F41" t="n">
         <v>938</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G41" t="n">
         <v>30016000</v>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,20 +492,20 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9520</v>
+        <v>20400</v>
       </c>
       <c r="F2" t="n">
-        <v>1132.5399</v>
+        <v>1577.2548</v>
       </c>
       <c r="G2" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,30 +524,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>38400</v>
+        <v>37600</v>
       </c>
       <c r="F3" t="n">
-        <v>561.551</v>
+        <v>285.2482</v>
       </c>
       <c r="G3" t="n">
-        <v>21563559.7</v>
+        <v>10725332.9</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,30 +556,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>79400</v>
+        <v>30100</v>
       </c>
       <c r="F4" t="n">
-        <v>135.7907</v>
+        <v>356.3234</v>
       </c>
       <c r="G4" t="n">
-        <v>10781779.8</v>
+        <v>10725332.9</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,30 +588,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>31050</v>
+        <v>36800</v>
       </c>
       <c r="F5" t="n">
-        <v>347.2393</v>
+        <v>874.3478</v>
       </c>
       <c r="G5" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>38500</v>
+        <v>46400</v>
       </c>
       <c r="F6" t="n">
-        <v>280.0462</v>
+        <v>693.4482</v>
       </c>
       <c r="G6" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -638,12 +638,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,30 +652,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>50100</v>
+        <v>9520</v>
       </c>
       <c r="F7" t="n">
-        <v>645.6156</v>
+        <v>1132.5399</v>
       </c>
       <c r="G7" t="n">
-        <v>32345339.5</v>
+        <v>10781779.8</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,96 +684,94 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9990</v>
+        <v>38400</v>
       </c>
       <c r="F8" t="n">
-        <v>3271.9446</v>
+        <v>561.551</v>
       </c>
       <c r="G8" t="n">
-        <v>32686726.8</v>
+        <v>21563559.7</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>32000</v>
+        <v>79400</v>
       </c>
       <c r="F9" t="n">
-        <v>2127.2811</v>
+        <v>135.7907</v>
       </c>
       <c r="G9" t="n">
-        <v>68072995.90000001</v>
-      </c>
-      <c r="H9" t="n">
-        <v>8.06</v>
-      </c>
+        <v>10781779.8</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>19830</v>
+        <v>31050</v>
       </c>
       <c r="F10" t="n">
-        <v>2747.2455</v>
+        <v>347.2393</v>
       </c>
       <c r="G10" t="n">
-        <v>54477878.1</v>
+        <v>10781779.8</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -782,30 +780,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>37100</v>
+        <v>38500</v>
       </c>
       <c r="F11" t="n">
-        <v>293.6813</v>
+        <v>280.0462</v>
       </c>
       <c r="G11" t="n">
-        <v>10895575.6</v>
+        <v>10781779.8</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -814,13 +812,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>80200</v>
+        <v>50100</v>
       </c>
       <c r="F12" t="n">
-        <v>407.5652</v>
+        <v>645.6156</v>
       </c>
       <c r="G12" t="n">
-        <v>32686726.8</v>
+        <v>32345339.5</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -832,12 +830,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -846,13 +844,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>31600</v>
+        <v>9990</v>
       </c>
       <c r="F13" t="n">
-        <v>344.7967</v>
+        <v>3271.9446</v>
       </c>
       <c r="G13" t="n">
-        <v>10895575.6</v>
+        <v>32686726.8</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -864,76 +862,78 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>38200</v>
+        <v>32000</v>
       </c>
       <c r="F14" t="n">
-        <v>855.6735</v>
+        <v>2127.2811</v>
       </c>
       <c r="G14" t="n">
-        <v>32686726.8</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>68072995.90000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>87800</v>
+        <v>19830</v>
       </c>
       <c r="F15" t="n">
-        <v>384.5603</v>
+        <v>2747.2455</v>
       </c>
       <c r="G15" t="n">
-        <v>33764396.5</v>
+        <v>54477878.1</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -942,126 +942,126 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>52400</v>
+        <v>37100</v>
       </c>
       <c r="F16" t="n">
-        <v>636.0417</v>
+        <v>293.6813</v>
       </c>
       <c r="G16" t="n">
-        <v>33328583.4</v>
+        <v>10895575.6</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10250</v>
+        <v>80200</v>
       </c>
       <c r="F17" t="n">
-        <v>3328.756</v>
+        <v>407.5652</v>
       </c>
       <c r="G17" t="n">
-        <v>34119749</v>
+        <v>32686726.8</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>10090</v>
+        <v>31600</v>
       </c>
       <c r="F18" t="n">
-        <v>3333.5276</v>
+        <v>344.7967</v>
       </c>
       <c r="G18" t="n">
-        <v>33635293.3</v>
+        <v>10895575.6</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53200</v>
+        <v>38200</v>
       </c>
       <c r="F19" t="n">
-        <v>632.2424</v>
+        <v>855.6735</v>
       </c>
       <c r="G19" t="n">
-        <v>33635293.3</v>
+        <v>32686726.8</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1070,160 +1070,158 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>35050</v>
+        <v>87800</v>
       </c>
       <c r="F20" t="n">
-        <v>941.2811</v>
+        <v>384.5603</v>
       </c>
       <c r="G20" t="n">
-        <v>32991903.3</v>
+        <v>33764396.5</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>29100</v>
+        <v>52400</v>
       </c>
       <c r="F21" t="n">
-        <v>1976.0221</v>
+        <v>636.0417</v>
       </c>
       <c r="G21" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>33328583.4</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>43700</v>
+        <v>10250</v>
       </c>
       <c r="F22" t="n">
-        <v>1509.9269</v>
+        <v>3328.756</v>
       </c>
       <c r="G22" t="n">
-        <v>65983806.6</v>
+        <v>34119749</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>49500</v>
+        <v>10090</v>
       </c>
       <c r="F23" t="n">
-        <v>1333.0062</v>
+        <v>3333.5276</v>
       </c>
       <c r="G23" t="n">
-        <v>65983806.6</v>
+        <v>33635293.3</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>86300</v>
+        <v>53200</v>
       </c>
       <c r="F24" t="n">
-        <v>366.4646</v>
+        <v>632.2424</v>
       </c>
       <c r="G24" t="n">
-        <v>31625898.5</v>
+        <v>33635293.3</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1232,94 +1230,96 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>8490</v>
+        <v>35050</v>
       </c>
       <c r="F25" t="n">
-        <v>3672.3539</v>
+        <v>941.2811</v>
       </c>
       <c r="G25" t="n">
-        <v>31178284.6</v>
+        <v>32991903.3</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>45500</v>
+        <v>29100</v>
       </c>
       <c r="F26" t="n">
-        <v>685.237</v>
+        <v>1976.0221</v>
       </c>
       <c r="G26" t="n">
-        <v>31178284.6</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>7520</v>
+        <v>43700</v>
       </c>
       <c r="F27" t="n">
-        <v>4087.0231</v>
+        <v>1509.9269</v>
       </c>
       <c r="G27" t="n">
-        <v>30734413.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1328,52 +1328,52 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>83000</v>
+        <v>49500</v>
       </c>
       <c r="F28" t="n">
-        <v>370.2941</v>
+        <v>1333.0062</v>
       </c>
       <c r="G28" t="n">
-        <v>30734413.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>47750</v>
+        <v>86300</v>
       </c>
       <c r="F29" t="n">
-        <v>643.6526</v>
+        <v>366.4646</v>
       </c>
       <c r="G29" t="n">
-        <v>30734413.9</v>
+        <v>31625898.5</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1388,34 +1388,34 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>8080</v>
+        <v>8490</v>
       </c>
       <c r="F30" t="n">
-        <v>3746.0511</v>
+        <v>3672.3539</v>
       </c>
       <c r="G30" t="n">
-        <v>30268092.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1424,194 +1424,190 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>21950</v>
+        <v>45500</v>
       </c>
       <c r="F31" t="n">
-        <v>1378.9564</v>
+        <v>685.237</v>
       </c>
       <c r="G31" t="n">
-        <v>30268092.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>22750</v>
+        <v>7520</v>
       </c>
       <c r="F32" t="n">
-        <v>2200.9656</v>
+        <v>4087.0231</v>
       </c>
       <c r="G32" t="n">
-        <v>50071968.5</v>
+        <v>30734413.9</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>33150</v>
+        <v>83000</v>
       </c>
       <c r="F33" t="n">
-        <v>921.4443</v>
+        <v>370.2941</v>
       </c>
       <c r="G33" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2</v>
-      </c>
+        <v>30734413.9</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>38050</v>
+        <v>47750</v>
       </c>
       <c r="F34" t="n">
-        <v>790.1567</v>
+        <v>643.6526</v>
       </c>
       <c r="G34" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.4</v>
-      </c>
+        <v>30734413.9</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>28850</v>
+        <v>8080</v>
       </c>
       <c r="F35" t="n">
-        <v>1038.0221</v>
+        <v>3746.0511</v>
       </c>
       <c r="G35" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>76400</v>
+        <v>21950</v>
       </c>
       <c r="F36" t="n">
-        <v>391.9756</v>
+        <v>1378.9564</v>
       </c>
       <c r="G36" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1620,20 +1616,20 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>21650</v>
+        <v>22750</v>
       </c>
       <c r="F37" t="n">
-        <v>1383.2304</v>
+        <v>2200.9656</v>
       </c>
       <c r="G37" t="n">
-        <v>29946939</v>
+        <v>50071968.5</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1648,24 +1644,26 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>32500</v>
+        <v>33150</v>
       </c>
       <c r="F38" t="n">
         <v>921.4443</v>
       </c>
       <c r="G38" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1680,83 +1678,245 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>37900</v>
+        <v>38050</v>
       </c>
       <c r="F39" t="n">
         <v>790.1567</v>
       </c>
       <c r="G39" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>25300</v>
+        <v>28850</v>
       </c>
       <c r="F40" t="n">
-        <v>1186</v>
+        <v>1038.0221</v>
       </c>
       <c r="G40" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>126340</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>76400</v>
+      </c>
+      <c r="F41" t="n">
+        <v>391.9756</v>
+      </c>
+      <c r="G41" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>21650</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1383.2304</v>
+      </c>
+      <c r="G42" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F43" t="n">
+        <v>921.4443</v>
+      </c>
+      <c r="G43" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F44" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G44" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G45" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E46" t="n">
         <v>32000</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F46" t="n">
         <v>938</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G46" t="n">
         <v>30016000</v>
       </c>
-      <c r="H41" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,62 +492,64 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>20400</v>
+        <v>8720</v>
       </c>
       <c r="F2" t="n">
-        <v>1577.2548</v>
+        <v>3255.4339</v>
       </c>
       <c r="G2" t="n">
-        <v>32175998.7</v>
+        <v>28387383.9</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>37600</v>
+        <v>16930</v>
       </c>
       <c r="F3" t="n">
-        <v>285.2482</v>
+        <v>4324.5003</v>
       </c>
       <c r="G3" t="n">
-        <v>10725332.9</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>73213790.59999999</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-15.51</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,30 +558,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30100</v>
+        <v>33050</v>
       </c>
       <c r="F4" t="n">
-        <v>356.3234</v>
+        <v>858.9224</v>
       </c>
       <c r="G4" t="n">
-        <v>10725332.9</v>
+        <v>28387383.9</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,30 +590,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>36800</v>
+        <v>73500</v>
       </c>
       <c r="F5" t="n">
-        <v>874.3478</v>
+        <v>386.2229</v>
       </c>
       <c r="G5" t="n">
-        <v>32175998.7</v>
+        <v>28387383.9</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -620,62 +622,64 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>46400</v>
+        <v>28400</v>
       </c>
       <c r="F6" t="n">
-        <v>693.4482</v>
+        <v>999.5558</v>
       </c>
       <c r="G6" t="n">
-        <v>32175998.7</v>
+        <v>28387383.9</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9520</v>
+        <v>30500</v>
       </c>
       <c r="F7" t="n">
-        <v>1132.5399</v>
+        <v>3519.9944</v>
       </c>
       <c r="G7" t="n">
-        <v>10781779.8</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>107359829.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-24.2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,62 +688,62 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>38400</v>
+        <v>38850</v>
       </c>
       <c r="F8" t="n">
-        <v>561.551</v>
+        <v>730.692</v>
       </c>
       <c r="G8" t="n">
-        <v>21563559.7</v>
+        <v>28387383.9</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>79400</v>
+        <v>37600</v>
       </c>
       <c r="F9" t="n">
-        <v>135.7907</v>
+        <v>2516.612</v>
       </c>
       <c r="G9" t="n">
-        <v>10781779.8</v>
+        <v>94624613</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -748,30 +752,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>31050</v>
+        <v>20400</v>
       </c>
       <c r="F10" t="n">
-        <v>347.2393</v>
+        <v>1577.2548</v>
       </c>
       <c r="G10" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -780,30 +784,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>38500</v>
+        <v>37600</v>
       </c>
       <c r="F11" t="n">
-        <v>280.0462</v>
+        <v>285.2482</v>
       </c>
       <c r="G11" t="n">
-        <v>10781779.8</v>
+        <v>10725332.9</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -812,30 +816,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>50100</v>
+        <v>30100</v>
       </c>
       <c r="F12" t="n">
-        <v>645.6156</v>
+        <v>356.3234</v>
       </c>
       <c r="G12" t="n">
-        <v>32345339.5</v>
+        <v>10725332.9</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -844,86 +848,84 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9990</v>
+        <v>36800</v>
       </c>
       <c r="F13" t="n">
-        <v>3271.9446</v>
+        <v>874.3478</v>
       </c>
       <c r="G13" t="n">
-        <v>32686726.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>32000</v>
+        <v>46400</v>
       </c>
       <c r="F14" t="n">
-        <v>2127.2811</v>
+        <v>693.4482</v>
       </c>
       <c r="G14" t="n">
-        <v>68072995.90000001</v>
-      </c>
-      <c r="H14" t="n">
-        <v>8.06</v>
-      </c>
+        <v>32175998.7</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>19830</v>
+        <v>9520</v>
       </c>
       <c r="F15" t="n">
-        <v>2747.2455</v>
+        <v>1132.5399</v>
       </c>
       <c r="G15" t="n">
-        <v>54477878.1</v>
+        <v>10781779.8</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -942,20 +944,20 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>37100</v>
+        <v>38400</v>
       </c>
       <c r="F16" t="n">
-        <v>293.6813</v>
+        <v>561.551</v>
       </c>
       <c r="G16" t="n">
-        <v>10895575.6</v>
+        <v>21563559.7</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -974,20 +976,20 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>80200</v>
+        <v>79400</v>
       </c>
       <c r="F17" t="n">
-        <v>407.5652</v>
+        <v>135.7907</v>
       </c>
       <c r="G17" t="n">
-        <v>32686726.8</v>
+        <v>10781779.8</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1006,20 +1008,20 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>31600</v>
+        <v>31050</v>
       </c>
       <c r="F18" t="n">
-        <v>344.7967</v>
+        <v>347.2393</v>
       </c>
       <c r="G18" t="n">
-        <v>10895575.6</v>
+        <v>10781779.8</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1038,30 +1040,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>38200</v>
+        <v>38500</v>
       </c>
       <c r="F19" t="n">
-        <v>855.6735</v>
+        <v>280.0462</v>
       </c>
       <c r="G19" t="n">
-        <v>32686726.8</v>
+        <v>10781779.8</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1070,30 +1072,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>87800</v>
+        <v>50100</v>
       </c>
       <c r="F20" t="n">
-        <v>384.5603</v>
+        <v>645.6156</v>
       </c>
       <c r="G20" t="n">
-        <v>33764396.5</v>
+        <v>32345339.5</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1102,126 +1104,128 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>52400</v>
+        <v>9990</v>
       </c>
       <c r="F21" t="n">
-        <v>636.0417</v>
+        <v>3271.9446</v>
       </c>
       <c r="G21" t="n">
-        <v>33328583.4</v>
+        <v>32686726.8</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>10250</v>
+        <v>32000</v>
       </c>
       <c r="F22" t="n">
-        <v>3328.756</v>
+        <v>2127.2811</v>
       </c>
       <c r="G22" t="n">
-        <v>34119749</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>68072995.90000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>10090</v>
+        <v>19830</v>
       </c>
       <c r="F23" t="n">
-        <v>3333.5276</v>
+        <v>2747.2455</v>
       </c>
       <c r="G23" t="n">
-        <v>33635293.3</v>
+        <v>54477878.1</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53200</v>
+        <v>37100</v>
       </c>
       <c r="F24" t="n">
-        <v>632.2424</v>
+        <v>293.6813</v>
       </c>
       <c r="G24" t="n">
-        <v>33635293.3</v>
+        <v>10895575.6</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1230,54 +1234,52 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>35050</v>
+        <v>80200</v>
       </c>
       <c r="F25" t="n">
-        <v>941.2811</v>
+        <v>407.5652</v>
       </c>
       <c r="G25" t="n">
-        <v>32991903.3</v>
+        <v>32686726.8</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>29100</v>
+        <v>31600</v>
       </c>
       <c r="F26" t="n">
-        <v>1976.0221</v>
+        <v>344.7967</v>
       </c>
       <c r="G26" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>10895575.6</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1292,34 +1294,34 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>43700</v>
+        <v>38200</v>
       </c>
       <c r="F27" t="n">
-        <v>1509.9269</v>
+        <v>855.6735</v>
       </c>
       <c r="G27" t="n">
-        <v>65983806.6</v>
+        <v>32686726.8</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1328,30 +1330,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>49500</v>
+        <v>87800</v>
       </c>
       <c r="F28" t="n">
-        <v>1333.0062</v>
+        <v>384.5603</v>
       </c>
       <c r="G28" t="n">
-        <v>65983806.6</v>
+        <v>33764396.5</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1360,20 +1362,20 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>86300</v>
+        <v>52400</v>
       </c>
       <c r="F29" t="n">
-        <v>366.4646</v>
+        <v>636.0417</v>
       </c>
       <c r="G29" t="n">
-        <v>31625898.5</v>
+        <v>33328583.4</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1388,98 +1390,98 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>8490</v>
+        <v>10250</v>
       </c>
       <c r="F30" t="n">
-        <v>3672.3539</v>
+        <v>3328.756</v>
       </c>
       <c r="G30" t="n">
-        <v>31178284.6</v>
+        <v>34119749</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>45500</v>
+        <v>10090</v>
       </c>
       <c r="F31" t="n">
-        <v>685.237</v>
+        <v>3333.5276</v>
       </c>
       <c r="G31" t="n">
-        <v>31178284.6</v>
+        <v>33635293.3</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>7520</v>
+        <v>53200</v>
       </c>
       <c r="F32" t="n">
-        <v>4087.0231</v>
+        <v>632.2424</v>
       </c>
       <c r="G32" t="n">
-        <v>30734413.9</v>
+        <v>33635293.3</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1488,62 +1490,64 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>83000</v>
+        <v>35050</v>
       </c>
       <c r="F33" t="n">
-        <v>370.2941</v>
+        <v>941.2811</v>
       </c>
       <c r="G33" t="n">
-        <v>30734413.9</v>
+        <v>32991903.3</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>47750</v>
+        <v>29100</v>
       </c>
       <c r="F34" t="n">
-        <v>643.6526</v>
+        <v>1976.0221</v>
       </c>
       <c r="G34" t="n">
-        <v>30734413.9</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1552,30 +1556,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>8080</v>
+        <v>43700</v>
       </c>
       <c r="F35" t="n">
-        <v>3746.0511</v>
+        <v>1509.9269</v>
       </c>
       <c r="G35" t="n">
-        <v>30268092.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1584,130 +1588,126 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>21950</v>
+        <v>49500</v>
       </c>
       <c r="F36" t="n">
-        <v>1378.9564</v>
+        <v>1333.0062</v>
       </c>
       <c r="G36" t="n">
-        <v>30268092.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>22750</v>
+        <v>86300</v>
       </c>
       <c r="F37" t="n">
-        <v>2200.9656</v>
+        <v>366.4646</v>
       </c>
       <c r="G37" t="n">
-        <v>50071968.5</v>
+        <v>31625898.5</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>33150</v>
+        <v>8490</v>
       </c>
       <c r="F38" t="n">
-        <v>921.4443</v>
+        <v>3672.3539</v>
       </c>
       <c r="G38" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H38" t="n">
-        <v>2</v>
-      </c>
+        <v>31178284.6</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>38050</v>
+        <v>45500</v>
       </c>
       <c r="F39" t="n">
-        <v>790.1567</v>
+        <v>685.237</v>
       </c>
       <c r="G39" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.4</v>
-      </c>
+        <v>31178284.6</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1716,20 +1716,20 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>28850</v>
+        <v>7520</v>
       </c>
       <c r="F40" t="n">
-        <v>1038.0221</v>
+        <v>4087.0231</v>
       </c>
       <c r="G40" t="n">
-        <v>29946939</v>
+        <v>30734413.9</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1744,34 +1744,34 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>76400</v>
+        <v>83000</v>
       </c>
       <c r="F41" t="n">
-        <v>391.9756</v>
+        <v>370.2941</v>
       </c>
       <c r="G41" t="n">
-        <v>29946939</v>
+        <v>30734413.9</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1780,30 +1780,30 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>21650</v>
+        <v>47750</v>
       </c>
       <c r="F42" t="n">
-        <v>1383.2304</v>
+        <v>643.6526</v>
       </c>
       <c r="G42" t="n">
-        <v>29946939</v>
+        <v>30734413.9</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1812,62 +1812,62 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>32500</v>
+        <v>8080</v>
       </c>
       <c r="F43" t="n">
-        <v>921.4443</v>
+        <v>3746.0511</v>
       </c>
       <c r="G43" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>37900</v>
+        <v>21950</v>
       </c>
       <c r="F44" t="n">
-        <v>790.1567</v>
+        <v>1378.9564</v>
       </c>
       <c r="G44" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1876,47 +1876,307 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>25300</v>
+        <v>22750</v>
       </c>
       <c r="F45" t="n">
-        <v>1186</v>
+        <v>2200.9656</v>
       </c>
       <c r="G45" t="n">
-        <v>30005800</v>
+        <v>50071968.5</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>33150</v>
+      </c>
+      <c r="F46" t="n">
+        <v>921.4443</v>
+      </c>
+      <c r="G46" t="n">
+        <v>30545877.8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>38050</v>
+      </c>
+      <c r="F47" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G47" t="n">
+        <v>30065462.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>아이티센글로벌</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>124500</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>28850</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1038.0221</v>
+      </c>
+      <c r="G48" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>126340</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>76400</v>
+      </c>
+      <c r="F49" t="n">
+        <v>391.9756</v>
+      </c>
+      <c r="G49" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>21650</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1383.2304</v>
+      </c>
+      <c r="G50" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F51" t="n">
+        <v>921.4443</v>
+      </c>
+      <c r="G51" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F52" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G52" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G53" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E54" t="n">
         <v>32000</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F54" t="n">
         <v>938</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G54" t="n">
         <v>30016000</v>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,132 +488,130 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8720</v>
+        <v>9100</v>
       </c>
       <c r="F2" t="n">
-        <v>3255.4339</v>
+        <v>2259.594</v>
       </c>
       <c r="G2" t="n">
-        <v>28387383.9</v>
+        <v>20562305.7</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16930</v>
+        <v>39150</v>
       </c>
       <c r="F3" t="n">
-        <v>4324.5003</v>
+        <v>525.2184999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>73213790.59999999</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-15.51</v>
-      </c>
+        <v>20562305.7</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>33050</v>
+        <v>79900</v>
       </c>
       <c r="F4" t="n">
-        <v>858.9224</v>
+        <v>257.3505</v>
       </c>
       <c r="G4" t="n">
-        <v>28387383.9</v>
+        <v>20562305.7</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>73500</v>
+        <v>45500</v>
       </c>
       <c r="F5" t="n">
-        <v>386.2229</v>
+        <v>451.9188</v>
       </c>
       <c r="G5" t="n">
-        <v>28387383.9</v>
+        <v>20562305.7</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -622,13 +620,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28400</v>
+        <v>39050</v>
       </c>
       <c r="F6" t="n">
-        <v>999.5558</v>
+        <v>789.8453</v>
       </c>
       <c r="G6" t="n">
-        <v>28387383.9</v>
+        <v>30843458.5</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -640,31 +638,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>30500</v>
+        <v>8720</v>
       </c>
       <c r="F7" t="n">
-        <v>3519.9944</v>
+        <v>3255.4339</v>
       </c>
       <c r="G7" t="n">
-        <v>107359829.8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-24.2</v>
-      </c>
+        <v>28387383.9</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -674,29 +670,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>38850</v>
+        <v>16930</v>
       </c>
       <c r="F8" t="n">
-        <v>730.692</v>
+        <v>4324.5003</v>
       </c>
       <c r="G8" t="n">
-        <v>28387383.9</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>73213790.59999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-15.51</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -706,44 +704,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>37600</v>
+        <v>33050</v>
       </c>
       <c r="F9" t="n">
-        <v>2516.612</v>
+        <v>858.9224</v>
       </c>
       <c r="G9" t="n">
-        <v>94624613</v>
+        <v>28387383.9</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -752,30 +750,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20400</v>
+        <v>73500</v>
       </c>
       <c r="F10" t="n">
-        <v>1577.2548</v>
+        <v>386.2229</v>
       </c>
       <c r="G10" t="n">
-        <v>32175998.7</v>
+        <v>28387383.9</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -784,62 +782,64 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>37600</v>
+        <v>28400</v>
       </c>
       <c r="F11" t="n">
-        <v>285.2482</v>
+        <v>999.5558</v>
       </c>
       <c r="G11" t="n">
-        <v>10725332.9</v>
+        <v>28387383.9</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>30100</v>
+        <v>30500</v>
       </c>
       <c r="F12" t="n">
-        <v>356.3234</v>
+        <v>3519.9944</v>
       </c>
       <c r="G12" t="n">
-        <v>10725332.9</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>107359829.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-24.2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -848,62 +848,62 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>36800</v>
+        <v>38850</v>
       </c>
       <c r="F13" t="n">
-        <v>874.3478</v>
+        <v>730.692</v>
       </c>
       <c r="G13" t="n">
-        <v>32175998.7</v>
+        <v>28387383.9</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>46400</v>
+        <v>37600</v>
       </c>
       <c r="F14" t="n">
-        <v>693.4482</v>
+        <v>2516.612</v>
       </c>
       <c r="G14" t="n">
-        <v>32175998.7</v>
+        <v>94624613</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -912,20 +912,20 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9520</v>
+        <v>20400</v>
       </c>
       <c r="F15" t="n">
-        <v>1132.5399</v>
+        <v>1577.2548</v>
       </c>
       <c r="G15" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -944,30 +944,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>38400</v>
+        <v>37600</v>
       </c>
       <c r="F16" t="n">
-        <v>561.551</v>
+        <v>285.2482</v>
       </c>
       <c r="G16" t="n">
-        <v>21563559.7</v>
+        <v>10725332.9</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -976,30 +976,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>79400</v>
+        <v>30100</v>
       </c>
       <c r="F17" t="n">
-        <v>135.7907</v>
+        <v>356.3234</v>
       </c>
       <c r="G17" t="n">
-        <v>10781779.8</v>
+        <v>10725332.9</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1008,30 +1008,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>31050</v>
+        <v>36800</v>
       </c>
       <c r="F18" t="n">
-        <v>347.2393</v>
+        <v>874.3478</v>
       </c>
       <c r="G18" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1040,13 +1040,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>38500</v>
+        <v>46400</v>
       </c>
       <c r="F19" t="n">
-        <v>280.0462</v>
+        <v>693.4482</v>
       </c>
       <c r="G19" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1072,30 +1072,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>50100</v>
+        <v>9520</v>
       </c>
       <c r="F20" t="n">
-        <v>645.6156</v>
+        <v>1132.5399</v>
       </c>
       <c r="G20" t="n">
-        <v>32345339.5</v>
+        <v>10781779.8</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1104,96 +1104,94 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9990</v>
+        <v>38400</v>
       </c>
       <c r="F21" t="n">
-        <v>3271.9446</v>
+        <v>561.551</v>
       </c>
       <c r="G21" t="n">
-        <v>32686726.8</v>
+        <v>21563559.7</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>32000</v>
+        <v>79400</v>
       </c>
       <c r="F22" t="n">
-        <v>2127.2811</v>
+        <v>135.7907</v>
       </c>
       <c r="G22" t="n">
-        <v>68072995.90000001</v>
-      </c>
-      <c r="H22" t="n">
-        <v>8.06</v>
-      </c>
+        <v>10781779.8</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>19830</v>
+        <v>31050</v>
       </c>
       <c r="F23" t="n">
-        <v>2747.2455</v>
+        <v>347.2393</v>
       </c>
       <c r="G23" t="n">
-        <v>54477878.1</v>
+        <v>10781779.8</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1202,30 +1200,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>37100</v>
+        <v>38500</v>
       </c>
       <c r="F24" t="n">
-        <v>293.6813</v>
+        <v>280.0462</v>
       </c>
       <c r="G24" t="n">
-        <v>10895575.6</v>
+        <v>10781779.8</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1234,13 +1232,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>80200</v>
+        <v>50100</v>
       </c>
       <c r="F25" t="n">
-        <v>407.5652</v>
+        <v>645.6156</v>
       </c>
       <c r="G25" t="n">
-        <v>32686726.8</v>
+        <v>32345339.5</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1252,12 +1250,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1266,13 +1264,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>31600</v>
+        <v>9990</v>
       </c>
       <c r="F26" t="n">
-        <v>344.7967</v>
+        <v>3271.9446</v>
       </c>
       <c r="G26" t="n">
-        <v>10895575.6</v>
+        <v>32686726.8</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1284,76 +1282,78 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>38200</v>
+        <v>32000</v>
       </c>
       <c r="F27" t="n">
-        <v>855.6735</v>
+        <v>2127.2811</v>
       </c>
       <c r="G27" t="n">
-        <v>32686726.8</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+        <v>68072995.90000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>87800</v>
+        <v>19830</v>
       </c>
       <c r="F28" t="n">
-        <v>384.5603</v>
+        <v>2747.2455</v>
       </c>
       <c r="G28" t="n">
-        <v>33764396.5</v>
+        <v>54477878.1</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1362,126 +1362,126 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>52400</v>
+        <v>37100</v>
       </c>
       <c r="F29" t="n">
-        <v>636.0417</v>
+        <v>293.6813</v>
       </c>
       <c r="G29" t="n">
-        <v>33328583.4</v>
+        <v>10895575.6</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10250</v>
+        <v>80200</v>
       </c>
       <c r="F30" t="n">
-        <v>3328.756</v>
+        <v>407.5652</v>
       </c>
       <c r="G30" t="n">
-        <v>34119749</v>
+        <v>32686726.8</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>10090</v>
+        <v>31600</v>
       </c>
       <c r="F31" t="n">
-        <v>3333.5276</v>
+        <v>344.7967</v>
       </c>
       <c r="G31" t="n">
-        <v>33635293.3</v>
+        <v>10895575.6</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53200</v>
+        <v>38200</v>
       </c>
       <c r="F32" t="n">
-        <v>632.2424</v>
+        <v>855.6735</v>
       </c>
       <c r="G32" t="n">
-        <v>33635293.3</v>
+        <v>32686726.8</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1490,160 +1490,158 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>35050</v>
+        <v>87800</v>
       </c>
       <c r="F33" t="n">
-        <v>941.2811</v>
+        <v>384.5603</v>
       </c>
       <c r="G33" t="n">
-        <v>32991903.3</v>
+        <v>33764396.5</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>29100</v>
+        <v>52400</v>
       </c>
       <c r="F34" t="n">
-        <v>1976.0221</v>
+        <v>636.0417</v>
       </c>
       <c r="G34" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>33328583.4</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>43700</v>
+        <v>10250</v>
       </c>
       <c r="F35" t="n">
-        <v>1509.9269</v>
+        <v>3328.756</v>
       </c>
       <c r="G35" t="n">
-        <v>65983806.6</v>
+        <v>34119749</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>49500</v>
+        <v>10090</v>
       </c>
       <c r="F36" t="n">
-        <v>1333.0062</v>
+        <v>3333.5276</v>
       </c>
       <c r="G36" t="n">
-        <v>65983806.6</v>
+        <v>33635293.3</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>86300</v>
+        <v>53200</v>
       </c>
       <c r="F37" t="n">
-        <v>366.4646</v>
+        <v>632.2424</v>
       </c>
       <c r="G37" t="n">
-        <v>31625898.5</v>
+        <v>33635293.3</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1652,94 +1650,96 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>8490</v>
+        <v>35050</v>
       </c>
       <c r="F38" t="n">
-        <v>3672.3539</v>
+        <v>941.2811</v>
       </c>
       <c r="G38" t="n">
-        <v>31178284.6</v>
+        <v>32991903.3</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>45500</v>
+        <v>29100</v>
       </c>
       <c r="F39" t="n">
-        <v>685.237</v>
+        <v>1976.0221</v>
       </c>
       <c r="G39" t="n">
-        <v>31178284.6</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>7520</v>
+        <v>43700</v>
       </c>
       <c r="F40" t="n">
-        <v>4087.0231</v>
+        <v>1509.9269</v>
       </c>
       <c r="G40" t="n">
-        <v>30734413.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1748,52 +1748,52 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>83000</v>
+        <v>49500</v>
       </c>
       <c r="F41" t="n">
-        <v>370.2941</v>
+        <v>1333.0062</v>
       </c>
       <c r="G41" t="n">
-        <v>30734413.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>47750</v>
+        <v>86300</v>
       </c>
       <c r="F42" t="n">
-        <v>643.6526</v>
+        <v>366.4646</v>
       </c>
       <c r="G42" t="n">
-        <v>30734413.9</v>
+        <v>31625898.5</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1808,34 +1808,34 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8080</v>
+        <v>8490</v>
       </c>
       <c r="F43" t="n">
-        <v>3746.0511</v>
+        <v>3672.3539</v>
       </c>
       <c r="G43" t="n">
-        <v>30268092.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1844,194 +1844,190 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>21950</v>
+        <v>45500</v>
       </c>
       <c r="F44" t="n">
-        <v>1378.9564</v>
+        <v>685.237</v>
       </c>
       <c r="G44" t="n">
-        <v>30268092.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>22750</v>
+        <v>7520</v>
       </c>
       <c r="F45" t="n">
-        <v>2200.9656</v>
+        <v>4087.0231</v>
       </c>
       <c r="G45" t="n">
-        <v>50071968.5</v>
+        <v>30734413.9</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>33150</v>
+        <v>83000</v>
       </c>
       <c r="F46" t="n">
-        <v>921.4443</v>
+        <v>370.2941</v>
       </c>
       <c r="G46" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H46" t="n">
-        <v>2</v>
-      </c>
+        <v>30734413.9</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>38050</v>
+        <v>47750</v>
       </c>
       <c r="F47" t="n">
-        <v>790.1567</v>
+        <v>643.6526</v>
       </c>
       <c r="G47" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.4</v>
-      </c>
+        <v>30734413.9</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>28850</v>
+        <v>8080</v>
       </c>
       <c r="F48" t="n">
-        <v>1038.0221</v>
+        <v>3746.0511</v>
       </c>
       <c r="G48" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>76400</v>
+        <v>21950</v>
       </c>
       <c r="F49" t="n">
-        <v>391.9756</v>
+        <v>1378.9564</v>
       </c>
       <c r="G49" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2040,20 +2036,20 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>21650</v>
+        <v>22750</v>
       </c>
       <c r="F50" t="n">
-        <v>1383.2304</v>
+        <v>2200.9656</v>
       </c>
       <c r="G50" t="n">
-        <v>29946939</v>
+        <v>50071968.5</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2068,24 +2064,26 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>32500</v>
+        <v>33150</v>
       </c>
       <c r="F51" t="n">
         <v>921.4443</v>
       </c>
       <c r="G51" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2100,83 +2098,245 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>37900</v>
+        <v>38050</v>
       </c>
       <c r="F52" t="n">
         <v>790.1567</v>
       </c>
       <c r="G52" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>25300</v>
+        <v>28850</v>
       </c>
       <c r="F53" t="n">
-        <v>1186</v>
+        <v>1038.0221</v>
       </c>
       <c r="G53" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>126340</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>76400</v>
+      </c>
+      <c r="F54" t="n">
+        <v>391.9756</v>
+      </c>
+      <c r="G54" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>21650</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1383.2304</v>
+      </c>
+      <c r="G55" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F56" t="n">
+        <v>921.4443</v>
+      </c>
+      <c r="G56" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F57" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G57" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G58" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="E59" t="n">
         <v>32000</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F59" t="n">
         <v>938</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G59" t="n">
         <v>30016000</v>
       </c>
-      <c r="H54" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,24 +488,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9100</v>
+        <v>7490</v>
       </c>
       <c r="F2" t="n">
-        <v>2259.594</v>
+        <v>10243.469</v>
       </c>
       <c r="G2" t="n">
-        <v>20562305.7</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>76723582.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-15.37</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -520,24 +522,24 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>39150</v>
+        <v>30500</v>
       </c>
       <c r="F3" t="n">
-        <v>525.2184999999999</v>
+        <v>963.2346</v>
       </c>
       <c r="G3" t="n">
-        <v>20562305.7</v>
+        <v>29378655.8</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -556,13 +558,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>79900</v>
+        <v>88400</v>
       </c>
       <c r="F4" t="n">
-        <v>257.3505</v>
+        <v>332.3377</v>
       </c>
       <c r="G4" t="n">
-        <v>20562305.7</v>
+        <v>29378655.8</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -574,12 +576,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,10 +590,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>45500</v>
+        <v>9100</v>
       </c>
       <c r="F5" t="n">
-        <v>451.9188</v>
+        <v>2259.594</v>
       </c>
       <c r="G5" t="n">
         <v>20562305.7</v>
@@ -606,110 +608,108 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>39050</v>
+        <v>39150</v>
       </c>
       <c r="F6" t="n">
-        <v>789.8453</v>
+        <v>525.2184999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>30843458.5</v>
+        <v>20562305.7</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8720</v>
+        <v>79900</v>
       </c>
       <c r="F7" t="n">
-        <v>3255.4339</v>
+        <v>257.3505</v>
       </c>
       <c r="G7" t="n">
-        <v>28387383.9</v>
+        <v>20562305.7</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16930</v>
+        <v>45500</v>
       </c>
       <c r="F8" t="n">
-        <v>4324.5003</v>
+        <v>451.9188</v>
       </c>
       <c r="G8" t="n">
-        <v>73213790.59999999</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-15.51</v>
-      </c>
+        <v>20562305.7</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>33050</v>
+        <v>39050</v>
       </c>
       <c r="F9" t="n">
-        <v>858.9224</v>
+        <v>789.8453</v>
       </c>
       <c r="G9" t="n">
-        <v>28387383.9</v>
+        <v>30843458.5</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73500</v>
+        <v>8720</v>
       </c>
       <c r="F10" t="n">
-        <v>386.2229</v>
+        <v>3255.4339</v>
       </c>
       <c r="G10" t="n">
         <v>28387383.9</v>
@@ -768,29 +768,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>28400</v>
+        <v>16930</v>
       </c>
       <c r="F11" t="n">
-        <v>999.5558</v>
+        <v>4324.5003</v>
       </c>
       <c r="G11" t="n">
-        <v>28387383.9</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>73213790.59999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-15.51</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -800,31 +802,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>30500</v>
+        <v>33050</v>
       </c>
       <c r="F12" t="n">
-        <v>3519.9944</v>
+        <v>858.9224</v>
       </c>
       <c r="G12" t="n">
-        <v>107359829.8</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-24.2</v>
-      </c>
+        <v>28387383.9</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>38850</v>
+        <v>73500</v>
       </c>
       <c r="F13" t="n">
-        <v>730.692</v>
+        <v>386.2229</v>
       </c>
       <c r="G13" t="n">
         <v>28387383.9</v>
@@ -866,76 +866,78 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>37600</v>
+        <v>28400</v>
       </c>
       <c r="F14" t="n">
-        <v>2516.612</v>
+        <v>999.5558</v>
       </c>
       <c r="G14" t="n">
-        <v>94624613</v>
+        <v>28387383.9</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>20400</v>
+        <v>30500</v>
       </c>
       <c r="F15" t="n">
-        <v>1577.2548</v>
+        <v>3519.9944</v>
       </c>
       <c r="G15" t="n">
-        <v>32175998.7</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>107359829.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-24.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -944,45 +946,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>37600</v>
+        <v>38850</v>
       </c>
       <c r="F16" t="n">
-        <v>285.2482</v>
+        <v>730.692</v>
       </c>
       <c r="G16" t="n">
-        <v>10725332.9</v>
+        <v>28387383.9</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>30100</v>
+        <v>37600</v>
       </c>
       <c r="F17" t="n">
-        <v>356.3234</v>
+        <v>2516.612</v>
       </c>
       <c r="G17" t="n">
-        <v>10725332.9</v>
+        <v>94624613</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -994,12 +996,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1008,10 +1010,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>36800</v>
+        <v>20400</v>
       </c>
       <c r="F18" t="n">
-        <v>874.3478</v>
+        <v>1577.2548</v>
       </c>
       <c r="G18" t="n">
         <v>32175998.7</v>
@@ -1026,12 +1028,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1040,30 +1042,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>46400</v>
+        <v>37600</v>
       </c>
       <c r="F19" t="n">
-        <v>693.4482</v>
+        <v>285.2482</v>
       </c>
       <c r="G19" t="n">
-        <v>32175998.7</v>
+        <v>10725332.9</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1072,30 +1074,30 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9520</v>
+        <v>30100</v>
       </c>
       <c r="F20" t="n">
-        <v>1132.5399</v>
+        <v>356.3234</v>
       </c>
       <c r="G20" t="n">
-        <v>10781779.8</v>
+        <v>10725332.9</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1104,30 +1106,30 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>38400</v>
+        <v>36800</v>
       </c>
       <c r="F21" t="n">
-        <v>561.551</v>
+        <v>874.3478</v>
       </c>
       <c r="G21" t="n">
-        <v>21563559.7</v>
+        <v>32175998.7</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1136,13 +1138,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>79400</v>
+        <v>46400</v>
       </c>
       <c r="F22" t="n">
-        <v>135.7907</v>
+        <v>693.4482</v>
       </c>
       <c r="G22" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1154,12 +1156,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1168,10 +1170,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>31050</v>
+        <v>9520</v>
       </c>
       <c r="F23" t="n">
-        <v>347.2393</v>
+        <v>1132.5399</v>
       </c>
       <c r="G23" t="n">
         <v>10781779.8</v>
@@ -1186,12 +1188,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1200,13 +1202,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>38500</v>
+        <v>38400</v>
       </c>
       <c r="F24" t="n">
-        <v>280.0462</v>
+        <v>561.551</v>
       </c>
       <c r="G24" t="n">
-        <v>10781779.8</v>
+        <v>21563559.7</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1218,12 +1220,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1232,30 +1234,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>50100</v>
+        <v>79400</v>
       </c>
       <c r="F25" t="n">
-        <v>645.6156</v>
+        <v>135.7907</v>
       </c>
       <c r="G25" t="n">
-        <v>32345339.5</v>
+        <v>10781779.8</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1264,79 +1266,77 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>9990</v>
+        <v>31050</v>
       </c>
       <c r="F26" t="n">
-        <v>3271.9446</v>
+        <v>347.2393</v>
       </c>
       <c r="G26" t="n">
-        <v>32686726.8</v>
+        <v>10781779.8</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>32000</v>
+        <v>38500</v>
       </c>
       <c r="F27" t="n">
-        <v>2127.2811</v>
+        <v>280.0462</v>
       </c>
       <c r="G27" t="n">
-        <v>68072995.90000001</v>
-      </c>
-      <c r="H27" t="n">
-        <v>8.06</v>
-      </c>
+        <v>10781779.8</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>19830</v>
+        <v>50100</v>
       </c>
       <c r="F28" t="n">
-        <v>2747.2455</v>
+        <v>645.6156</v>
       </c>
       <c r="G28" t="n">
-        <v>54477878.1</v>
+        <v>32345339.5</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>37100</v>
+        <v>9990</v>
       </c>
       <c r="F29" t="n">
-        <v>293.6813</v>
+        <v>3271.9446</v>
       </c>
       <c r="G29" t="n">
-        <v>10895575.6</v>
+        <v>32686726.8</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1380,29 +1380,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>80200</v>
+        <v>32000</v>
       </c>
       <c r="F30" t="n">
-        <v>407.5652</v>
+        <v>2127.2811</v>
       </c>
       <c r="G30" t="n">
-        <v>32686726.8</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>68072995.90000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1412,27 +1414,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>31600</v>
+        <v>19830</v>
       </c>
       <c r="F31" t="n">
-        <v>344.7967</v>
+        <v>2747.2455</v>
       </c>
       <c r="G31" t="n">
-        <v>10895575.6</v>
+        <v>54477878.1</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1444,12 +1446,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1458,20 +1460,20 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>38200</v>
+        <v>37100</v>
       </c>
       <c r="F32" t="n">
-        <v>855.6735</v>
+        <v>293.6813</v>
       </c>
       <c r="G32" t="n">
-        <v>32686726.8</v>
+        <v>10895575.6</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1490,30 +1492,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>87800</v>
+        <v>80200</v>
       </c>
       <c r="F33" t="n">
-        <v>384.5603</v>
+        <v>407.5652</v>
       </c>
       <c r="G33" t="n">
-        <v>33764396.5</v>
+        <v>32686726.8</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1522,84 +1524,84 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>52400</v>
+        <v>31600</v>
       </c>
       <c r="F34" t="n">
-        <v>636.0417</v>
+        <v>344.7967</v>
       </c>
       <c r="G34" t="n">
-        <v>33328583.4</v>
+        <v>10895575.6</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10250</v>
+        <v>38200</v>
       </c>
       <c r="F35" t="n">
-        <v>3328.756</v>
+        <v>855.6735</v>
       </c>
       <c r="G35" t="n">
-        <v>34119749</v>
+        <v>32686726.8</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>10090</v>
+        <v>87800</v>
       </c>
       <c r="F36" t="n">
-        <v>3333.5276</v>
+        <v>384.5603</v>
       </c>
       <c r="G36" t="n">
-        <v>33635293.3</v>
+        <v>33764396.5</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1614,115 +1616,113 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53200</v>
+        <v>52400</v>
       </c>
       <c r="F37" t="n">
-        <v>632.2424</v>
+        <v>636.0417</v>
       </c>
       <c r="G37" t="n">
-        <v>33635293.3</v>
+        <v>33328583.4</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>35050</v>
+        <v>10250</v>
       </c>
       <c r="F38" t="n">
-        <v>941.2811</v>
+        <v>3328.756</v>
       </c>
       <c r="G38" t="n">
-        <v>32991903.3</v>
+        <v>34119749</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>29100</v>
+        <v>10090</v>
       </c>
       <c r="F39" t="n">
-        <v>1976.0221</v>
+        <v>3333.5276</v>
       </c>
       <c r="G39" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>33635293.3</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>43700</v>
+        <v>53200</v>
       </c>
       <c r="F40" t="n">
-        <v>1509.9269</v>
+        <v>632.2424</v>
       </c>
       <c r="G40" t="n">
-        <v>65983806.6</v>
+        <v>33635293.3</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1748,84 +1748,86 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>49500</v>
+        <v>35050</v>
       </c>
       <c r="F41" t="n">
-        <v>1333.0062</v>
+        <v>941.2811</v>
       </c>
       <c r="G41" t="n">
-        <v>65983806.6</v>
+        <v>32991903.3</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>86300</v>
+        <v>29100</v>
       </c>
       <c r="F42" t="n">
-        <v>366.4646</v>
+        <v>1976.0221</v>
       </c>
       <c r="G42" t="n">
-        <v>31625898.5</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>8490</v>
+        <v>43700</v>
       </c>
       <c r="F43" t="n">
-        <v>3672.3539</v>
+        <v>1509.9269</v>
       </c>
       <c r="G43" t="n">
-        <v>31178284.6</v>
+        <v>65983806.6</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1844,30 +1846,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>45500</v>
+        <v>49500</v>
       </c>
       <c r="F44" t="n">
-        <v>685.237</v>
+        <v>1333.0062</v>
       </c>
       <c r="G44" t="n">
-        <v>31178284.6</v>
+        <v>65983806.6</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1876,30 +1878,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>7520</v>
+        <v>86300</v>
       </c>
       <c r="F45" t="n">
-        <v>4087.0231</v>
+        <v>366.4646</v>
       </c>
       <c r="G45" t="n">
-        <v>30734413.9</v>
+        <v>31625898.5</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1908,20 +1910,20 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>83000</v>
+        <v>8490</v>
       </c>
       <c r="F46" t="n">
-        <v>370.2941</v>
+        <v>3672.3539</v>
       </c>
       <c r="G46" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1936,24 +1938,24 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>47750</v>
+        <v>45500</v>
       </c>
       <c r="F47" t="n">
-        <v>643.6526</v>
+        <v>685.237</v>
       </c>
       <c r="G47" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1968,34 +1970,34 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8080</v>
+        <v>7520</v>
       </c>
       <c r="F48" t="n">
-        <v>3746.0511</v>
+        <v>4087.0231</v>
       </c>
       <c r="G48" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2004,30 +2006,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>21950</v>
+        <v>83000</v>
       </c>
       <c r="F49" t="n">
-        <v>1378.9564</v>
+        <v>370.2941</v>
       </c>
       <c r="G49" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2036,179 +2038,179 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>22750</v>
+        <v>47750</v>
       </c>
       <c r="F50" t="n">
-        <v>2200.9656</v>
+        <v>643.6526</v>
       </c>
       <c r="G50" t="n">
-        <v>50071968.5</v>
+        <v>30734413.9</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>33150</v>
+        <v>8080</v>
       </c>
       <c r="F51" t="n">
-        <v>921.4443</v>
+        <v>3746.0511</v>
       </c>
       <c r="G51" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H51" t="n">
-        <v>2</v>
-      </c>
+        <v>30268092.9</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>38050</v>
+        <v>21950</v>
       </c>
       <c r="F52" t="n">
-        <v>790.1567</v>
+        <v>1378.9564</v>
       </c>
       <c r="G52" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.4</v>
-      </c>
+        <v>30268092.9</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>28850</v>
+        <v>22750</v>
       </c>
       <c r="F53" t="n">
-        <v>1038.0221</v>
+        <v>2200.9656</v>
       </c>
       <c r="G53" t="n">
-        <v>29946939</v>
+        <v>50071968.5</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>76400</v>
+        <v>33150</v>
       </c>
       <c r="F54" t="n">
-        <v>391.9756</v>
+        <v>921.4443</v>
       </c>
       <c r="G54" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H54" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>21650</v>
+        <v>38050</v>
       </c>
       <c r="F55" t="n">
-        <v>1383.2304</v>
+        <v>790.1567</v>
       </c>
       <c r="G55" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2218,24 +2220,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>32500</v>
+        <v>28850</v>
       </c>
       <c r="F56" t="n">
-        <v>921.4443</v>
+        <v>1038.0221</v>
       </c>
       <c r="G56" t="n">
         <v>29946939</v>
@@ -2250,12 +2252,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2264,10 +2266,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>37900</v>
+        <v>76400</v>
       </c>
       <c r="F57" t="n">
-        <v>790.1567</v>
+        <v>391.9756</v>
       </c>
       <c r="G57" t="n">
         <v>29946939</v>
@@ -2277,17 +2279,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2296,47 +2298,143 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>25300</v>
+        <v>21650</v>
       </c>
       <c r="F58" t="n">
-        <v>1186</v>
+        <v>1383.2304</v>
       </c>
       <c r="G58" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F59" t="n">
+        <v>921.4443</v>
+      </c>
+      <c r="G59" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F60" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G60" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G61" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="E62" t="n">
         <v>32000</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F62" t="n">
         <v>938</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G62" t="n">
         <v>30016000</v>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,36 +473,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7490</v>
+        <v>36050</v>
       </c>
       <c r="F2" t="n">
-        <v>10243.469</v>
+        <v>869.3262999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>76723582.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-15.37</v>
-      </c>
+        <v>31339214.2</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,29 +510,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>30500</v>
+        <v>7490</v>
       </c>
       <c r="F3" t="n">
-        <v>963.2346</v>
+        <v>10243.469</v>
       </c>
       <c r="G3" t="n">
-        <v>29378655.8</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>76723582.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-15.37</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,24 +544,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>88400</v>
+        <v>30500</v>
       </c>
       <c r="F4" t="n">
-        <v>332.3377</v>
+        <v>963.2346</v>
       </c>
       <c r="G4" t="n">
         <v>29378655.8</v>
@@ -571,17 +571,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9100</v>
+        <v>88400</v>
       </c>
       <c r="F5" t="n">
-        <v>2259.594</v>
+        <v>332.3377</v>
       </c>
       <c r="G5" t="n">
-        <v>20562305.7</v>
+        <v>29378655.8</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -608,12 +608,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>39150</v>
+        <v>9100</v>
       </c>
       <c r="F6" t="n">
-        <v>525.2184999999999</v>
+        <v>2259.594</v>
       </c>
       <c r="G6" t="n">
         <v>20562305.7</v>
@@ -640,12 +640,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>79900</v>
+        <v>39150</v>
       </c>
       <c r="F7" t="n">
-        <v>257.3505</v>
+        <v>525.2184999999999</v>
       </c>
       <c r="G7" t="n">
         <v>20562305.7</v>
@@ -672,12 +672,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>45500</v>
+        <v>79900</v>
       </c>
       <c r="F8" t="n">
-        <v>451.9188</v>
+        <v>257.3505</v>
       </c>
       <c r="G8" t="n">
         <v>20562305.7</v>
@@ -704,44 +704,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>39050</v>
+        <v>45500</v>
       </c>
       <c r="F9" t="n">
-        <v>789.8453</v>
+        <v>451.9188</v>
       </c>
       <c r="G9" t="n">
-        <v>30843458.5</v>
+        <v>20562305.7</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8720</v>
+        <v>39050</v>
       </c>
       <c r="F10" t="n">
-        <v>3255.4339</v>
+        <v>789.8453</v>
       </c>
       <c r="G10" t="n">
-        <v>28387383.9</v>
+        <v>30843458.5</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -768,31 +768,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>16930</v>
+        <v>8720</v>
       </c>
       <c r="F11" t="n">
-        <v>4324.5003</v>
+        <v>3255.4339</v>
       </c>
       <c r="G11" t="n">
-        <v>73213790.59999999</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-15.51</v>
-      </c>
+        <v>28387383.9</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -802,29 +800,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>33050</v>
+        <v>16930</v>
       </c>
       <c r="F12" t="n">
-        <v>858.9224</v>
+        <v>4324.5003</v>
       </c>
       <c r="G12" t="n">
-        <v>28387383.9</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>73213790.59999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-15.51</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>73500</v>
+        <v>33050</v>
       </c>
       <c r="F13" t="n">
-        <v>386.2229</v>
+        <v>858.9224</v>
       </c>
       <c r="G13" t="n">
         <v>28387383.9</v>
@@ -866,12 +866,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>28400</v>
+        <v>73500</v>
       </c>
       <c r="F14" t="n">
-        <v>999.5558</v>
+        <v>386.2229</v>
       </c>
       <c r="G14" t="n">
         <v>28387383.9</v>
@@ -898,31 +898,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>30500</v>
+        <v>28400</v>
       </c>
       <c r="F15" t="n">
-        <v>3519.9944</v>
+        <v>999.5558</v>
       </c>
       <c r="G15" t="n">
-        <v>107359829.8</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-24.2</v>
-      </c>
+        <v>28387383.9</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -932,29 +930,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>38850</v>
+        <v>30500</v>
       </c>
       <c r="F16" t="n">
-        <v>730.692</v>
+        <v>3519.9944</v>
       </c>
       <c r="G16" t="n">
-        <v>28387383.9</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>107359829.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-24.2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -964,59 +964,59 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>37600</v>
+        <v>38850</v>
       </c>
       <c r="F17" t="n">
-        <v>2516.612</v>
+        <v>730.692</v>
       </c>
       <c r="G17" t="n">
-        <v>94624613</v>
+        <v>28387383.9</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>20400</v>
+        <v>37600</v>
       </c>
       <c r="F18" t="n">
-        <v>1577.2548</v>
+        <v>2516.612</v>
       </c>
       <c r="G18" t="n">
-        <v>32175998.7</v>
+        <v>94624613</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>37600</v>
+        <v>20400</v>
       </c>
       <c r="F19" t="n">
-        <v>285.2482</v>
+        <v>1577.2548</v>
       </c>
       <c r="G19" t="n">
-        <v>10725332.9</v>
+        <v>32175998.7</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1074,10 +1074,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>30100</v>
+        <v>37600</v>
       </c>
       <c r="F20" t="n">
-        <v>356.3234</v>
+        <v>285.2482</v>
       </c>
       <c r="G20" t="n">
         <v>10725332.9</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>36800</v>
+        <v>30100</v>
       </c>
       <c r="F21" t="n">
-        <v>874.3478</v>
+        <v>356.3234</v>
       </c>
       <c r="G21" t="n">
-        <v>32175998.7</v>
+        <v>10725332.9</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>46400</v>
+        <v>36800</v>
       </c>
       <c r="F22" t="n">
-        <v>693.4482</v>
+        <v>874.3478</v>
       </c>
       <c r="G22" t="n">
         <v>32175998.7</v>
@@ -1151,17 +1151,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9520</v>
+        <v>46400</v>
       </c>
       <c r="F23" t="n">
-        <v>1132.5399</v>
+        <v>693.4482</v>
       </c>
       <c r="G23" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>38400</v>
+        <v>9520</v>
       </c>
       <c r="F24" t="n">
-        <v>561.551</v>
+        <v>1132.5399</v>
       </c>
       <c r="G24" t="n">
-        <v>21563559.7</v>
+        <v>10781779.8</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1234,13 +1234,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>79400</v>
+        <v>38400</v>
       </c>
       <c r="F25" t="n">
-        <v>135.7907</v>
+        <v>561.551</v>
       </c>
       <c r="G25" t="n">
-        <v>10781779.8</v>
+        <v>21563559.7</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>31050</v>
+        <v>79400</v>
       </c>
       <c r="F26" t="n">
-        <v>347.2393</v>
+        <v>135.7907</v>
       </c>
       <c r="G26" t="n">
         <v>10781779.8</v>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>38500</v>
+        <v>31050</v>
       </c>
       <c r="F27" t="n">
-        <v>280.0462</v>
+        <v>347.2393</v>
       </c>
       <c r="G27" t="n">
         <v>10781779.8</v>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1330,30 +1330,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>50100</v>
+        <v>38500</v>
       </c>
       <c r="F28" t="n">
-        <v>645.6156</v>
+        <v>280.0462</v>
       </c>
       <c r="G28" t="n">
-        <v>32345339.5</v>
+        <v>10781779.8</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>9990</v>
+        <v>50100</v>
       </c>
       <c r="F29" t="n">
-        <v>3271.9446</v>
+        <v>645.6156</v>
       </c>
       <c r="G29" t="n">
-        <v>32686726.8</v>
+        <v>32345339.5</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1380,31 +1380,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>32000</v>
+        <v>9990</v>
       </c>
       <c r="F30" t="n">
-        <v>2127.2811</v>
+        <v>3271.9446</v>
       </c>
       <c r="G30" t="n">
-        <v>68072995.90000001</v>
-      </c>
-      <c r="H30" t="n">
-        <v>8.06</v>
-      </c>
+        <v>32686726.8</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1414,29 +1412,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>19830</v>
+        <v>32000</v>
       </c>
       <c r="F31" t="n">
-        <v>2747.2455</v>
+        <v>2127.2811</v>
       </c>
       <c r="G31" t="n">
-        <v>54477878.1</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>68072995.90000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>37100</v>
+        <v>19830</v>
       </c>
       <c r="F32" t="n">
-        <v>293.6813</v>
+        <v>2747.2455</v>
       </c>
       <c r="G32" t="n">
-        <v>10895575.6</v>
+        <v>54477878.1</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>80200</v>
+        <v>37100</v>
       </c>
       <c r="F33" t="n">
-        <v>407.5652</v>
+        <v>293.6813</v>
       </c>
       <c r="G33" t="n">
-        <v>32686726.8</v>
+        <v>10895575.6</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1524,13 +1524,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>31600</v>
+        <v>80200</v>
       </c>
       <c r="F34" t="n">
-        <v>344.7967</v>
+        <v>407.5652</v>
       </c>
       <c r="G34" t="n">
-        <v>10895575.6</v>
+        <v>32686726.8</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1556,30 +1556,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>38200</v>
+        <v>31600</v>
       </c>
       <c r="F35" t="n">
-        <v>855.6735</v>
+        <v>344.7967</v>
       </c>
       <c r="G35" t="n">
-        <v>32686726.8</v>
+        <v>10895575.6</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1588,30 +1588,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>87800</v>
+        <v>38200</v>
       </c>
       <c r="F36" t="n">
-        <v>384.5603</v>
+        <v>855.6735</v>
       </c>
       <c r="G36" t="n">
-        <v>33764396.5</v>
+        <v>32686726.8</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1620,52 +1620,52 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>52400</v>
+        <v>87800</v>
       </c>
       <c r="F37" t="n">
-        <v>636.0417</v>
+        <v>384.5603</v>
       </c>
       <c r="G37" t="n">
-        <v>33328583.4</v>
+        <v>33764396.5</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>10250</v>
+        <v>52400</v>
       </c>
       <c r="F38" t="n">
-        <v>3328.756</v>
+        <v>636.0417</v>
       </c>
       <c r="G38" t="n">
-        <v>34119749</v>
+        <v>33328583.4</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1684,13 +1684,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>10090</v>
+        <v>10250</v>
       </c>
       <c r="F39" t="n">
-        <v>3333.5276</v>
+        <v>3328.756</v>
       </c>
       <c r="G39" t="n">
-        <v>33635293.3</v>
+        <v>34119749</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>53200</v>
+        <v>10090</v>
       </c>
       <c r="F40" t="n">
-        <v>632.2424</v>
+        <v>3333.5276</v>
       </c>
       <c r="G40" t="n">
         <v>33635293.3</v>
@@ -1729,32 +1729,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>35050</v>
+        <v>53200</v>
       </c>
       <c r="F41" t="n">
-        <v>941.2811</v>
+        <v>632.2424</v>
       </c>
       <c r="G41" t="n">
-        <v>32991903.3</v>
+        <v>33635293.3</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1766,31 +1766,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>29100</v>
+        <v>35050</v>
       </c>
       <c r="F42" t="n">
-        <v>1976.0221</v>
+        <v>941.2811</v>
       </c>
       <c r="G42" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>32991903.3</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1800,29 +1798,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>43700</v>
+        <v>29100</v>
       </c>
       <c r="F43" t="n">
-        <v>1509.9269</v>
+        <v>1976.0221</v>
       </c>
       <c r="G43" t="n">
-        <v>65983806.6</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1832,24 +1832,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>49500</v>
+        <v>43700</v>
       </c>
       <c r="F44" t="n">
-        <v>1333.0062</v>
+        <v>1509.9269</v>
       </c>
       <c r="G44" t="n">
         <v>65983806.6</v>
@@ -1859,17 +1859,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1878,30 +1878,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>86300</v>
+        <v>49500</v>
       </c>
       <c r="F45" t="n">
-        <v>366.4646</v>
+        <v>1333.0062</v>
       </c>
       <c r="G45" t="n">
-        <v>31625898.5</v>
+        <v>65983806.6</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>8490</v>
+        <v>86300</v>
       </c>
       <c r="F46" t="n">
-        <v>3672.3539</v>
+        <v>366.4646</v>
       </c>
       <c r="G46" t="n">
-        <v>31178284.6</v>
+        <v>31625898.5</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1928,12 +1928,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>45500</v>
+        <v>8490</v>
       </c>
       <c r="F47" t="n">
-        <v>685.237</v>
+        <v>3672.3539</v>
       </c>
       <c r="G47" t="n">
         <v>31178284.6</v>
@@ -1955,17 +1955,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>7520</v>
+        <v>45500</v>
       </c>
       <c r="F48" t="n">
-        <v>4087.0231</v>
+        <v>685.237</v>
       </c>
       <c r="G48" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1992,12 +1992,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>83000</v>
+        <v>7520</v>
       </c>
       <c r="F49" t="n">
-        <v>370.2941</v>
+        <v>4087.0231</v>
       </c>
       <c r="G49" t="n">
         <v>30734413.9</v>
@@ -2024,24 +2024,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>47750</v>
+        <v>83000</v>
       </c>
       <c r="F50" t="n">
-        <v>643.6526</v>
+        <v>370.2941</v>
       </c>
       <c r="G50" t="n">
         <v>30734413.9</v>
@@ -2051,17 +2051,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2070,13 +2070,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>8080</v>
+        <v>47750</v>
       </c>
       <c r="F51" t="n">
-        <v>3746.0511</v>
+        <v>643.6526</v>
       </c>
       <c r="G51" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2088,24 +2088,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>21950</v>
+        <v>8080</v>
       </c>
       <c r="F52" t="n">
-        <v>1378.9564</v>
+        <v>3746.0511</v>
       </c>
       <c r="G52" t="n">
         <v>30268092.9</v>
@@ -2115,32 +2115,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>22750</v>
+        <v>21950</v>
       </c>
       <c r="F53" t="n">
-        <v>2200.9656</v>
+        <v>1378.9564</v>
       </c>
       <c r="G53" t="n">
-        <v>50071968.5</v>
+        <v>30268092.9</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2152,31 +2152,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>33150</v>
+        <v>22750</v>
       </c>
       <c r="F54" t="n">
-        <v>921.4443</v>
+        <v>2200.9656</v>
       </c>
       <c r="G54" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H54" t="n">
-        <v>2</v>
-      </c>
+        <v>50071968.5</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2186,12 +2184,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2200,49 +2198,51 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>38050</v>
+        <v>33150</v>
       </c>
       <c r="F55" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G55" t="n">
-        <v>30065462.5</v>
+        <v>30545877.8</v>
       </c>
       <c r="H55" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>28850</v>
+        <v>38050</v>
       </c>
       <c r="F56" t="n">
-        <v>1038.0221</v>
+        <v>790.1567</v>
       </c>
       <c r="G56" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2252,24 +2252,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>76400</v>
+        <v>28850</v>
       </c>
       <c r="F57" t="n">
-        <v>391.9756</v>
+        <v>1038.0221</v>
       </c>
       <c r="G57" t="n">
         <v>29946939</v>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>21650</v>
+        <v>76400</v>
       </c>
       <c r="F58" t="n">
-        <v>1383.2304</v>
+        <v>391.9756</v>
       </c>
       <c r="G58" t="n">
         <v>29946939</v>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>32500</v>
+        <v>21650</v>
       </c>
       <c r="F59" t="n">
-        <v>921.4443</v>
+        <v>1383.2304</v>
       </c>
       <c r="G59" t="n">
         <v>29946939</v>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>37900</v>
+        <v>32500</v>
       </c>
       <c r="F60" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G60" t="n">
         <v>29946939</v>
@@ -2375,17 +2375,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2394,13 +2394,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>25300</v>
+        <v>37900</v>
       </c>
       <c r="F61" t="n">
-        <v>1186</v>
+        <v>790.1567</v>
       </c>
       <c r="G61" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2412,29 +2412,61 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G62" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E62" t="n">
+      <c r="E63" t="n">
         <v>32000</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F63" t="n">
         <v>938</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G63" t="n">
         <v>30016000</v>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,49 +492,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>36050</v>
+        <v>108700</v>
       </c>
       <c r="F2" t="n">
-        <v>869.3262999999999</v>
+        <v>285.6073</v>
       </c>
       <c r="G2" t="n">
-        <v>31339214.2</v>
+        <v>31045517.4</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7490</v>
+        <v>36050</v>
       </c>
       <c r="F3" t="n">
-        <v>10243.469</v>
+        <v>869.3262999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>76723582.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-15.37</v>
-      </c>
+        <v>31339214.2</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,29 +542,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30500</v>
+        <v>7490</v>
       </c>
       <c r="F4" t="n">
-        <v>963.2346</v>
+        <v>10243.469</v>
       </c>
       <c r="G4" t="n">
-        <v>29378655.8</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>76723582.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-15.37</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -576,24 +576,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>88400</v>
+        <v>30500</v>
       </c>
       <c r="F5" t="n">
-        <v>332.3377</v>
+        <v>963.2346</v>
       </c>
       <c r="G5" t="n">
         <v>29378655.8</v>
@@ -603,17 +603,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9100</v>
+        <v>88400</v>
       </c>
       <c r="F6" t="n">
-        <v>2259.594</v>
+        <v>332.3377</v>
       </c>
       <c r="G6" t="n">
-        <v>20562305.7</v>
+        <v>29378655.8</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -640,12 +640,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>39150</v>
+        <v>9100</v>
       </c>
       <c r="F7" t="n">
-        <v>525.2184999999999</v>
+        <v>2259.594</v>
       </c>
       <c r="G7" t="n">
         <v>20562305.7</v>
@@ -672,12 +672,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>79900</v>
+        <v>39150</v>
       </c>
       <c r="F8" t="n">
-        <v>257.3505</v>
+        <v>525.2184999999999</v>
       </c>
       <c r="G8" t="n">
         <v>20562305.7</v>
@@ -704,12 +704,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>45500</v>
+        <v>79900</v>
       </c>
       <c r="F9" t="n">
-        <v>451.9188</v>
+        <v>257.3505</v>
       </c>
       <c r="G9" t="n">
         <v>20562305.7</v>
@@ -736,44 +736,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>39050</v>
+        <v>45500</v>
       </c>
       <c r="F10" t="n">
-        <v>789.8453</v>
+        <v>451.9188</v>
       </c>
       <c r="G10" t="n">
-        <v>30843458.5</v>
+        <v>20562305.7</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8720</v>
+        <v>39050</v>
       </c>
       <c r="F11" t="n">
-        <v>3255.4339</v>
+        <v>789.8453</v>
       </c>
       <c r="G11" t="n">
-        <v>28387383.9</v>
+        <v>30843458.5</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -800,31 +800,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>16930</v>
+        <v>8720</v>
       </c>
       <c r="F12" t="n">
-        <v>4324.5003</v>
+        <v>3255.4339</v>
       </c>
       <c r="G12" t="n">
-        <v>73213790.59999999</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-15.51</v>
-      </c>
+        <v>28387383.9</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -834,29 +832,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>33050</v>
+        <v>16930</v>
       </c>
       <c r="F13" t="n">
-        <v>858.9224</v>
+        <v>4324.5003</v>
       </c>
       <c r="G13" t="n">
-        <v>28387383.9</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>73213790.59999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-15.51</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>73500</v>
+        <v>33050</v>
       </c>
       <c r="F14" t="n">
-        <v>386.2229</v>
+        <v>858.9224</v>
       </c>
       <c r="G14" t="n">
         <v>28387383.9</v>
@@ -898,12 +898,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>28400</v>
+        <v>73500</v>
       </c>
       <c r="F15" t="n">
-        <v>999.5558</v>
+        <v>386.2229</v>
       </c>
       <c r="G15" t="n">
         <v>28387383.9</v>
@@ -930,31 +930,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>30500</v>
+        <v>28400</v>
       </c>
       <c r="F16" t="n">
-        <v>3519.9944</v>
+        <v>999.5558</v>
       </c>
       <c r="G16" t="n">
-        <v>107359829.8</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-24.2</v>
-      </c>
+        <v>28387383.9</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -964,29 +962,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>38850</v>
+        <v>30500</v>
       </c>
       <c r="F17" t="n">
-        <v>730.692</v>
+        <v>3519.9944</v>
       </c>
       <c r="G17" t="n">
-        <v>28387383.9</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>107359829.8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-24.2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -996,59 +996,59 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>37600</v>
+        <v>38850</v>
       </c>
       <c r="F18" t="n">
-        <v>2516.612</v>
+        <v>730.692</v>
       </c>
       <c r="G18" t="n">
-        <v>94624613</v>
+        <v>28387383.9</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>20400</v>
+        <v>37600</v>
       </c>
       <c r="F19" t="n">
-        <v>1577.2548</v>
+        <v>2516.612</v>
       </c>
       <c r="G19" t="n">
-        <v>32175998.7</v>
+        <v>94624613</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1074,13 +1074,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>37600</v>
+        <v>20400</v>
       </c>
       <c r="F20" t="n">
-        <v>285.2482</v>
+        <v>1577.2548</v>
       </c>
       <c r="G20" t="n">
-        <v>10725332.9</v>
+        <v>32175998.7</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>30100</v>
+        <v>37600</v>
       </c>
       <c r="F21" t="n">
-        <v>356.3234</v>
+        <v>285.2482</v>
       </c>
       <c r="G21" t="n">
         <v>10725332.9</v>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>36800</v>
+        <v>30100</v>
       </c>
       <c r="F22" t="n">
-        <v>874.3478</v>
+        <v>356.3234</v>
       </c>
       <c r="G22" t="n">
-        <v>32175998.7</v>
+        <v>10725332.9</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>46400</v>
+        <v>36800</v>
       </c>
       <c r="F23" t="n">
-        <v>693.4482</v>
+        <v>874.3478</v>
       </c>
       <c r="G23" t="n">
         <v>32175998.7</v>
@@ -1183,17 +1183,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9520</v>
+        <v>46400</v>
       </c>
       <c r="F24" t="n">
-        <v>1132.5399</v>
+        <v>693.4482</v>
       </c>
       <c r="G24" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1234,13 +1234,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>38400</v>
+        <v>9520</v>
       </c>
       <c r="F25" t="n">
-        <v>561.551</v>
+        <v>1132.5399</v>
       </c>
       <c r="G25" t="n">
-        <v>21563559.7</v>
+        <v>10781779.8</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>79400</v>
+        <v>38400</v>
       </c>
       <c r="F26" t="n">
-        <v>135.7907</v>
+        <v>561.551</v>
       </c>
       <c r="G26" t="n">
-        <v>10781779.8</v>
+        <v>21563559.7</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>31050</v>
+        <v>79400</v>
       </c>
       <c r="F27" t="n">
-        <v>347.2393</v>
+        <v>135.7907</v>
       </c>
       <c r="G27" t="n">
         <v>10781779.8</v>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>38500</v>
+        <v>31050</v>
       </c>
       <c r="F28" t="n">
-        <v>280.0462</v>
+        <v>347.2393</v>
       </c>
       <c r="G28" t="n">
         <v>10781779.8</v>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1362,30 +1362,30 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>50100</v>
+        <v>38500</v>
       </c>
       <c r="F29" t="n">
-        <v>645.6156</v>
+        <v>280.0462</v>
       </c>
       <c r="G29" t="n">
-        <v>32345339.5</v>
+        <v>10781779.8</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9990</v>
+        <v>50100</v>
       </c>
       <c r="F30" t="n">
-        <v>3271.9446</v>
+        <v>645.6156</v>
       </c>
       <c r="G30" t="n">
-        <v>32686726.8</v>
+        <v>32345339.5</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1412,31 +1412,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>32000</v>
+        <v>9990</v>
       </c>
       <c r="F31" t="n">
-        <v>2127.2811</v>
+        <v>3271.9446</v>
       </c>
       <c r="G31" t="n">
-        <v>68072995.90000001</v>
-      </c>
-      <c r="H31" t="n">
-        <v>8.06</v>
-      </c>
+        <v>32686726.8</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1446,29 +1444,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>19830</v>
+        <v>32000</v>
       </c>
       <c r="F32" t="n">
-        <v>2747.2455</v>
+        <v>2127.2811</v>
       </c>
       <c r="G32" t="n">
-        <v>54477878.1</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
+        <v>68072995.90000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1478,27 +1478,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>37100</v>
+        <v>19830</v>
       </c>
       <c r="F33" t="n">
-        <v>293.6813</v>
+        <v>2747.2455</v>
       </c>
       <c r="G33" t="n">
-        <v>10895575.6</v>
+        <v>54477878.1</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1510,12 +1510,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1524,13 +1524,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>80200</v>
+        <v>37100</v>
       </c>
       <c r="F34" t="n">
-        <v>407.5652</v>
+        <v>293.6813</v>
       </c>
       <c r="G34" t="n">
-        <v>32686726.8</v>
+        <v>10895575.6</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1556,13 +1556,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>31600</v>
+        <v>80200</v>
       </c>
       <c r="F35" t="n">
-        <v>344.7967</v>
+        <v>407.5652</v>
       </c>
       <c r="G35" t="n">
-        <v>10895575.6</v>
+        <v>32686726.8</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1588,30 +1588,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>38200</v>
+        <v>31600</v>
       </c>
       <c r="F36" t="n">
-        <v>855.6735</v>
+        <v>344.7967</v>
       </c>
       <c r="G36" t="n">
-        <v>32686726.8</v>
+        <v>10895575.6</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1620,30 +1620,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>87800</v>
+        <v>38200</v>
       </c>
       <c r="F37" t="n">
-        <v>384.5603</v>
+        <v>855.6735</v>
       </c>
       <c r="G37" t="n">
-        <v>33764396.5</v>
+        <v>32686726.8</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1652,52 +1652,52 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>52400</v>
+        <v>87800</v>
       </c>
       <c r="F38" t="n">
-        <v>636.0417</v>
+        <v>384.5603</v>
       </c>
       <c r="G38" t="n">
-        <v>33328583.4</v>
+        <v>33764396.5</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>10250</v>
+        <v>52400</v>
       </c>
       <c r="F39" t="n">
-        <v>3328.756</v>
+        <v>636.0417</v>
       </c>
       <c r="G39" t="n">
-        <v>34119749</v>
+        <v>33328583.4</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1716,13 +1716,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10090</v>
+        <v>10250</v>
       </c>
       <c r="F40" t="n">
-        <v>3333.5276</v>
+        <v>3328.756</v>
       </c>
       <c r="G40" t="n">
-        <v>33635293.3</v>
+        <v>34119749</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53200</v>
+        <v>10090</v>
       </c>
       <c r="F41" t="n">
-        <v>632.2424</v>
+        <v>3333.5276</v>
       </c>
       <c r="G41" t="n">
         <v>33635293.3</v>
@@ -1761,32 +1761,32 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>35050</v>
+        <v>53200</v>
       </c>
       <c r="F42" t="n">
-        <v>941.2811</v>
+        <v>632.2424</v>
       </c>
       <c r="G42" t="n">
-        <v>32991903.3</v>
+        <v>33635293.3</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1798,31 +1798,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>29100</v>
+        <v>35050</v>
       </c>
       <c r="F43" t="n">
-        <v>1976.0221</v>
+        <v>941.2811</v>
       </c>
       <c r="G43" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>32991903.3</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1832,29 +1830,31 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>43700</v>
+        <v>29100</v>
       </c>
       <c r="F44" t="n">
-        <v>1509.9269</v>
+        <v>1976.0221</v>
       </c>
       <c r="G44" t="n">
-        <v>65983806.6</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>49500</v>
+        <v>43700</v>
       </c>
       <c r="F45" t="n">
-        <v>1333.0062</v>
+        <v>1509.9269</v>
       </c>
       <c r="G45" t="n">
         <v>65983806.6</v>
@@ -1891,17 +1891,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1910,30 +1910,30 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>86300</v>
+        <v>49500</v>
       </c>
       <c r="F46" t="n">
-        <v>366.4646</v>
+        <v>1333.0062</v>
       </c>
       <c r="G46" t="n">
-        <v>31625898.5</v>
+        <v>65983806.6</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>8490</v>
+        <v>86300</v>
       </c>
       <c r="F47" t="n">
-        <v>3672.3539</v>
+        <v>366.4646</v>
       </c>
       <c r="G47" t="n">
-        <v>31178284.6</v>
+        <v>31625898.5</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>45500</v>
+        <v>8490</v>
       </c>
       <c r="F48" t="n">
-        <v>685.237</v>
+        <v>3672.3539</v>
       </c>
       <c r="G48" t="n">
         <v>31178284.6</v>
@@ -1987,17 +1987,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2006,13 +2006,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>7520</v>
+        <v>45500</v>
       </c>
       <c r="F49" t="n">
-        <v>4087.0231</v>
+        <v>685.237</v>
       </c>
       <c r="G49" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>83000</v>
+        <v>7520</v>
       </c>
       <c r="F50" t="n">
-        <v>370.2941</v>
+        <v>4087.0231</v>
       </c>
       <c r="G50" t="n">
         <v>30734413.9</v>
@@ -2056,24 +2056,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>47750</v>
+        <v>83000</v>
       </c>
       <c r="F51" t="n">
-        <v>643.6526</v>
+        <v>370.2941</v>
       </c>
       <c r="G51" t="n">
         <v>30734413.9</v>
@@ -2083,17 +2083,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>8080</v>
+        <v>47750</v>
       </c>
       <c r="F52" t="n">
-        <v>3746.0511</v>
+        <v>643.6526</v>
       </c>
       <c r="G52" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2120,24 +2120,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>21950</v>
+        <v>8080</v>
       </c>
       <c r="F53" t="n">
-        <v>1378.9564</v>
+        <v>3746.0511</v>
       </c>
       <c r="G53" t="n">
         <v>30268092.9</v>
@@ -2147,32 +2147,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>22750</v>
+        <v>21950</v>
       </c>
       <c r="F54" t="n">
-        <v>2200.9656</v>
+        <v>1378.9564</v>
       </c>
       <c r="G54" t="n">
-        <v>50071968.5</v>
+        <v>30268092.9</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2184,31 +2184,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>33150</v>
+        <v>22750</v>
       </c>
       <c r="F55" t="n">
-        <v>921.4443</v>
+        <v>2200.9656</v>
       </c>
       <c r="G55" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H55" t="n">
-        <v>2</v>
-      </c>
+        <v>50071968.5</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2218,12 +2216,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2232,49 +2230,51 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>38050</v>
+        <v>33150</v>
       </c>
       <c r="F56" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G56" t="n">
-        <v>30065462.5</v>
+        <v>30545877.8</v>
       </c>
       <c r="H56" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>28850</v>
+        <v>38050</v>
       </c>
       <c r="F57" t="n">
-        <v>1038.0221</v>
+        <v>790.1567</v>
       </c>
       <c r="G57" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2284,24 +2284,24 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>76400</v>
+        <v>28850</v>
       </c>
       <c r="F58" t="n">
-        <v>391.9756</v>
+        <v>1038.0221</v>
       </c>
       <c r="G58" t="n">
         <v>29946939</v>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>21650</v>
+        <v>76400</v>
       </c>
       <c r="F59" t="n">
-        <v>1383.2304</v>
+        <v>391.9756</v>
       </c>
       <c r="G59" t="n">
         <v>29946939</v>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>32500</v>
+        <v>21650</v>
       </c>
       <c r="F60" t="n">
-        <v>921.4443</v>
+        <v>1383.2304</v>
       </c>
       <c r="G60" t="n">
         <v>29946939</v>
@@ -2380,12 +2380,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>37900</v>
+        <v>32500</v>
       </c>
       <c r="F61" t="n">
-        <v>790.1567</v>
+        <v>921.4443</v>
       </c>
       <c r="G61" t="n">
         <v>29946939</v>
@@ -2407,17 +2407,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2426,13 +2426,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>25300</v>
+        <v>37900</v>
       </c>
       <c r="F62" t="n">
-        <v>1186</v>
+        <v>790.1567</v>
       </c>
       <c r="G62" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2444,29 +2444,61 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G63" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E63" t="n">
+      <c r="E64" t="n">
         <v>32000</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F64" t="n">
         <v>938</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G64" t="n">
         <v>30016000</v>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,30 +492,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>108700</v>
+        <v>117500</v>
       </c>
       <c r="F2" t="n">
-        <v>285.6073</v>
+        <v>267.9088</v>
       </c>
       <c r="G2" t="n">
-        <v>31045517.4</v>
+        <v>31479278.3</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,96 +524,94 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>36050</v>
+        <v>32050</v>
       </c>
       <c r="F3" t="n">
-        <v>869.3262999999999</v>
+        <v>982.1928</v>
       </c>
       <c r="G3" t="n">
-        <v>31339214.2</v>
+        <v>31479278.3</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>사피엔반도체</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>452430</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7490</v>
+        <v>25750</v>
       </c>
       <c r="F4" t="n">
-        <v>10243.469</v>
+        <v>1222.4962</v>
       </c>
       <c r="G4" t="n">
-        <v>76723582.5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-15.37</v>
-      </c>
+        <v>31479278.3</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>30500</v>
+        <v>108700</v>
       </c>
       <c r="F5" t="n">
-        <v>963.2346</v>
+        <v>285.6073</v>
       </c>
       <c r="G5" t="n">
-        <v>29378655.8</v>
+        <v>31045517.4</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -622,20 +620,20 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>88400</v>
+        <v>36050</v>
       </c>
       <c r="F6" t="n">
-        <v>332.3377</v>
+        <v>869.3262999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>29378655.8</v>
+        <v>31339214.2</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -650,24 +648,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9100</v>
+        <v>7490</v>
       </c>
       <c r="F7" t="n">
-        <v>2259.594</v>
+        <v>10243.469</v>
       </c>
       <c r="G7" t="n">
-        <v>20562305.7</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>76723582.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-15.37</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -682,24 +682,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>39150</v>
+        <v>30500</v>
       </c>
       <c r="F8" t="n">
-        <v>525.2184999999999</v>
+        <v>963.2346</v>
       </c>
       <c r="G8" t="n">
-        <v>20562305.7</v>
+        <v>29378655.8</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>79900</v>
+        <v>88400</v>
       </c>
       <c r="F9" t="n">
-        <v>257.3505</v>
+        <v>332.3377</v>
       </c>
       <c r="G9" t="n">
-        <v>20562305.7</v>
+        <v>29378655.8</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>45500</v>
+        <v>9100</v>
       </c>
       <c r="F10" t="n">
-        <v>451.9188</v>
+        <v>2259.594</v>
       </c>
       <c r="G10" t="n">
         <v>20562305.7</v>
@@ -768,110 +768,108 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>39050</v>
+        <v>39150</v>
       </c>
       <c r="F11" t="n">
-        <v>789.8453</v>
+        <v>525.2184999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>30843458.5</v>
+        <v>20562305.7</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8720</v>
+        <v>79900</v>
       </c>
       <c r="F12" t="n">
-        <v>3255.4339</v>
+        <v>257.3505</v>
       </c>
       <c r="G12" t="n">
-        <v>28387383.9</v>
+        <v>20562305.7</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>16930</v>
+        <v>45500</v>
       </c>
       <c r="F13" t="n">
-        <v>4324.5003</v>
+        <v>451.9188</v>
       </c>
       <c r="G13" t="n">
-        <v>73213790.59999999</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-15.51</v>
-      </c>
+        <v>20562305.7</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,13 +878,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>33050</v>
+        <v>39050</v>
       </c>
       <c r="F14" t="n">
-        <v>858.9224</v>
+        <v>789.8453</v>
       </c>
       <c r="G14" t="n">
-        <v>28387383.9</v>
+        <v>30843458.5</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -898,12 +896,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -912,10 +910,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>73500</v>
+        <v>8720</v>
       </c>
       <c r="F15" t="n">
-        <v>386.2229</v>
+        <v>3255.4339</v>
       </c>
       <c r="G15" t="n">
         <v>28387383.9</v>
@@ -930,29 +928,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>28400</v>
+        <v>16930</v>
       </c>
       <c r="F16" t="n">
-        <v>999.5558</v>
+        <v>4324.5003</v>
       </c>
       <c r="G16" t="n">
-        <v>28387383.9</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>73213790.59999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-15.51</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -962,31 +962,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>30500</v>
+        <v>33050</v>
       </c>
       <c r="F17" t="n">
-        <v>3519.9944</v>
+        <v>858.9224</v>
       </c>
       <c r="G17" t="n">
-        <v>107359829.8</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-24.2</v>
-      </c>
+        <v>28387383.9</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -996,12 +994,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1010,10 +1008,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>38850</v>
+        <v>73500</v>
       </c>
       <c r="F18" t="n">
-        <v>730.692</v>
+        <v>386.2229</v>
       </c>
       <c r="G18" t="n">
         <v>28387383.9</v>
@@ -1028,76 +1026,78 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>37600</v>
+        <v>28400</v>
       </c>
       <c r="F19" t="n">
-        <v>2516.612</v>
+        <v>999.5558</v>
       </c>
       <c r="G19" t="n">
-        <v>94624613</v>
+        <v>28387383.9</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>20400</v>
+        <v>30500</v>
       </c>
       <c r="F20" t="n">
-        <v>1577.2548</v>
+        <v>3519.9944</v>
       </c>
       <c r="G20" t="n">
-        <v>32175998.7</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>107359829.8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-24.2</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1106,45 +1106,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>37600</v>
+        <v>38850</v>
       </c>
       <c r="F21" t="n">
-        <v>285.2482</v>
+        <v>730.692</v>
       </c>
       <c r="G21" t="n">
-        <v>10725332.9</v>
+        <v>28387383.9</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>30100</v>
+        <v>37600</v>
       </c>
       <c r="F22" t="n">
-        <v>356.3234</v>
+        <v>2516.612</v>
       </c>
       <c r="G22" t="n">
-        <v>10725332.9</v>
+        <v>94624613</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>36800</v>
+        <v>20400</v>
       </c>
       <c r="F23" t="n">
-        <v>874.3478</v>
+        <v>1577.2548</v>
       </c>
       <c r="G23" t="n">
         <v>32175998.7</v>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1202,30 +1202,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>46400</v>
+        <v>37600</v>
       </c>
       <c r="F24" t="n">
-        <v>693.4482</v>
+        <v>285.2482</v>
       </c>
       <c r="G24" t="n">
-        <v>32175998.7</v>
+        <v>10725332.9</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1234,30 +1234,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>9520</v>
+        <v>30100</v>
       </c>
       <c r="F25" t="n">
-        <v>1132.5399</v>
+        <v>356.3234</v>
       </c>
       <c r="G25" t="n">
-        <v>10781779.8</v>
+        <v>10725332.9</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1266,30 +1266,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>38400</v>
+        <v>36800</v>
       </c>
       <c r="F26" t="n">
-        <v>561.551</v>
+        <v>874.3478</v>
       </c>
       <c r="G26" t="n">
-        <v>21563559.7</v>
+        <v>32175998.7</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>79400</v>
+        <v>46400</v>
       </c>
       <c r="F27" t="n">
-        <v>135.7907</v>
+        <v>693.4482</v>
       </c>
       <c r="G27" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>31050</v>
+        <v>9520</v>
       </c>
       <c r="F28" t="n">
-        <v>347.2393</v>
+        <v>1132.5399</v>
       </c>
       <c r="G28" t="n">
         <v>10781779.8</v>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>38500</v>
+        <v>38400</v>
       </c>
       <c r="F29" t="n">
-        <v>280.0462</v>
+        <v>561.551</v>
       </c>
       <c r="G29" t="n">
-        <v>10781779.8</v>
+        <v>21563559.7</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1394,30 +1394,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>50100</v>
+        <v>79400</v>
       </c>
       <c r="F30" t="n">
-        <v>645.6156</v>
+        <v>135.7907</v>
       </c>
       <c r="G30" t="n">
-        <v>32345339.5</v>
+        <v>10781779.8</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1426,79 +1426,77 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>9990</v>
+        <v>31050</v>
       </c>
       <c r="F31" t="n">
-        <v>3271.9446</v>
+        <v>347.2393</v>
       </c>
       <c r="G31" t="n">
-        <v>32686726.8</v>
+        <v>10781779.8</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>32000</v>
+        <v>38500</v>
       </c>
       <c r="F32" t="n">
-        <v>2127.2811</v>
+        <v>280.0462</v>
       </c>
       <c r="G32" t="n">
-        <v>68072995.90000001</v>
-      </c>
-      <c r="H32" t="n">
-        <v>8.06</v>
-      </c>
+        <v>10781779.8</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>19830</v>
+        <v>50100</v>
       </c>
       <c r="F33" t="n">
-        <v>2747.2455</v>
+        <v>645.6156</v>
       </c>
       <c r="G33" t="n">
-        <v>54477878.1</v>
+        <v>32345339.5</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1510,12 +1508,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1524,13 +1522,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>37100</v>
+        <v>9990</v>
       </c>
       <c r="F34" t="n">
-        <v>293.6813</v>
+        <v>3271.9446</v>
       </c>
       <c r="G34" t="n">
-        <v>10895575.6</v>
+        <v>32686726.8</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1542,29 +1540,31 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>80200</v>
+        <v>32000</v>
       </c>
       <c r="F35" t="n">
-        <v>407.5652</v>
+        <v>2127.2811</v>
       </c>
       <c r="G35" t="n">
-        <v>32686726.8</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>68072995.90000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1574,27 +1574,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>31600</v>
+        <v>19830</v>
       </c>
       <c r="F36" t="n">
-        <v>344.7967</v>
+        <v>2747.2455</v>
       </c>
       <c r="G36" t="n">
-        <v>10895575.6</v>
+        <v>54477878.1</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1606,12 +1606,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1620,20 +1620,20 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>38200</v>
+        <v>37100</v>
       </c>
       <c r="F37" t="n">
-        <v>855.6735</v>
+        <v>293.6813</v>
       </c>
       <c r="G37" t="n">
-        <v>32686726.8</v>
+        <v>10895575.6</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1652,30 +1652,30 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>87800</v>
+        <v>80200</v>
       </c>
       <c r="F38" t="n">
-        <v>384.5603</v>
+        <v>407.5652</v>
       </c>
       <c r="G38" t="n">
-        <v>33764396.5</v>
+        <v>32686726.8</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1684,84 +1684,84 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>52400</v>
+        <v>31600</v>
       </c>
       <c r="F39" t="n">
-        <v>636.0417</v>
+        <v>344.7967</v>
       </c>
       <c r="G39" t="n">
-        <v>33328583.4</v>
+        <v>10895575.6</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>10250</v>
+        <v>38200</v>
       </c>
       <c r="F40" t="n">
-        <v>3328.756</v>
+        <v>855.6735</v>
       </c>
       <c r="G40" t="n">
-        <v>34119749</v>
+        <v>32686726.8</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>10090</v>
+        <v>87800</v>
       </c>
       <c r="F41" t="n">
-        <v>3333.5276</v>
+        <v>384.5603</v>
       </c>
       <c r="G41" t="n">
-        <v>33635293.3</v>
+        <v>33764396.5</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1776,115 +1776,113 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53200</v>
+        <v>52400</v>
       </c>
       <c r="F42" t="n">
-        <v>632.2424</v>
+        <v>636.0417</v>
       </c>
       <c r="G42" t="n">
-        <v>33635293.3</v>
+        <v>33328583.4</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>35050</v>
+        <v>10250</v>
       </c>
       <c r="F43" t="n">
-        <v>941.2811</v>
+        <v>3328.756</v>
       </c>
       <c r="G43" t="n">
-        <v>32991903.3</v>
+        <v>34119749</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>29100</v>
+        <v>10090</v>
       </c>
       <c r="F44" t="n">
-        <v>1976.0221</v>
+        <v>3333.5276</v>
       </c>
       <c r="G44" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>33635293.3</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>43700</v>
+        <v>53200</v>
       </c>
       <c r="F45" t="n">
-        <v>1509.9269</v>
+        <v>632.2424</v>
       </c>
       <c r="G45" t="n">
-        <v>65983806.6</v>
+        <v>33635293.3</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1896,12 +1894,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1910,84 +1908,86 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>49500</v>
+        <v>35050</v>
       </c>
       <c r="F46" t="n">
-        <v>1333.0062</v>
+        <v>941.2811</v>
       </c>
       <c r="G46" t="n">
-        <v>65983806.6</v>
+        <v>32991903.3</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>86300</v>
+        <v>29100</v>
       </c>
       <c r="F47" t="n">
-        <v>366.4646</v>
+        <v>1976.0221</v>
       </c>
       <c r="G47" t="n">
-        <v>31625898.5</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>8490</v>
+        <v>43700</v>
       </c>
       <c r="F48" t="n">
-        <v>3672.3539</v>
+        <v>1509.9269</v>
       </c>
       <c r="G48" t="n">
-        <v>31178284.6</v>
+        <v>65983806.6</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2006,30 +2006,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>45500</v>
+        <v>49500</v>
       </c>
       <c r="F49" t="n">
-        <v>685.237</v>
+        <v>1333.0062</v>
       </c>
       <c r="G49" t="n">
-        <v>31178284.6</v>
+        <v>65983806.6</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2038,30 +2038,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>7520</v>
+        <v>86300</v>
       </c>
       <c r="F50" t="n">
-        <v>4087.0231</v>
+        <v>366.4646</v>
       </c>
       <c r="G50" t="n">
-        <v>30734413.9</v>
+        <v>31625898.5</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2070,20 +2070,20 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>83000</v>
+        <v>8490</v>
       </c>
       <c r="F51" t="n">
-        <v>370.2941</v>
+        <v>3672.3539</v>
       </c>
       <c r="G51" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2098,24 +2098,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>47750</v>
+        <v>45500</v>
       </c>
       <c r="F52" t="n">
-        <v>643.6526</v>
+        <v>685.237</v>
       </c>
       <c r="G52" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2130,34 +2130,34 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>8080</v>
+        <v>7520</v>
       </c>
       <c r="F53" t="n">
-        <v>3746.0511</v>
+        <v>4087.0231</v>
       </c>
       <c r="G53" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2166,30 +2166,30 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>21950</v>
+        <v>83000</v>
       </c>
       <c r="F54" t="n">
-        <v>1378.9564</v>
+        <v>370.2941</v>
       </c>
       <c r="G54" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2198,179 +2198,179 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>22750</v>
+        <v>47750</v>
       </c>
       <c r="F55" t="n">
-        <v>2200.9656</v>
+        <v>643.6526</v>
       </c>
       <c r="G55" t="n">
-        <v>50071968.5</v>
+        <v>30734413.9</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>33150</v>
+        <v>8080</v>
       </c>
       <c r="F56" t="n">
-        <v>921.4443</v>
+        <v>3746.0511</v>
       </c>
       <c r="G56" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H56" t="n">
-        <v>2</v>
-      </c>
+        <v>30268092.9</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>38050</v>
+        <v>21950</v>
       </c>
       <c r="F57" t="n">
-        <v>790.1567</v>
+        <v>1378.9564</v>
       </c>
       <c r="G57" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.4</v>
-      </c>
+        <v>30268092.9</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>28850</v>
+        <v>22750</v>
       </c>
       <c r="F58" t="n">
-        <v>1038.0221</v>
+        <v>2200.9656</v>
       </c>
       <c r="G58" t="n">
-        <v>29946939</v>
+        <v>50071968.5</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>76400</v>
+        <v>33150</v>
       </c>
       <c r="F59" t="n">
-        <v>391.9756</v>
+        <v>921.4443</v>
       </c>
       <c r="G59" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>21650</v>
+        <v>38050</v>
       </c>
       <c r="F60" t="n">
-        <v>1383.2304</v>
+        <v>790.1567</v>
       </c>
       <c r="G60" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2380,24 +2380,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>32500</v>
+        <v>28850</v>
       </c>
       <c r="F61" t="n">
-        <v>921.4443</v>
+        <v>1038.0221</v>
       </c>
       <c r="G61" t="n">
         <v>29946939</v>
@@ -2412,12 +2412,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>37900</v>
+        <v>76400</v>
       </c>
       <c r="F62" t="n">
-        <v>790.1567</v>
+        <v>391.9756</v>
       </c>
       <c r="G62" t="n">
         <v>29946939</v>
@@ -2439,17 +2439,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2458,47 +2458,143 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>25300</v>
+        <v>21650</v>
       </c>
       <c r="F63" t="n">
-        <v>1186</v>
+        <v>1383.2304</v>
       </c>
       <c r="G63" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F64" t="n">
+        <v>921.4443</v>
+      </c>
+      <c r="G64" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F65" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G65" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G66" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E64" t="n">
+      <c r="E67" t="n">
         <v>32000</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F67" t="n">
         <v>938</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G67" t="n">
         <v>30016000</v>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,62 +492,62 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>117500</v>
+        <v>105500</v>
       </c>
       <c r="F2" t="n">
-        <v>267.9088</v>
+        <v>283.1607</v>
       </c>
       <c r="G2" t="n">
-        <v>31479278.3</v>
+        <v>29873454.8</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>32050</v>
+        <v>36200</v>
       </c>
       <c r="F3" t="n">
-        <v>982.1928</v>
+        <v>825.2336</v>
       </c>
       <c r="G3" t="n">
-        <v>31479278.3</v>
+        <v>29873454.8</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>사피엔반도체</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>452430</t>
+          <t>468530</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,20 +556,20 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25750</v>
+        <v>47800</v>
       </c>
       <c r="F4" t="n">
-        <v>1222.4962</v>
+        <v>624.9677</v>
       </c>
       <c r="G4" t="n">
-        <v>31479278.3</v>
+        <v>29873454.8</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -588,30 +588,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>108700</v>
+        <v>117500</v>
       </c>
       <c r="F5" t="n">
-        <v>285.6073</v>
+        <v>267.9088</v>
       </c>
       <c r="G5" t="n">
-        <v>31045517.4</v>
+        <v>31479278.3</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -620,96 +620,94 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>36050</v>
+        <v>32050</v>
       </c>
       <c r="F6" t="n">
-        <v>869.3262999999999</v>
+        <v>982.1928</v>
       </c>
       <c r="G6" t="n">
-        <v>31339214.2</v>
+        <v>31479278.3</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>사피엔반도체</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>452430</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7490</v>
+        <v>25750</v>
       </c>
       <c r="F7" t="n">
-        <v>10243.469</v>
+        <v>1222.4962</v>
       </c>
       <c r="G7" t="n">
-        <v>76723582.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-15.37</v>
-      </c>
+        <v>31479278.3</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30500</v>
+        <v>108700</v>
       </c>
       <c r="F8" t="n">
-        <v>963.2346</v>
+        <v>285.6073</v>
       </c>
       <c r="G8" t="n">
-        <v>29378655.8</v>
+        <v>31045517.4</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -718,20 +716,20 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>88400</v>
+        <v>36050</v>
       </c>
       <c r="F9" t="n">
-        <v>332.3377</v>
+        <v>869.3262999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>29378655.8</v>
+        <v>31339214.2</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -746,24 +744,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9100</v>
+        <v>7490</v>
       </c>
       <c r="F10" t="n">
-        <v>2259.594</v>
+        <v>10243.469</v>
       </c>
       <c r="G10" t="n">
-        <v>20562305.7</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>76723582.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-15.37</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -778,24 +778,24 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>39150</v>
+        <v>30500</v>
       </c>
       <c r="F11" t="n">
-        <v>525.2184999999999</v>
+        <v>963.2346</v>
       </c>
       <c r="G11" t="n">
-        <v>20562305.7</v>
+        <v>29378655.8</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -814,13 +814,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>79900</v>
+        <v>88400</v>
       </c>
       <c r="F12" t="n">
-        <v>257.3505</v>
+        <v>332.3377</v>
       </c>
       <c r="G12" t="n">
-        <v>20562305.7</v>
+        <v>29378655.8</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>45500</v>
+        <v>9100</v>
       </c>
       <c r="F13" t="n">
-        <v>451.9188</v>
+        <v>2259.594</v>
       </c>
       <c r="G13" t="n">
         <v>20562305.7</v>
@@ -864,110 +864,108 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>39050</v>
+        <v>39150</v>
       </c>
       <c r="F14" t="n">
-        <v>789.8453</v>
+        <v>525.2184999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>30843458.5</v>
+        <v>20562305.7</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8720</v>
+        <v>79900</v>
       </c>
       <c r="F15" t="n">
-        <v>3255.4339</v>
+        <v>257.3505</v>
       </c>
       <c r="G15" t="n">
-        <v>28387383.9</v>
+        <v>20562305.7</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>16930</v>
+        <v>45500</v>
       </c>
       <c r="F16" t="n">
-        <v>4324.5003</v>
+        <v>451.9188</v>
       </c>
       <c r="G16" t="n">
-        <v>73213790.59999999</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-15.51</v>
-      </c>
+        <v>20562305.7</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -976,13 +974,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>33050</v>
+        <v>39050</v>
       </c>
       <c r="F17" t="n">
-        <v>858.9224</v>
+        <v>789.8453</v>
       </c>
       <c r="G17" t="n">
-        <v>28387383.9</v>
+        <v>30843458.5</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -994,12 +992,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1008,10 +1006,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73500</v>
+        <v>8720</v>
       </c>
       <c r="F18" t="n">
-        <v>386.2229</v>
+        <v>3255.4339</v>
       </c>
       <c r="G18" t="n">
         <v>28387383.9</v>
@@ -1026,29 +1024,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>28400</v>
+        <v>16930</v>
       </c>
       <c r="F19" t="n">
-        <v>999.5558</v>
+        <v>4324.5003</v>
       </c>
       <c r="G19" t="n">
-        <v>28387383.9</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>73213790.59999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-15.51</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1058,31 +1058,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>30500</v>
+        <v>33050</v>
       </c>
       <c r="F20" t="n">
-        <v>3519.9944</v>
+        <v>858.9224</v>
       </c>
       <c r="G20" t="n">
-        <v>107359829.8</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-24.2</v>
-      </c>
+        <v>28387383.9</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1092,12 +1090,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1106,10 +1104,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>38850</v>
+        <v>73500</v>
       </c>
       <c r="F21" t="n">
-        <v>730.692</v>
+        <v>386.2229</v>
       </c>
       <c r="G21" t="n">
         <v>28387383.9</v>
@@ -1124,76 +1122,78 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>37600</v>
+        <v>28400</v>
       </c>
       <c r="F22" t="n">
-        <v>2516.612</v>
+        <v>999.5558</v>
       </c>
       <c r="G22" t="n">
-        <v>94624613</v>
+        <v>28387383.9</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>20400</v>
+        <v>30500</v>
       </c>
       <c r="F23" t="n">
-        <v>1577.2548</v>
+        <v>3519.9944</v>
       </c>
       <c r="G23" t="n">
-        <v>32175998.7</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>107359829.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-24.2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1202,45 +1202,45 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>37600</v>
+        <v>38850</v>
       </c>
       <c r="F24" t="n">
-        <v>285.2482</v>
+        <v>730.692</v>
       </c>
       <c r="G24" t="n">
-        <v>10725332.9</v>
+        <v>28387383.9</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>30100</v>
+        <v>37600</v>
       </c>
       <c r="F25" t="n">
-        <v>356.3234</v>
+        <v>2516.612</v>
       </c>
       <c r="G25" t="n">
-        <v>10725332.9</v>
+        <v>94624613</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>36800</v>
+        <v>20400</v>
       </c>
       <c r="F26" t="n">
-        <v>874.3478</v>
+        <v>1577.2548</v>
       </c>
       <c r="G26" t="n">
         <v>32175998.7</v>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1298,30 +1298,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>46400</v>
+        <v>37600</v>
       </c>
       <c r="F27" t="n">
-        <v>693.4482</v>
+        <v>285.2482</v>
       </c>
       <c r="G27" t="n">
-        <v>32175998.7</v>
+        <v>10725332.9</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1330,30 +1330,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>9520</v>
+        <v>30100</v>
       </c>
       <c r="F28" t="n">
-        <v>1132.5399</v>
+        <v>356.3234</v>
       </c>
       <c r="G28" t="n">
-        <v>10781779.8</v>
+        <v>10725332.9</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1362,30 +1362,30 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>38400</v>
+        <v>36800</v>
       </c>
       <c r="F29" t="n">
-        <v>561.551</v>
+        <v>874.3478</v>
       </c>
       <c r="G29" t="n">
-        <v>21563559.7</v>
+        <v>32175998.7</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>79400</v>
+        <v>46400</v>
       </c>
       <c r="F30" t="n">
-        <v>135.7907</v>
+        <v>693.4482</v>
       </c>
       <c r="G30" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>31050</v>
+        <v>9520</v>
       </c>
       <c r="F31" t="n">
-        <v>347.2393</v>
+        <v>1132.5399</v>
       </c>
       <c r="G31" t="n">
         <v>10781779.8</v>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>38500</v>
+        <v>38400</v>
       </c>
       <c r="F32" t="n">
-        <v>280.0462</v>
+        <v>561.551</v>
       </c>
       <c r="G32" t="n">
-        <v>10781779.8</v>
+        <v>21563559.7</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1490,30 +1490,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>50100</v>
+        <v>79400</v>
       </c>
       <c r="F33" t="n">
-        <v>645.6156</v>
+        <v>135.7907</v>
       </c>
       <c r="G33" t="n">
-        <v>32345339.5</v>
+        <v>10781779.8</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1522,79 +1522,77 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>9990</v>
+        <v>31050</v>
       </c>
       <c r="F34" t="n">
-        <v>3271.9446</v>
+        <v>347.2393</v>
       </c>
       <c r="G34" t="n">
-        <v>32686726.8</v>
+        <v>10781779.8</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>32000</v>
+        <v>38500</v>
       </c>
       <c r="F35" t="n">
-        <v>2127.2811</v>
+        <v>280.0462</v>
       </c>
       <c r="G35" t="n">
-        <v>68072995.90000001</v>
-      </c>
-      <c r="H35" t="n">
-        <v>8.06</v>
-      </c>
+        <v>10781779.8</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>19830</v>
+        <v>50100</v>
       </c>
       <c r="F36" t="n">
-        <v>2747.2455</v>
+        <v>645.6156</v>
       </c>
       <c r="G36" t="n">
-        <v>54477878.1</v>
+        <v>32345339.5</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1606,12 +1604,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1620,13 +1618,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>37100</v>
+        <v>9990</v>
       </c>
       <c r="F37" t="n">
-        <v>293.6813</v>
+        <v>3271.9446</v>
       </c>
       <c r="G37" t="n">
-        <v>10895575.6</v>
+        <v>32686726.8</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1638,29 +1636,31 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>80200</v>
+        <v>32000</v>
       </c>
       <c r="F38" t="n">
-        <v>407.5652</v>
+        <v>2127.2811</v>
       </c>
       <c r="G38" t="n">
-        <v>32686726.8</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>68072995.90000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1670,27 +1670,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>31600</v>
+        <v>19830</v>
       </c>
       <c r="F39" t="n">
-        <v>344.7967</v>
+        <v>2747.2455</v>
       </c>
       <c r="G39" t="n">
-        <v>10895575.6</v>
+        <v>54477878.1</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1716,20 +1716,20 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>38200</v>
+        <v>37100</v>
       </c>
       <c r="F40" t="n">
-        <v>855.6735</v>
+        <v>293.6813</v>
       </c>
       <c r="G40" t="n">
-        <v>32686726.8</v>
+        <v>10895575.6</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1748,30 +1748,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>87800</v>
+        <v>80200</v>
       </c>
       <c r="F41" t="n">
-        <v>384.5603</v>
+        <v>407.5652</v>
       </c>
       <c r="G41" t="n">
-        <v>33764396.5</v>
+        <v>32686726.8</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1780,84 +1780,84 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>52400</v>
+        <v>31600</v>
       </c>
       <c r="F42" t="n">
-        <v>636.0417</v>
+        <v>344.7967</v>
       </c>
       <c r="G42" t="n">
-        <v>33328583.4</v>
+        <v>10895575.6</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>10250</v>
+        <v>38200</v>
       </c>
       <c r="F43" t="n">
-        <v>3328.756</v>
+        <v>855.6735</v>
       </c>
       <c r="G43" t="n">
-        <v>34119749</v>
+        <v>32686726.8</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>10090</v>
+        <v>87800</v>
       </c>
       <c r="F44" t="n">
-        <v>3333.5276</v>
+        <v>384.5603</v>
       </c>
       <c r="G44" t="n">
-        <v>33635293.3</v>
+        <v>33764396.5</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1872,115 +1872,113 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53200</v>
+        <v>52400</v>
       </c>
       <c r="F45" t="n">
-        <v>632.2424</v>
+        <v>636.0417</v>
       </c>
       <c r="G45" t="n">
-        <v>33635293.3</v>
+        <v>33328583.4</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>35050</v>
+        <v>10250</v>
       </c>
       <c r="F46" t="n">
-        <v>941.2811</v>
+        <v>3328.756</v>
       </c>
       <c r="G46" t="n">
-        <v>32991903.3</v>
+        <v>34119749</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>29100</v>
+        <v>10090</v>
       </c>
       <c r="F47" t="n">
-        <v>1976.0221</v>
+        <v>3333.5276</v>
       </c>
       <c r="G47" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>33635293.3</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>43700</v>
+        <v>53200</v>
       </c>
       <c r="F48" t="n">
-        <v>1509.9269</v>
+        <v>632.2424</v>
       </c>
       <c r="G48" t="n">
-        <v>65983806.6</v>
+        <v>33635293.3</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1992,12 +1990,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2006,84 +2004,86 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>49500</v>
+        <v>35050</v>
       </c>
       <c r="F49" t="n">
-        <v>1333.0062</v>
+        <v>941.2811</v>
       </c>
       <c r="G49" t="n">
-        <v>65983806.6</v>
+        <v>32991903.3</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>86300</v>
+        <v>29100</v>
       </c>
       <c r="F50" t="n">
-        <v>366.4646</v>
+        <v>1976.0221</v>
       </c>
       <c r="G50" t="n">
-        <v>31625898.5</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>8490</v>
+        <v>43700</v>
       </c>
       <c r="F51" t="n">
-        <v>3672.3539</v>
+        <v>1509.9269</v>
       </c>
       <c r="G51" t="n">
-        <v>31178284.6</v>
+        <v>65983806.6</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2102,30 +2102,30 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>45500</v>
+        <v>49500</v>
       </c>
       <c r="F52" t="n">
-        <v>685.237</v>
+        <v>1333.0062</v>
       </c>
       <c r="G52" t="n">
-        <v>31178284.6</v>
+        <v>65983806.6</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2134,30 +2134,30 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>7520</v>
+        <v>86300</v>
       </c>
       <c r="F53" t="n">
-        <v>4087.0231</v>
+        <v>366.4646</v>
       </c>
       <c r="G53" t="n">
-        <v>30734413.9</v>
+        <v>31625898.5</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2166,20 +2166,20 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>83000</v>
+        <v>8490</v>
       </c>
       <c r="F54" t="n">
-        <v>370.2941</v>
+        <v>3672.3539</v>
       </c>
       <c r="G54" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2194,24 +2194,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>47750</v>
+        <v>45500</v>
       </c>
       <c r="F55" t="n">
-        <v>643.6526</v>
+        <v>685.237</v>
       </c>
       <c r="G55" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2226,34 +2226,34 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>8080</v>
+        <v>7520</v>
       </c>
       <c r="F56" t="n">
-        <v>3746.0511</v>
+        <v>4087.0231</v>
       </c>
       <c r="G56" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2262,30 +2262,30 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>21950</v>
+        <v>83000</v>
       </c>
       <c r="F57" t="n">
-        <v>1378.9564</v>
+        <v>370.2941</v>
       </c>
       <c r="G57" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2294,179 +2294,179 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>22750</v>
+        <v>47750</v>
       </c>
       <c r="F58" t="n">
-        <v>2200.9656</v>
+        <v>643.6526</v>
       </c>
       <c r="G58" t="n">
-        <v>50071968.5</v>
+        <v>30734413.9</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>33150</v>
+        <v>8080</v>
       </c>
       <c r="F59" t="n">
-        <v>921.4443</v>
+        <v>3746.0511</v>
       </c>
       <c r="G59" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H59" t="n">
-        <v>2</v>
-      </c>
+        <v>30268092.9</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>38050</v>
+        <v>21950</v>
       </c>
       <c r="F60" t="n">
-        <v>790.1567</v>
+        <v>1378.9564</v>
       </c>
       <c r="G60" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.4</v>
-      </c>
+        <v>30268092.9</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>28850</v>
+        <v>22750</v>
       </c>
       <c r="F61" t="n">
-        <v>1038.0221</v>
+        <v>2200.9656</v>
       </c>
       <c r="G61" t="n">
-        <v>29946939</v>
+        <v>50071968.5</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>76400</v>
+        <v>33150</v>
       </c>
       <c r="F62" t="n">
-        <v>391.9756</v>
+        <v>921.4443</v>
       </c>
       <c r="G62" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>21650</v>
+        <v>38050</v>
       </c>
       <c r="F63" t="n">
-        <v>1383.2304</v>
+        <v>790.1567</v>
       </c>
       <c r="G63" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2476,24 +2476,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>32500</v>
+        <v>28850</v>
       </c>
       <c r="F64" t="n">
-        <v>921.4443</v>
+        <v>1038.0221</v>
       </c>
       <c r="G64" t="n">
         <v>29946939</v>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>37900</v>
+        <v>76400</v>
       </c>
       <c r="F65" t="n">
-        <v>790.1567</v>
+        <v>391.9756</v>
       </c>
       <c r="G65" t="n">
         <v>29946939</v>
@@ -2535,17 +2535,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2554,47 +2554,143 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>25300</v>
+        <v>21650</v>
       </c>
       <c r="F66" t="n">
-        <v>1186</v>
+        <v>1383.2304</v>
       </c>
       <c r="G66" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F67" t="n">
+        <v>921.4443</v>
+      </c>
+      <c r="G67" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F68" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G68" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G69" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E67" t="n">
+      <c r="E70" t="n">
         <v>32000</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F70" t="n">
         <v>938</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G70" t="n">
         <v>30016000</v>
       </c>
-      <c r="H67" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,352 +492,350 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105500</v>
+        <v>38200</v>
       </c>
       <c r="F2" t="n">
-        <v>283.1607</v>
+        <v>814.4501</v>
       </c>
       <c r="G2" t="n">
-        <v>29873454.8</v>
+        <v>31111995.5</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>192650</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>36200</v>
+        <v>7510</v>
       </c>
       <c r="F3" t="n">
-        <v>825.2336</v>
+        <v>6904.5707</v>
       </c>
       <c r="G3" t="n">
-        <v>29873454.8</v>
+        <v>51853325.9</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>468530</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>47800</v>
+        <v>35050</v>
       </c>
       <c r="F4" t="n">
-        <v>624.9677</v>
+        <v>2662.9383</v>
       </c>
       <c r="G4" t="n">
-        <v>29873454.8</v>
+        <v>93335986.59999999</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>사피엔반도체</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>452430</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>117500</v>
+        <v>25400</v>
       </c>
       <c r="F5" t="n">
-        <v>267.9088</v>
+        <v>1224.8817</v>
       </c>
       <c r="G5" t="n">
-        <v>31479278.3</v>
+        <v>31111995.5</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>468530</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>32050</v>
+        <v>48750</v>
       </c>
       <c r="F6" t="n">
-        <v>982.1928</v>
+        <v>638.1948</v>
       </c>
       <c r="G6" t="n">
-        <v>31479278.3</v>
+        <v>31111995.5</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>사피엔반도체</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>452430</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25750</v>
+        <v>105500</v>
       </c>
       <c r="F7" t="n">
-        <v>1222.4962</v>
+        <v>283.1607</v>
       </c>
       <c r="G7" t="n">
-        <v>31479278.3</v>
+        <v>29873454.8</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>108700</v>
+        <v>36200</v>
       </c>
       <c r="F8" t="n">
-        <v>285.6073</v>
+        <v>825.2336</v>
       </c>
       <c r="G8" t="n">
-        <v>31045517.4</v>
+        <v>29873454.8</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>468530</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36050</v>
+        <v>47800</v>
       </c>
       <c r="F9" t="n">
-        <v>869.3262999999999</v>
+        <v>624.9677</v>
       </c>
       <c r="G9" t="n">
-        <v>31339214.2</v>
+        <v>29873454.8</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7490</v>
+        <v>117500</v>
       </c>
       <c r="F10" t="n">
-        <v>10243.469</v>
+        <v>267.9088</v>
       </c>
       <c r="G10" t="n">
-        <v>76723582.5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-15.37</v>
-      </c>
+        <v>31479278.3</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>30500</v>
+        <v>32050</v>
       </c>
       <c r="F11" t="n">
-        <v>963.2346</v>
+        <v>982.1928</v>
       </c>
       <c r="G11" t="n">
-        <v>29378655.8</v>
+        <v>31479278.3</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>사피엔반도체</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>452430</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>88400</v>
+        <v>25750</v>
       </c>
       <c r="F12" t="n">
-        <v>332.3377</v>
+        <v>1222.4962</v>
       </c>
       <c r="G12" t="n">
-        <v>29378655.8</v>
+        <v>31479278.3</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -846,20 +844,20 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9100</v>
+        <v>108700</v>
       </c>
       <c r="F13" t="n">
-        <v>2259.594</v>
+        <v>285.6073</v>
       </c>
       <c r="G13" t="n">
-        <v>20562305.7</v>
+        <v>31045517.4</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -878,116 +876,118 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>39150</v>
+        <v>36050</v>
       </c>
       <c r="F14" t="n">
-        <v>525.2184999999999</v>
+        <v>869.3262999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>20562305.7</v>
+        <v>31339214.2</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>79900</v>
+        <v>7490</v>
       </c>
       <c r="F15" t="n">
-        <v>257.3505</v>
+        <v>10243.469</v>
       </c>
       <c r="G15" t="n">
-        <v>20562305.7</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>76723582.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-15.37</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>45500</v>
+        <v>30500</v>
       </c>
       <c r="F16" t="n">
-        <v>451.9188</v>
+        <v>963.2346</v>
       </c>
       <c r="G16" t="n">
-        <v>20562305.7</v>
+        <v>29378655.8</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>39050</v>
+        <v>88400</v>
       </c>
       <c r="F17" t="n">
-        <v>789.8453</v>
+        <v>332.3377</v>
       </c>
       <c r="G17" t="n">
-        <v>30843458.5</v>
+        <v>29378655.8</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1002,132 +1002,130 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8720</v>
+        <v>9100</v>
       </c>
       <c r="F18" t="n">
-        <v>3255.4339</v>
+        <v>2259.594</v>
       </c>
       <c r="G18" t="n">
-        <v>28387383.9</v>
+        <v>20562305.7</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>16930</v>
+        <v>39150</v>
       </c>
       <c r="F19" t="n">
-        <v>4324.5003</v>
+        <v>525.2184999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>73213790.59999999</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-15.51</v>
-      </c>
+        <v>20562305.7</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>33050</v>
+        <v>79900</v>
       </c>
       <c r="F20" t="n">
-        <v>858.9224</v>
+        <v>257.3505</v>
       </c>
       <c r="G20" t="n">
-        <v>28387383.9</v>
+        <v>20562305.7</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>73500</v>
+        <v>45500</v>
       </c>
       <c r="F21" t="n">
-        <v>386.2229</v>
+        <v>451.9188</v>
       </c>
       <c r="G21" t="n">
-        <v>28387383.9</v>
+        <v>20562305.7</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1136,13 +1134,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>28400</v>
+        <v>39050</v>
       </c>
       <c r="F22" t="n">
-        <v>999.5558</v>
+        <v>789.8453</v>
       </c>
       <c r="G22" t="n">
-        <v>28387383.9</v>
+        <v>30843458.5</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1154,31 +1152,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>30500</v>
+        <v>8720</v>
       </c>
       <c r="F23" t="n">
-        <v>3519.9944</v>
+        <v>3255.4339</v>
       </c>
       <c r="G23" t="n">
-        <v>107359829.8</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-24.2</v>
-      </c>
+        <v>28387383.9</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1188,29 +1184,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>38850</v>
+        <v>16930</v>
       </c>
       <c r="F24" t="n">
-        <v>730.692</v>
+        <v>4324.5003</v>
       </c>
       <c r="G24" t="n">
-        <v>28387383.9</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>73213790.59999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-15.51</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1220,44 +1218,44 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>37600</v>
+        <v>33050</v>
       </c>
       <c r="F25" t="n">
-        <v>2516.612</v>
+        <v>858.9224</v>
       </c>
       <c r="G25" t="n">
-        <v>94624613</v>
+        <v>28387383.9</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1266,30 +1264,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>20400</v>
+        <v>73500</v>
       </c>
       <c r="F26" t="n">
-        <v>1577.2548</v>
+        <v>386.2229</v>
       </c>
       <c r="G26" t="n">
-        <v>32175998.7</v>
+        <v>28387383.9</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1298,62 +1296,64 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>37600</v>
+        <v>28400</v>
       </c>
       <c r="F27" t="n">
-        <v>285.2482</v>
+        <v>999.5558</v>
       </c>
       <c r="G27" t="n">
-        <v>10725332.9</v>
+        <v>28387383.9</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>30100</v>
+        <v>30500</v>
       </c>
       <c r="F28" t="n">
-        <v>356.3234</v>
+        <v>3519.9944</v>
       </c>
       <c r="G28" t="n">
-        <v>10725332.9</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>107359829.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-24.2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1362,62 +1362,62 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>36800</v>
+        <v>38850</v>
       </c>
       <c r="F29" t="n">
-        <v>874.3478</v>
+        <v>730.692</v>
       </c>
       <c r="G29" t="n">
-        <v>32175998.7</v>
+        <v>28387383.9</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>46400</v>
+        <v>37600</v>
       </c>
       <c r="F30" t="n">
-        <v>693.4482</v>
+        <v>2516.612</v>
       </c>
       <c r="G30" t="n">
-        <v>32175998.7</v>
+        <v>94624613</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1426,20 +1426,20 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>9520</v>
+        <v>20400</v>
       </c>
       <c r="F31" t="n">
-        <v>1132.5399</v>
+        <v>1577.2548</v>
       </c>
       <c r="G31" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1458,30 +1458,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>38400</v>
+        <v>37600</v>
       </c>
       <c r="F32" t="n">
-        <v>561.551</v>
+        <v>285.2482</v>
       </c>
       <c r="G32" t="n">
-        <v>21563559.7</v>
+        <v>10725332.9</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1490,30 +1490,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>79400</v>
+        <v>30100</v>
       </c>
       <c r="F33" t="n">
-        <v>135.7907</v>
+        <v>356.3234</v>
       </c>
       <c r="G33" t="n">
-        <v>10781779.8</v>
+        <v>10725332.9</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1522,30 +1522,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>31050</v>
+        <v>36800</v>
       </c>
       <c r="F34" t="n">
-        <v>347.2393</v>
+        <v>874.3478</v>
       </c>
       <c r="G34" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1554,13 +1554,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>38500</v>
+        <v>46400</v>
       </c>
       <c r="F35" t="n">
-        <v>280.0462</v>
+        <v>693.4482</v>
       </c>
       <c r="G35" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1586,30 +1586,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>50100</v>
+        <v>9520</v>
       </c>
       <c r="F36" t="n">
-        <v>645.6156</v>
+        <v>1132.5399</v>
       </c>
       <c r="G36" t="n">
-        <v>32345339.5</v>
+        <v>10781779.8</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1618,96 +1618,94 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>9990</v>
+        <v>38400</v>
       </c>
       <c r="F37" t="n">
-        <v>3271.9446</v>
+        <v>561.551</v>
       </c>
       <c r="G37" t="n">
-        <v>32686726.8</v>
+        <v>21563559.7</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>32000</v>
+        <v>79400</v>
       </c>
       <c r="F38" t="n">
-        <v>2127.2811</v>
+        <v>135.7907</v>
       </c>
       <c r="G38" t="n">
-        <v>68072995.90000001</v>
-      </c>
-      <c r="H38" t="n">
-        <v>8.06</v>
-      </c>
+        <v>10781779.8</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>19830</v>
+        <v>31050</v>
       </c>
       <c r="F39" t="n">
-        <v>2747.2455</v>
+        <v>347.2393</v>
       </c>
       <c r="G39" t="n">
-        <v>54477878.1</v>
+        <v>10781779.8</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1716,30 +1714,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>37100</v>
+        <v>38500</v>
       </c>
       <c r="F40" t="n">
-        <v>293.6813</v>
+        <v>280.0462</v>
       </c>
       <c r="G40" t="n">
-        <v>10895575.6</v>
+        <v>10781779.8</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1748,13 +1746,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>80200</v>
+        <v>50100</v>
       </c>
       <c r="F41" t="n">
-        <v>407.5652</v>
+        <v>645.6156</v>
       </c>
       <c r="G41" t="n">
-        <v>32686726.8</v>
+        <v>32345339.5</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1766,12 +1764,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1780,13 +1778,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>31600</v>
+        <v>9990</v>
       </c>
       <c r="F42" t="n">
-        <v>344.7967</v>
+        <v>3271.9446</v>
       </c>
       <c r="G42" t="n">
-        <v>10895575.6</v>
+        <v>32686726.8</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1798,76 +1796,78 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>38200</v>
+        <v>32000</v>
       </c>
       <c r="F43" t="n">
-        <v>855.6735</v>
+        <v>2127.2811</v>
       </c>
       <c r="G43" t="n">
-        <v>32686726.8</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>68072995.90000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>87800</v>
+        <v>19830</v>
       </c>
       <c r="F44" t="n">
-        <v>384.5603</v>
+        <v>2747.2455</v>
       </c>
       <c r="G44" t="n">
-        <v>33764396.5</v>
+        <v>54477878.1</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1876,126 +1876,126 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>52400</v>
+        <v>37100</v>
       </c>
       <c r="F45" t="n">
-        <v>636.0417</v>
+        <v>293.6813</v>
       </c>
       <c r="G45" t="n">
-        <v>33328583.4</v>
+        <v>10895575.6</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>10250</v>
+        <v>80200</v>
       </c>
       <c r="F46" t="n">
-        <v>3328.756</v>
+        <v>407.5652</v>
       </c>
       <c r="G46" t="n">
-        <v>34119749</v>
+        <v>32686726.8</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>10090</v>
+        <v>31600</v>
       </c>
       <c r="F47" t="n">
-        <v>3333.5276</v>
+        <v>344.7967</v>
       </c>
       <c r="G47" t="n">
-        <v>33635293.3</v>
+        <v>10895575.6</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53200</v>
+        <v>38200</v>
       </c>
       <c r="F48" t="n">
-        <v>632.2424</v>
+        <v>855.6735</v>
       </c>
       <c r="G48" t="n">
-        <v>33635293.3</v>
+        <v>32686726.8</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2004,160 +2004,158 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>35050</v>
+        <v>87800</v>
       </c>
       <c r="F49" t="n">
-        <v>941.2811</v>
+        <v>384.5603</v>
       </c>
       <c r="G49" t="n">
-        <v>32991903.3</v>
+        <v>33764396.5</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>29100</v>
+        <v>52400</v>
       </c>
       <c r="F50" t="n">
-        <v>1976.0221</v>
+        <v>636.0417</v>
       </c>
       <c r="G50" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>33328583.4</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>43700</v>
+        <v>10250</v>
       </c>
       <c r="F51" t="n">
-        <v>1509.9269</v>
+        <v>3328.756</v>
       </c>
       <c r="G51" t="n">
-        <v>65983806.6</v>
+        <v>34119749</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>49500</v>
+        <v>10090</v>
       </c>
       <c r="F52" t="n">
-        <v>1333.0062</v>
+        <v>3333.5276</v>
       </c>
       <c r="G52" t="n">
-        <v>65983806.6</v>
+        <v>33635293.3</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>86300</v>
+        <v>53200</v>
       </c>
       <c r="F53" t="n">
-        <v>366.4646</v>
+        <v>632.2424</v>
       </c>
       <c r="G53" t="n">
-        <v>31625898.5</v>
+        <v>33635293.3</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2166,94 +2164,96 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>8490</v>
+        <v>35050</v>
       </c>
       <c r="F54" t="n">
-        <v>3672.3539</v>
+        <v>941.2811</v>
       </c>
       <c r="G54" t="n">
-        <v>31178284.6</v>
+        <v>32991903.3</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>45500</v>
+        <v>29100</v>
       </c>
       <c r="F55" t="n">
-        <v>685.237</v>
+        <v>1976.0221</v>
       </c>
       <c r="G55" t="n">
-        <v>31178284.6</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>7520</v>
+        <v>43700</v>
       </c>
       <c r="F56" t="n">
-        <v>4087.0231</v>
+        <v>1509.9269</v>
       </c>
       <c r="G56" t="n">
-        <v>30734413.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2262,52 +2262,52 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>83000</v>
+        <v>49500</v>
       </c>
       <c r="F57" t="n">
-        <v>370.2941</v>
+        <v>1333.0062</v>
       </c>
       <c r="G57" t="n">
-        <v>30734413.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>47750</v>
+        <v>86300</v>
       </c>
       <c r="F58" t="n">
-        <v>643.6526</v>
+        <v>366.4646</v>
       </c>
       <c r="G58" t="n">
-        <v>30734413.9</v>
+        <v>31625898.5</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2322,34 +2322,34 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>8080</v>
+        <v>8490</v>
       </c>
       <c r="F59" t="n">
-        <v>3746.0511</v>
+        <v>3672.3539</v>
       </c>
       <c r="G59" t="n">
-        <v>30268092.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2358,194 +2358,190 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>21950</v>
+        <v>45500</v>
       </c>
       <c r="F60" t="n">
-        <v>1378.9564</v>
+        <v>685.237</v>
       </c>
       <c r="G60" t="n">
-        <v>30268092.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>22750</v>
+        <v>7520</v>
       </c>
       <c r="F61" t="n">
-        <v>2200.9656</v>
+        <v>4087.0231</v>
       </c>
       <c r="G61" t="n">
-        <v>50071968.5</v>
+        <v>30734413.9</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>33150</v>
+        <v>83000</v>
       </c>
       <c r="F62" t="n">
-        <v>921.4443</v>
+        <v>370.2941</v>
       </c>
       <c r="G62" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H62" t="n">
-        <v>2</v>
-      </c>
+        <v>30734413.9</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>38050</v>
+        <v>47750</v>
       </c>
       <c r="F63" t="n">
-        <v>790.1567</v>
+        <v>643.6526</v>
       </c>
       <c r="G63" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.4</v>
-      </c>
+        <v>30734413.9</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>28850</v>
+        <v>8080</v>
       </c>
       <c r="F64" t="n">
-        <v>1038.0221</v>
+        <v>3746.0511</v>
       </c>
       <c r="G64" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>76400</v>
+        <v>21950</v>
       </c>
       <c r="F65" t="n">
-        <v>391.9756</v>
+        <v>1378.9564</v>
       </c>
       <c r="G65" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2554,20 +2550,20 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>21650</v>
+        <v>22750</v>
       </c>
       <c r="F66" t="n">
-        <v>1383.2304</v>
+        <v>2200.9656</v>
       </c>
       <c r="G66" t="n">
-        <v>29946939</v>
+        <v>50071968.5</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2582,24 +2578,26 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>32500</v>
+        <v>33150</v>
       </c>
       <c r="F67" t="n">
         <v>921.4443</v>
       </c>
       <c r="G67" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H67" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2614,83 +2612,245 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>37900</v>
+        <v>38050</v>
       </c>
       <c r="F68" t="n">
         <v>790.1567</v>
       </c>
       <c r="G68" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>25300</v>
+        <v>28850</v>
       </c>
       <c r="F69" t="n">
-        <v>1186</v>
+        <v>1038.0221</v>
       </c>
       <c r="G69" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>126340</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>76400</v>
+      </c>
+      <c r="F70" t="n">
+        <v>391.9756</v>
+      </c>
+      <c r="G70" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>21650</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1383.2304</v>
+      </c>
+      <c r="G71" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F72" t="n">
+        <v>921.4443</v>
+      </c>
+      <c r="G72" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F73" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G73" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G74" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E70" t="n">
+      <c r="E75" t="n">
         <v>32000</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F75" t="n">
         <v>938</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G75" t="n">
         <v>30016000</v>
       </c>
-      <c r="H70" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,66 +473,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>192650</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>38200</v>
+        <v>7330</v>
       </c>
       <c r="F2" t="n">
-        <v>814.4501</v>
+        <v>4370.3697</v>
       </c>
       <c r="G2" t="n">
-        <v>31111995.5</v>
+        <v>32034809.8</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>드림텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>192650</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7510</v>
+        <v>35200</v>
       </c>
       <c r="F3" t="n">
-        <v>6904.5707</v>
+        <v>2445.8275</v>
       </c>
       <c r="G3" t="n">
-        <v>51853325.9</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>86093126.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-22.58</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -542,12 +544,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,13 +558,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>35050</v>
+        <v>38200</v>
       </c>
       <c r="F4" t="n">
-        <v>2662.9383</v>
+        <v>814.4501</v>
       </c>
       <c r="G4" t="n">
-        <v>93335986.59999999</v>
+        <v>31111995.5</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -574,27 +576,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>사피엔반도체</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>452430</t>
+          <t>192650</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>25400</v>
+        <v>7510</v>
       </c>
       <c r="F5" t="n">
-        <v>1224.8817</v>
+        <v>6904.5707</v>
       </c>
       <c r="G5" t="n">
-        <v>31111995.5</v>
+        <v>51853325.9</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -606,76 +608,76 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>468530</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>48750</v>
+        <v>35050</v>
       </c>
       <c r="F6" t="n">
-        <v>638.1948</v>
+        <v>2662.9383</v>
       </c>
       <c r="G6" t="n">
-        <v>31111995.5</v>
+        <v>93335986.59999999</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>사피엔반도체</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>452430</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105500</v>
+        <v>25400</v>
       </c>
       <c r="F7" t="n">
-        <v>283.1607</v>
+        <v>1224.8817</v>
       </c>
       <c r="G7" t="n">
-        <v>29873454.8</v>
+        <v>31111995.5</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>468530</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,13 +686,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>36200</v>
+        <v>48750</v>
       </c>
       <c r="F8" t="n">
-        <v>825.2336</v>
+        <v>638.1948</v>
       </c>
       <c r="G8" t="n">
-        <v>29873454.8</v>
+        <v>31111995.5</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -702,24 +704,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>468530</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47800</v>
+        <v>105500</v>
       </c>
       <c r="F9" t="n">
-        <v>624.9677</v>
+        <v>283.1607</v>
       </c>
       <c r="G9" t="n">
         <v>29873454.8</v>
@@ -729,64 +731,64 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>117500</v>
+        <v>36200</v>
       </c>
       <c r="F10" t="n">
-        <v>267.9088</v>
+        <v>825.2336</v>
       </c>
       <c r="G10" t="n">
-        <v>31479278.3</v>
+        <v>29873454.8</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>468530</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>32050</v>
+        <v>47800</v>
       </c>
       <c r="F11" t="n">
-        <v>982.1928</v>
+        <v>624.9677</v>
       </c>
       <c r="G11" t="n">
-        <v>31479278.3</v>
+        <v>29873454.8</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -798,24 +800,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>사피엔반도체</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>452430</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>25750</v>
+        <v>117500</v>
       </c>
       <c r="F12" t="n">
-        <v>1222.4962</v>
+        <v>267.9088</v>
       </c>
       <c r="G12" t="n">
         <v>31479278.3</v>
@@ -825,17 +827,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -844,86 +846,84 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>108700</v>
+        <v>32050</v>
       </c>
       <c r="F13" t="n">
-        <v>285.6073</v>
+        <v>982.1928</v>
       </c>
       <c r="G13" t="n">
-        <v>31045517.4</v>
+        <v>31479278.3</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>사피엔반도체</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>452430</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>36050</v>
+        <v>25750</v>
       </c>
       <c r="F14" t="n">
-        <v>869.3262999999999</v>
+        <v>1222.4962</v>
       </c>
       <c r="G14" t="n">
-        <v>31339214.2</v>
+        <v>31479278.3</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>7490</v>
+        <v>108700</v>
       </c>
       <c r="F15" t="n">
-        <v>10243.469</v>
+        <v>285.6073</v>
       </c>
       <c r="G15" t="n">
-        <v>76723582.5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-15.37</v>
-      </c>
+        <v>31045517.4</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -938,17 +938,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>30500</v>
+        <v>36050</v>
       </c>
       <c r="F16" t="n">
-        <v>963.2346</v>
+        <v>869.3262999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>29378655.8</v>
+        <v>31339214.2</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -960,76 +960,78 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>88400</v>
+        <v>7490</v>
       </c>
       <c r="F17" t="n">
-        <v>332.3377</v>
+        <v>10243.469</v>
       </c>
       <c r="G17" t="n">
-        <v>29378655.8</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>76723582.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-15.37</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9100</v>
+        <v>30500</v>
       </c>
       <c r="F18" t="n">
-        <v>2259.594</v>
+        <v>963.2346</v>
       </c>
       <c r="G18" t="n">
-        <v>20562305.7</v>
+        <v>29378655.8</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1038,13 +1040,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>39150</v>
+        <v>88400</v>
       </c>
       <c r="F19" t="n">
-        <v>525.2184999999999</v>
+        <v>332.3377</v>
       </c>
       <c r="G19" t="n">
-        <v>20562305.7</v>
+        <v>29378655.8</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1056,12 +1058,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1070,10 +1072,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>79900</v>
+        <v>9100</v>
       </c>
       <c r="F20" t="n">
-        <v>257.3505</v>
+        <v>2259.594</v>
       </c>
       <c r="G20" t="n">
         <v>20562305.7</v>
@@ -1088,12 +1090,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1102,10 +1104,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>45500</v>
+        <v>39150</v>
       </c>
       <c r="F21" t="n">
-        <v>451.9188</v>
+        <v>525.2184999999999</v>
       </c>
       <c r="G21" t="n">
         <v>20562305.7</v>
@@ -1120,95 +1122,93 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>39050</v>
+        <v>79900</v>
       </c>
       <c r="F22" t="n">
-        <v>789.8453</v>
+        <v>257.3505</v>
       </c>
       <c r="G22" t="n">
-        <v>30843458.5</v>
+        <v>20562305.7</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8720</v>
+        <v>45500</v>
       </c>
       <c r="F23" t="n">
-        <v>3255.4339</v>
+        <v>451.9188</v>
       </c>
       <c r="G23" t="n">
-        <v>28387383.9</v>
+        <v>20562305.7</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>16930</v>
+        <v>39050</v>
       </c>
       <c r="F24" t="n">
-        <v>4324.5003</v>
+        <v>789.8453</v>
       </c>
       <c r="G24" t="n">
-        <v>73213790.59999999</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-15.51</v>
-      </c>
+        <v>30843458.5</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>33050</v>
+        <v>8720</v>
       </c>
       <c r="F25" t="n">
-        <v>858.9224</v>
+        <v>3255.4339</v>
       </c>
       <c r="G25" t="n">
         <v>28387383.9</v>
@@ -1250,29 +1250,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>73500</v>
+        <v>16930</v>
       </c>
       <c r="F26" t="n">
-        <v>386.2229</v>
+        <v>4324.5003</v>
       </c>
       <c r="G26" t="n">
-        <v>28387383.9</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>73213790.59999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-15.51</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1282,12 +1284,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1296,10 +1298,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>28400</v>
+        <v>33050</v>
       </c>
       <c r="F27" t="n">
-        <v>999.5558</v>
+        <v>858.9224</v>
       </c>
       <c r="G27" t="n">
         <v>28387383.9</v>
@@ -1314,31 +1316,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>30500</v>
+        <v>73500</v>
       </c>
       <c r="F28" t="n">
-        <v>3519.9944</v>
+        <v>386.2229</v>
       </c>
       <c r="G28" t="n">
-        <v>107359829.8</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-24.2</v>
-      </c>
+        <v>28387383.9</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>38850</v>
+        <v>28400</v>
       </c>
       <c r="F29" t="n">
-        <v>730.692</v>
+        <v>999.5558</v>
       </c>
       <c r="G29" t="n">
         <v>28387383.9</v>
@@ -1380,44 +1380,46 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>37600</v>
+        <v>30500</v>
       </c>
       <c r="F30" t="n">
-        <v>2516.612</v>
+        <v>3519.9944</v>
       </c>
       <c r="G30" t="n">
-        <v>94624613</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>107359829.8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-24.2</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1426,45 +1428,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>20400</v>
+        <v>38850</v>
       </c>
       <c r="F31" t="n">
-        <v>1577.2548</v>
+        <v>730.692</v>
       </c>
       <c r="G31" t="n">
-        <v>32175998.7</v>
+        <v>28387383.9</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>37600</v>
       </c>
       <c r="F32" t="n">
-        <v>285.2482</v>
+        <v>2516.612</v>
       </c>
       <c r="G32" t="n">
-        <v>10725332.9</v>
+        <v>94624613</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1476,12 +1478,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1490,13 +1492,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>30100</v>
+        <v>20400</v>
       </c>
       <c r="F33" t="n">
-        <v>356.3234</v>
+        <v>1577.2548</v>
       </c>
       <c r="G33" t="n">
-        <v>10725332.9</v>
+        <v>32175998.7</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1508,12 +1510,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1522,13 +1524,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>36800</v>
+        <v>37600</v>
       </c>
       <c r="F34" t="n">
-        <v>874.3478</v>
+        <v>285.2482</v>
       </c>
       <c r="G34" t="n">
-        <v>32175998.7</v>
+        <v>10725332.9</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1540,12 +1542,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1554,30 +1556,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>46400</v>
+        <v>30100</v>
       </c>
       <c r="F35" t="n">
-        <v>693.4482</v>
+        <v>356.3234</v>
       </c>
       <c r="G35" t="n">
-        <v>32175998.7</v>
+        <v>10725332.9</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1586,30 +1588,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>9520</v>
+        <v>36800</v>
       </c>
       <c r="F36" t="n">
-        <v>1132.5399</v>
+        <v>874.3478</v>
       </c>
       <c r="G36" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1618,13 +1620,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>38400</v>
+        <v>46400</v>
       </c>
       <c r="F37" t="n">
-        <v>561.551</v>
+        <v>693.4482</v>
       </c>
       <c r="G37" t="n">
-        <v>21563559.7</v>
+        <v>32175998.7</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1636,12 +1638,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1650,10 +1652,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>79400</v>
+        <v>9520</v>
       </c>
       <c r="F38" t="n">
-        <v>135.7907</v>
+        <v>1132.5399</v>
       </c>
       <c r="G38" t="n">
         <v>10781779.8</v>
@@ -1668,12 +1670,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1682,13 +1684,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>31050</v>
+        <v>38400</v>
       </c>
       <c r="F39" t="n">
-        <v>347.2393</v>
+        <v>561.551</v>
       </c>
       <c r="G39" t="n">
-        <v>10781779.8</v>
+        <v>21563559.7</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1700,12 +1702,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1714,10 +1716,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>38500</v>
+        <v>79400</v>
       </c>
       <c r="F40" t="n">
-        <v>280.0462</v>
+        <v>135.7907</v>
       </c>
       <c r="G40" t="n">
         <v>10781779.8</v>
@@ -1732,12 +1734,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1746,30 +1748,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>50100</v>
+        <v>31050</v>
       </c>
       <c r="F41" t="n">
-        <v>645.6156</v>
+        <v>347.2393</v>
       </c>
       <c r="G41" t="n">
-        <v>32345339.5</v>
+        <v>10781779.8</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1778,49 +1780,47 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>9990</v>
+        <v>38500</v>
       </c>
       <c r="F42" t="n">
-        <v>3271.9446</v>
+        <v>280.0462</v>
       </c>
       <c r="G42" t="n">
-        <v>32686726.8</v>
+        <v>10781779.8</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>32000</v>
+        <v>50100</v>
       </c>
       <c r="F43" t="n">
-        <v>2127.2811</v>
+        <v>645.6156</v>
       </c>
       <c r="G43" t="n">
-        <v>68072995.90000001</v>
-      </c>
-      <c r="H43" t="n">
-        <v>8.06</v>
-      </c>
+        <v>32345339.5</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1830,27 +1830,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>19830</v>
+        <v>9990</v>
       </c>
       <c r="F44" t="n">
-        <v>2747.2455</v>
+        <v>3271.9446</v>
       </c>
       <c r="G44" t="n">
-        <v>54477878.1</v>
+        <v>32686726.8</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1862,29 +1862,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>37100</v>
+        <v>32000</v>
       </c>
       <c r="F45" t="n">
-        <v>293.6813</v>
+        <v>2127.2811</v>
       </c>
       <c r="G45" t="n">
-        <v>10895575.6</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
+        <v>68072995.90000001</v>
+      </c>
+      <c r="H45" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1894,27 +1896,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>80200</v>
+        <v>19830</v>
       </c>
       <c r="F46" t="n">
-        <v>407.5652</v>
+        <v>2747.2455</v>
       </c>
       <c r="G46" t="n">
-        <v>32686726.8</v>
+        <v>54477878.1</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1926,12 +1928,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1940,10 +1942,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>31600</v>
+        <v>37100</v>
       </c>
       <c r="F47" t="n">
-        <v>344.7967</v>
+        <v>293.6813</v>
       </c>
       <c r="G47" t="n">
         <v>10895575.6</v>
@@ -1958,12 +1960,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1972,10 +1974,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>38200</v>
+        <v>80200</v>
       </c>
       <c r="F48" t="n">
-        <v>855.6735</v>
+        <v>407.5652</v>
       </c>
       <c r="G48" t="n">
         <v>32686726.8</v>
@@ -1985,17 +1987,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2004,30 +2006,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>87800</v>
+        <v>31600</v>
       </c>
       <c r="F49" t="n">
-        <v>384.5603</v>
+        <v>344.7967</v>
       </c>
       <c r="G49" t="n">
-        <v>33764396.5</v>
+        <v>10895575.6</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2036,94 +2038,94 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>52400</v>
+        <v>38200</v>
       </c>
       <c r="F50" t="n">
-        <v>636.0417</v>
+        <v>855.6735</v>
       </c>
       <c r="G50" t="n">
-        <v>33328583.4</v>
+        <v>32686726.8</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>10250</v>
+        <v>87800</v>
       </c>
       <c r="F51" t="n">
-        <v>3328.756</v>
+        <v>384.5603</v>
       </c>
       <c r="G51" t="n">
-        <v>34119749</v>
+        <v>33764396.5</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>10090</v>
+        <v>52400</v>
       </c>
       <c r="F52" t="n">
-        <v>3333.5276</v>
+        <v>636.0417</v>
       </c>
       <c r="G52" t="n">
-        <v>33635293.3</v>
+        <v>33328583.4</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2132,81 +2134,79 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53200</v>
+        <v>10250</v>
       </c>
       <c r="F53" t="n">
-        <v>632.2424</v>
+        <v>3328.756</v>
       </c>
       <c r="G53" t="n">
-        <v>33635293.3</v>
+        <v>34119749</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>35050</v>
+        <v>10090</v>
       </c>
       <c r="F54" t="n">
-        <v>941.2811</v>
+        <v>3333.5276</v>
       </c>
       <c r="G54" t="n">
-        <v>32991903.3</v>
+        <v>33635293.3</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>29100</v>
+        <v>53200</v>
       </c>
       <c r="F55" t="n">
-        <v>1976.0221</v>
+        <v>632.2424</v>
       </c>
       <c r="G55" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>33635293.3</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2216,27 +2216,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>43700</v>
+        <v>35050</v>
       </c>
       <c r="F56" t="n">
-        <v>1509.9269</v>
+        <v>941.2811</v>
       </c>
       <c r="G56" t="n">
-        <v>65983806.6</v>
+        <v>32991903.3</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2248,76 +2248,78 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>49500</v>
+        <v>29100</v>
       </c>
       <c r="F57" t="n">
-        <v>1333.0062</v>
+        <v>1976.0221</v>
       </c>
       <c r="G57" t="n">
-        <v>65983806.6</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>86300</v>
+        <v>43700</v>
       </c>
       <c r="F58" t="n">
-        <v>366.4646</v>
+        <v>1509.9269</v>
       </c>
       <c r="G58" t="n">
-        <v>31625898.5</v>
+        <v>65983806.6</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2326,30 +2328,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>8490</v>
+        <v>49500</v>
       </c>
       <c r="F59" t="n">
-        <v>3672.3539</v>
+        <v>1333.0062</v>
       </c>
       <c r="G59" t="n">
-        <v>31178284.6</v>
+        <v>65983806.6</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2358,20 +2360,20 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>45500</v>
+        <v>86300</v>
       </c>
       <c r="F60" t="n">
-        <v>685.237</v>
+        <v>366.4646</v>
       </c>
       <c r="G60" t="n">
-        <v>31178284.6</v>
+        <v>31625898.5</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2390,30 +2392,30 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>7520</v>
+        <v>8490</v>
       </c>
       <c r="F61" t="n">
-        <v>4087.0231</v>
+        <v>3672.3539</v>
       </c>
       <c r="G61" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2422,13 +2424,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>83000</v>
+        <v>45500</v>
       </c>
       <c r="F62" t="n">
-        <v>370.2941</v>
+        <v>685.237</v>
       </c>
       <c r="G62" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2440,24 +2442,24 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>47750</v>
+        <v>7520</v>
       </c>
       <c r="F63" t="n">
-        <v>643.6526</v>
+        <v>4087.0231</v>
       </c>
       <c r="G63" t="n">
         <v>30734413.9</v>
@@ -2467,81 +2469,81 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>8080</v>
+        <v>83000</v>
       </c>
       <c r="F64" t="n">
-        <v>3746.0511</v>
+        <v>370.2941</v>
       </c>
       <c r="G64" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>21950</v>
+        <v>47750</v>
       </c>
       <c r="F65" t="n">
-        <v>1378.9564</v>
+        <v>643.6526</v>
       </c>
       <c r="G65" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2550,49 +2552,47 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>22750</v>
+        <v>8080</v>
       </c>
       <c r="F66" t="n">
-        <v>2200.9656</v>
+        <v>3746.0511</v>
       </c>
       <c r="G66" t="n">
-        <v>50071968.5</v>
+        <v>30268092.9</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>33150</v>
+        <v>21950</v>
       </c>
       <c r="F67" t="n">
-        <v>921.4443</v>
+        <v>1378.9564</v>
       </c>
       <c r="G67" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H67" t="n">
-        <v>2</v>
-      </c>
+        <v>30268092.9</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2602,95 +2602,97 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>38050</v>
+        <v>22750</v>
       </c>
       <c r="F68" t="n">
-        <v>790.1567</v>
+        <v>2200.9656</v>
       </c>
       <c r="G68" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.4</v>
-      </c>
+        <v>50071968.5</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>28850</v>
+        <v>33150</v>
       </c>
       <c r="F69" t="n">
-        <v>1038.0221</v>
+        <v>921.4443</v>
       </c>
       <c r="G69" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H69" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>76400</v>
+        <v>38050</v>
       </c>
       <c r="F70" t="n">
-        <v>391.9756</v>
+        <v>790.1567</v>
       </c>
       <c r="G70" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2700,24 +2702,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>21650</v>
+        <v>28850</v>
       </c>
       <c r="F71" t="n">
-        <v>1383.2304</v>
+        <v>1038.0221</v>
       </c>
       <c r="G71" t="n">
         <v>29946939</v>
@@ -2732,12 +2734,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2746,10 +2748,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>32500</v>
+        <v>76400</v>
       </c>
       <c r="F72" t="n">
-        <v>921.4443</v>
+        <v>391.9756</v>
       </c>
       <c r="G72" t="n">
         <v>29946939</v>
@@ -2764,12 +2766,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2778,10 +2780,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>37900</v>
+        <v>21650</v>
       </c>
       <c r="F73" t="n">
-        <v>790.1567</v>
+        <v>1383.2304</v>
       </c>
       <c r="G73" t="n">
         <v>29946939</v>
@@ -2791,17 +2793,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2810,47 +2812,111 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>25300</v>
+        <v>32500</v>
       </c>
       <c r="F74" t="n">
-        <v>1186</v>
+        <v>921.4443</v>
       </c>
       <c r="G74" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F75" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G75" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G76" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E75" t="n">
+      <c r="E77" t="n">
         <v>32000</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F77" t="n">
         <v>938</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G77" t="n">
         <v>30016000</v>
       </c>
-      <c r="H75" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,83 +473,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>드림텍</t>
+          <t>한라캐스트</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>192650</t>
+          <t>125490</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7330</v>
+        <v>10790</v>
       </c>
       <c r="F2" t="n">
-        <v>4370.3697</v>
+        <v>2939.9458</v>
       </c>
       <c r="G2" t="n">
-        <v>32034809.8</v>
+        <v>31722015.4</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>35200</v>
+        <v>100500</v>
       </c>
       <c r="F3" t="n">
-        <v>2445.8275</v>
+        <v>315.6419</v>
       </c>
       <c r="G3" t="n">
-        <v>86093126.3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-22.58</v>
-      </c>
+        <v>31722015.4</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -558,20 +556,20 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>38200</v>
+        <v>35850</v>
       </c>
       <c r="F4" t="n">
-        <v>814.4501</v>
+        <v>884.854</v>
       </c>
       <c r="G4" t="n">
-        <v>31111995.5</v>
+        <v>31722015.4</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -586,34 +584,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7510</v>
+        <v>6960</v>
       </c>
       <c r="F5" t="n">
-        <v>6904.5707</v>
+        <v>4557.7608</v>
       </c>
       <c r="G5" t="n">
-        <v>51853325.9</v>
+        <v>31722015.4</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>468530</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -622,30 +620,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>35050</v>
+        <v>53900</v>
       </c>
       <c r="F6" t="n">
-        <v>2662.9383</v>
+        <v>588.5346</v>
       </c>
       <c r="G6" t="n">
-        <v>93335986.59999999</v>
+        <v>31722015.4</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>사피엔반도체</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>452430</t>
+          <t>192650</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -654,62 +652,64 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25400</v>
+        <v>7330</v>
       </c>
       <c r="F7" t="n">
-        <v>1224.8817</v>
+        <v>4370.3697</v>
       </c>
       <c r="G7" t="n">
-        <v>31111995.5</v>
+        <v>32034809.8</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>468530</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48750</v>
+        <v>35200</v>
       </c>
       <c r="F8" t="n">
-        <v>638.1948</v>
+        <v>2445.8275</v>
       </c>
       <c r="G8" t="n">
-        <v>31111995.5</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>86093126.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-22.58</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -718,352 +718,350 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105500</v>
+        <v>38200</v>
       </c>
       <c r="F9" t="n">
-        <v>283.1607</v>
+        <v>814.4501</v>
       </c>
       <c r="G9" t="n">
-        <v>29873454.8</v>
+        <v>31111995.5</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>192650</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>36200</v>
+        <v>7510</v>
       </c>
       <c r="F10" t="n">
-        <v>825.2336</v>
+        <v>6904.5707</v>
       </c>
       <c r="G10" t="n">
-        <v>29873454.8</v>
+        <v>51853325.9</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>468530</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>47800</v>
+        <v>35050</v>
       </c>
       <c r="F11" t="n">
-        <v>624.9677</v>
+        <v>2662.9383</v>
       </c>
       <c r="G11" t="n">
-        <v>29873454.8</v>
+        <v>93335986.59999999</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>사피엔반도체</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>452430</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>117500</v>
+        <v>25400</v>
       </c>
       <c r="F12" t="n">
-        <v>267.9088</v>
+        <v>1224.8817</v>
       </c>
       <c r="G12" t="n">
-        <v>31479278.3</v>
+        <v>31111995.5</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>468530</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>32050</v>
+        <v>48750</v>
       </c>
       <c r="F13" t="n">
-        <v>982.1928</v>
+        <v>638.1948</v>
       </c>
       <c r="G13" t="n">
-        <v>31479278.3</v>
+        <v>31111995.5</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>사피엔반도체</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>452430</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>25750</v>
+        <v>105500</v>
       </c>
       <c r="F14" t="n">
-        <v>1222.4962</v>
+        <v>283.1607</v>
       </c>
       <c r="G14" t="n">
-        <v>31479278.3</v>
+        <v>29873454.8</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>108700</v>
+        <v>36200</v>
       </c>
       <c r="F15" t="n">
-        <v>285.6073</v>
+        <v>825.2336</v>
       </c>
       <c r="G15" t="n">
-        <v>31045517.4</v>
+        <v>29873454.8</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>468530</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>36050</v>
+        <v>47800</v>
       </c>
       <c r="F16" t="n">
-        <v>869.3262999999999</v>
+        <v>624.9677</v>
       </c>
       <c r="G16" t="n">
-        <v>31339214.2</v>
+        <v>29873454.8</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7490</v>
+        <v>117500</v>
       </c>
       <c r="F17" t="n">
-        <v>10243.469</v>
+        <v>267.9088</v>
       </c>
       <c r="G17" t="n">
-        <v>76723582.5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-15.37</v>
-      </c>
+        <v>31479278.3</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>30500</v>
+        <v>32050</v>
       </c>
       <c r="F18" t="n">
-        <v>963.2346</v>
+        <v>982.1928</v>
       </c>
       <c r="G18" t="n">
-        <v>29378655.8</v>
+        <v>31479278.3</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>사피엔반도체</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>452430</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>88400</v>
+        <v>25750</v>
       </c>
       <c r="F19" t="n">
-        <v>332.3377</v>
+        <v>1222.4962</v>
       </c>
       <c r="G19" t="n">
-        <v>29378655.8</v>
+        <v>31479278.3</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1072,20 +1070,20 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9100</v>
+        <v>108700</v>
       </c>
       <c r="F20" t="n">
-        <v>2259.594</v>
+        <v>285.6073</v>
       </c>
       <c r="G20" t="n">
-        <v>20562305.7</v>
+        <v>31045517.4</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1104,116 +1102,118 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>39150</v>
+        <v>36050</v>
       </c>
       <c r="F21" t="n">
-        <v>525.2184999999999</v>
+        <v>869.3262999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>20562305.7</v>
+        <v>31339214.2</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>79900</v>
+        <v>7490</v>
       </c>
       <c r="F22" t="n">
-        <v>257.3505</v>
+        <v>10243.469</v>
       </c>
       <c r="G22" t="n">
-        <v>20562305.7</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>76723582.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-15.37</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>45500</v>
+        <v>30500</v>
       </c>
       <c r="F23" t="n">
-        <v>451.9188</v>
+        <v>963.2346</v>
       </c>
       <c r="G23" t="n">
-        <v>20562305.7</v>
+        <v>29378655.8</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>39050</v>
+        <v>88400</v>
       </c>
       <c r="F24" t="n">
-        <v>789.8453</v>
+        <v>332.3377</v>
       </c>
       <c r="G24" t="n">
-        <v>30843458.5</v>
+        <v>29378655.8</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1228,132 +1228,130 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>8720</v>
+        <v>9100</v>
       </c>
       <c r="F25" t="n">
-        <v>3255.4339</v>
+        <v>2259.594</v>
       </c>
       <c r="G25" t="n">
-        <v>28387383.9</v>
+        <v>20562305.7</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>16930</v>
+        <v>39150</v>
       </c>
       <c r="F26" t="n">
-        <v>4324.5003</v>
+        <v>525.2184999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>73213790.59999999</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-15.51</v>
-      </c>
+        <v>20562305.7</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>33050</v>
+        <v>79900</v>
       </c>
       <c r="F27" t="n">
-        <v>858.9224</v>
+        <v>257.3505</v>
       </c>
       <c r="G27" t="n">
-        <v>28387383.9</v>
+        <v>20562305.7</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>73500</v>
+        <v>45500</v>
       </c>
       <c r="F28" t="n">
-        <v>386.2229</v>
+        <v>451.9188</v>
       </c>
       <c r="G28" t="n">
-        <v>28387383.9</v>
+        <v>20562305.7</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1362,13 +1360,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>28400</v>
+        <v>39050</v>
       </c>
       <c r="F29" t="n">
-        <v>999.5558</v>
+        <v>789.8453</v>
       </c>
       <c r="G29" t="n">
-        <v>28387383.9</v>
+        <v>30843458.5</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1380,31 +1378,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>30500</v>
+        <v>8720</v>
       </c>
       <c r="F30" t="n">
-        <v>3519.9944</v>
+        <v>3255.4339</v>
       </c>
       <c r="G30" t="n">
-        <v>107359829.8</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-24.2</v>
-      </c>
+        <v>28387383.9</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1414,29 +1410,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>38850</v>
+        <v>16930</v>
       </c>
       <c r="F31" t="n">
-        <v>730.692</v>
+        <v>4324.5003</v>
       </c>
       <c r="G31" t="n">
-        <v>28387383.9</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>73213790.59999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-15.51</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1446,44 +1444,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>37600</v>
+        <v>33050</v>
       </c>
       <c r="F32" t="n">
-        <v>2516.612</v>
+        <v>858.9224</v>
       </c>
       <c r="G32" t="n">
-        <v>94624613</v>
+        <v>28387383.9</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1492,30 +1490,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>20400</v>
+        <v>73500</v>
       </c>
       <c r="F33" t="n">
-        <v>1577.2548</v>
+        <v>386.2229</v>
       </c>
       <c r="G33" t="n">
-        <v>32175998.7</v>
+        <v>28387383.9</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1524,62 +1522,64 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>37600</v>
+        <v>28400</v>
       </c>
       <c r="F34" t="n">
-        <v>285.2482</v>
+        <v>999.5558</v>
       </c>
       <c r="G34" t="n">
-        <v>10725332.9</v>
+        <v>28387383.9</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>30100</v>
+        <v>30500</v>
       </c>
       <c r="F35" t="n">
-        <v>356.3234</v>
+        <v>3519.9944</v>
       </c>
       <c r="G35" t="n">
-        <v>10725332.9</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>107359829.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-24.2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1588,62 +1588,62 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>36800</v>
+        <v>38850</v>
       </c>
       <c r="F36" t="n">
-        <v>874.3478</v>
+        <v>730.692</v>
       </c>
       <c r="G36" t="n">
-        <v>32175998.7</v>
+        <v>28387383.9</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>46400</v>
+        <v>37600</v>
       </c>
       <c r="F37" t="n">
-        <v>693.4482</v>
+        <v>2516.612</v>
       </c>
       <c r="G37" t="n">
-        <v>32175998.7</v>
+        <v>94624613</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1652,20 +1652,20 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>9520</v>
+        <v>20400</v>
       </c>
       <c r="F38" t="n">
-        <v>1132.5399</v>
+        <v>1577.2548</v>
       </c>
       <c r="G38" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1684,30 +1684,30 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>38400</v>
+        <v>37600</v>
       </c>
       <c r="F39" t="n">
-        <v>561.551</v>
+        <v>285.2482</v>
       </c>
       <c r="G39" t="n">
-        <v>21563559.7</v>
+        <v>10725332.9</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1716,30 +1716,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>79400</v>
+        <v>30100</v>
       </c>
       <c r="F40" t="n">
-        <v>135.7907</v>
+        <v>356.3234</v>
       </c>
       <c r="G40" t="n">
-        <v>10781779.8</v>
+        <v>10725332.9</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1748,30 +1748,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>31050</v>
+        <v>36800</v>
       </c>
       <c r="F41" t="n">
-        <v>347.2393</v>
+        <v>874.3478</v>
       </c>
       <c r="G41" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1780,13 +1780,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>38500</v>
+        <v>46400</v>
       </c>
       <c r="F42" t="n">
-        <v>280.0462</v>
+        <v>693.4482</v>
       </c>
       <c r="G42" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1798,12 +1798,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1812,30 +1812,30 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>50100</v>
+        <v>9520</v>
       </c>
       <c r="F43" t="n">
-        <v>645.6156</v>
+        <v>1132.5399</v>
       </c>
       <c r="G43" t="n">
-        <v>32345339.5</v>
+        <v>10781779.8</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1844,96 +1844,94 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>9990</v>
+        <v>38400</v>
       </c>
       <c r="F44" t="n">
-        <v>3271.9446</v>
+        <v>561.551</v>
       </c>
       <c r="G44" t="n">
-        <v>32686726.8</v>
+        <v>21563559.7</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>32000</v>
+        <v>79400</v>
       </c>
       <c r="F45" t="n">
-        <v>2127.2811</v>
+        <v>135.7907</v>
       </c>
       <c r="G45" t="n">
-        <v>68072995.90000001</v>
-      </c>
-      <c r="H45" t="n">
-        <v>8.06</v>
-      </c>
+        <v>10781779.8</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>19830</v>
+        <v>31050</v>
       </c>
       <c r="F46" t="n">
-        <v>2747.2455</v>
+        <v>347.2393</v>
       </c>
       <c r="G46" t="n">
-        <v>54477878.1</v>
+        <v>10781779.8</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1942,30 +1940,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>37100</v>
+        <v>38500</v>
       </c>
       <c r="F47" t="n">
-        <v>293.6813</v>
+        <v>280.0462</v>
       </c>
       <c r="G47" t="n">
-        <v>10895575.6</v>
+        <v>10781779.8</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1974,13 +1972,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>80200</v>
+        <v>50100</v>
       </c>
       <c r="F48" t="n">
-        <v>407.5652</v>
+        <v>645.6156</v>
       </c>
       <c r="G48" t="n">
-        <v>32686726.8</v>
+        <v>32345339.5</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1992,12 +1990,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2006,13 +2004,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>31600</v>
+        <v>9990</v>
       </c>
       <c r="F49" t="n">
-        <v>344.7967</v>
+        <v>3271.9446</v>
       </c>
       <c r="G49" t="n">
-        <v>10895575.6</v>
+        <v>32686726.8</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2024,76 +2022,78 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>38200</v>
+        <v>32000</v>
       </c>
       <c r="F50" t="n">
-        <v>855.6735</v>
+        <v>2127.2811</v>
       </c>
       <c r="G50" t="n">
-        <v>32686726.8</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
+        <v>68072995.90000001</v>
+      </c>
+      <c r="H50" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>87800</v>
+        <v>19830</v>
       </c>
       <c r="F51" t="n">
-        <v>384.5603</v>
+        <v>2747.2455</v>
       </c>
       <c r="G51" t="n">
-        <v>33764396.5</v>
+        <v>54477878.1</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2102,126 +2102,126 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>52400</v>
+        <v>37100</v>
       </c>
       <c r="F52" t="n">
-        <v>636.0417</v>
+        <v>293.6813</v>
       </c>
       <c r="G52" t="n">
-        <v>33328583.4</v>
+        <v>10895575.6</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>10250</v>
+        <v>80200</v>
       </c>
       <c r="F53" t="n">
-        <v>3328.756</v>
+        <v>407.5652</v>
       </c>
       <c r="G53" t="n">
-        <v>34119749</v>
+        <v>32686726.8</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>10090</v>
+        <v>31600</v>
       </c>
       <c r="F54" t="n">
-        <v>3333.5276</v>
+        <v>344.7967</v>
       </c>
       <c r="G54" t="n">
-        <v>33635293.3</v>
+        <v>10895575.6</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53200</v>
+        <v>38200</v>
       </c>
       <c r="F55" t="n">
-        <v>632.2424</v>
+        <v>855.6735</v>
       </c>
       <c r="G55" t="n">
-        <v>33635293.3</v>
+        <v>32686726.8</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2230,160 +2230,158 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>35050</v>
+        <v>87800</v>
       </c>
       <c r="F56" t="n">
-        <v>941.2811</v>
+        <v>384.5603</v>
       </c>
       <c r="G56" t="n">
-        <v>32991903.3</v>
+        <v>33764396.5</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>29100</v>
+        <v>52400</v>
       </c>
       <c r="F57" t="n">
-        <v>1976.0221</v>
+        <v>636.0417</v>
       </c>
       <c r="G57" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>33328583.4</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>43700</v>
+        <v>10250</v>
       </c>
       <c r="F58" t="n">
-        <v>1509.9269</v>
+        <v>3328.756</v>
       </c>
       <c r="G58" t="n">
-        <v>65983806.6</v>
+        <v>34119749</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>49500</v>
+        <v>10090</v>
       </c>
       <c r="F59" t="n">
-        <v>1333.0062</v>
+        <v>3333.5276</v>
       </c>
       <c r="G59" t="n">
-        <v>65983806.6</v>
+        <v>33635293.3</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>86300</v>
+        <v>53200</v>
       </c>
       <c r="F60" t="n">
-        <v>366.4646</v>
+        <v>632.2424</v>
       </c>
       <c r="G60" t="n">
-        <v>31625898.5</v>
+        <v>33635293.3</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2392,94 +2390,96 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>8490</v>
+        <v>35050</v>
       </c>
       <c r="F61" t="n">
-        <v>3672.3539</v>
+        <v>941.2811</v>
       </c>
       <c r="G61" t="n">
-        <v>31178284.6</v>
+        <v>32991903.3</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>45500</v>
+        <v>29100</v>
       </c>
       <c r="F62" t="n">
-        <v>685.237</v>
+        <v>1976.0221</v>
       </c>
       <c r="G62" t="n">
-        <v>31178284.6</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>7520</v>
+        <v>43700</v>
       </c>
       <c r="F63" t="n">
-        <v>4087.0231</v>
+        <v>1509.9269</v>
       </c>
       <c r="G63" t="n">
-        <v>30734413.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2488,52 +2488,52 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>83000</v>
+        <v>49500</v>
       </c>
       <c r="F64" t="n">
-        <v>370.2941</v>
+        <v>1333.0062</v>
       </c>
       <c r="G64" t="n">
-        <v>30734413.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>47750</v>
+        <v>86300</v>
       </c>
       <c r="F65" t="n">
-        <v>643.6526</v>
+        <v>366.4646</v>
       </c>
       <c r="G65" t="n">
-        <v>30734413.9</v>
+        <v>31625898.5</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2548,34 +2548,34 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>8080</v>
+        <v>8490</v>
       </c>
       <c r="F66" t="n">
-        <v>3746.0511</v>
+        <v>3672.3539</v>
       </c>
       <c r="G66" t="n">
-        <v>30268092.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2584,194 +2584,190 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>21950</v>
+        <v>45500</v>
       </c>
       <c r="F67" t="n">
-        <v>1378.9564</v>
+        <v>685.237</v>
       </c>
       <c r="G67" t="n">
-        <v>30268092.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>22750</v>
+        <v>7520</v>
       </c>
       <c r="F68" t="n">
-        <v>2200.9656</v>
+        <v>4087.0231</v>
       </c>
       <c r="G68" t="n">
-        <v>50071968.5</v>
+        <v>30734413.9</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>33150</v>
+        <v>83000</v>
       </c>
       <c r="F69" t="n">
-        <v>921.4443</v>
+        <v>370.2941</v>
       </c>
       <c r="G69" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H69" t="n">
-        <v>2</v>
-      </c>
+        <v>30734413.9</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>38050</v>
+        <v>47750</v>
       </c>
       <c r="F70" t="n">
-        <v>790.1567</v>
+        <v>643.6526</v>
       </c>
       <c r="G70" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0.4</v>
-      </c>
+        <v>30734413.9</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>28850</v>
+        <v>8080</v>
       </c>
       <c r="F71" t="n">
-        <v>1038.0221</v>
+        <v>3746.0511</v>
       </c>
       <c r="G71" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>76400</v>
+        <v>21950</v>
       </c>
       <c r="F72" t="n">
-        <v>391.9756</v>
+        <v>1378.9564</v>
       </c>
       <c r="G72" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2780,20 +2776,20 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>21650</v>
+        <v>22750</v>
       </c>
       <c r="F73" t="n">
-        <v>1383.2304</v>
+        <v>2200.9656</v>
       </c>
       <c r="G73" t="n">
-        <v>29946939</v>
+        <v>50071968.5</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2808,24 +2804,26 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>32500</v>
+        <v>33150</v>
       </c>
       <c r="F74" t="n">
         <v>921.4443</v>
       </c>
       <c r="G74" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H74" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2840,83 +2838,245 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>37900</v>
+        <v>38050</v>
       </c>
       <c r="F75" t="n">
         <v>790.1567</v>
       </c>
       <c r="G75" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H75" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>25300</v>
+        <v>28850</v>
       </c>
       <c r="F76" t="n">
-        <v>1186</v>
+        <v>1038.0221</v>
       </c>
       <c r="G76" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>126340</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>76400</v>
+      </c>
+      <c r="F77" t="n">
+        <v>391.9756</v>
+      </c>
+      <c r="G77" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>21650</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1383.2304</v>
+      </c>
+      <c r="G78" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F79" t="n">
+        <v>921.4443</v>
+      </c>
+      <c r="G79" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F80" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G80" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G81" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E77" t="n">
+      <c r="E82" t="n">
         <v>32000</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F82" t="n">
         <v>938</v>
       </c>
-      <c r="G77" t="n">
+      <c r="G82" t="n">
         <v>30016000</v>
       </c>
-      <c r="H77" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/mingu_mp_history.xlsx
+++ b/docs/downloads/mingu_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,24 +488,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10790</v>
+        <v>10040</v>
       </c>
       <c r="F2" t="n">
-        <v>2939.9458</v>
+        <v>2975.4269</v>
       </c>
       <c r="G2" t="n">
-        <v>31722015.4</v>
+        <v>29873286.5</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -524,77 +524,77 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100500</v>
+        <v>92100</v>
       </c>
       <c r="F3" t="n">
-        <v>315.6419</v>
+        <v>324.3571</v>
       </c>
       <c r="G3" t="n">
-        <v>31722015.4</v>
+        <v>29873286.5</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>295310</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>35850</v>
+        <v>58600</v>
       </c>
       <c r="F4" t="n">
-        <v>884.854</v>
+        <v>509.783</v>
       </c>
       <c r="G4" t="n">
-        <v>31722015.4</v>
+        <v>29873286.5</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>드림텍</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>192650</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6960</v>
+        <v>36550</v>
       </c>
       <c r="F5" t="n">
-        <v>4557.7608</v>
+        <v>1634.6532</v>
       </c>
       <c r="G5" t="n">
-        <v>31722015.4</v>
+        <v>59746573.1</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -606,24 +606,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>한라캐스트</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>468530</t>
+          <t>125490</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53900</v>
+        <v>10790</v>
       </c>
       <c r="F6" t="n">
-        <v>588.5346</v>
+        <v>2939.9458</v>
       </c>
       <c r="G6" t="n">
         <v>31722015.4</v>
@@ -633,17 +633,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>드림텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>192650</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,177 +652,177 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7330</v>
+        <v>100500</v>
       </c>
       <c r="F7" t="n">
-        <v>4370.3697</v>
+        <v>315.6419</v>
       </c>
       <c r="G7" t="n">
-        <v>32034809.8</v>
+        <v>31722015.4</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>35200</v>
+        <v>35850</v>
       </c>
       <c r="F8" t="n">
-        <v>2445.8275</v>
+        <v>884.854</v>
       </c>
       <c r="G8" t="n">
-        <v>86093126.3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-22.58</v>
-      </c>
+        <v>31722015.4</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>192650</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38200</v>
+        <v>6960</v>
       </c>
       <c r="F9" t="n">
-        <v>814.4501</v>
+        <v>4557.7608</v>
       </c>
       <c r="G9" t="n">
-        <v>31111995.5</v>
+        <v>31722015.4</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>드림텍</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>192650</t>
+          <t>468530</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7510</v>
+        <v>53900</v>
       </c>
       <c r="F10" t="n">
-        <v>6904.5707</v>
+        <v>588.5346</v>
       </c>
       <c r="G10" t="n">
-        <v>51853325.9</v>
+        <v>31722015.4</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>192650</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>35050</v>
+        <v>7330</v>
       </c>
       <c r="F11" t="n">
-        <v>2662.9383</v>
+        <v>4370.3697</v>
       </c>
       <c r="G11" t="n">
-        <v>93335986.59999999</v>
+        <v>32034809.8</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>사피엔반도체</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>452430</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>25400</v>
+        <v>35200</v>
       </c>
       <c r="F12" t="n">
-        <v>1224.8817</v>
+        <v>2445.8275</v>
       </c>
       <c r="G12" t="n">
-        <v>31111995.5</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>86093126.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-22.58</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -832,24 +832,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>468530</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>48750</v>
+        <v>38200</v>
       </c>
       <c r="F13" t="n">
-        <v>638.1948</v>
+        <v>814.4501</v>
       </c>
       <c r="G13" t="n">
         <v>31111995.5</v>
@@ -859,39 +859,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>192650</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105500</v>
+        <v>7510</v>
       </c>
       <c r="F14" t="n">
-        <v>283.1607</v>
+        <v>6904.5707</v>
       </c>
       <c r="G14" t="n">
-        <v>29873454.8</v>
+        <v>51853325.9</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -906,98 +906,98 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>36200</v>
+        <v>35050</v>
       </c>
       <c r="F15" t="n">
-        <v>825.2336</v>
+        <v>2662.9383</v>
       </c>
       <c r="G15" t="n">
-        <v>29873454.8</v>
+        <v>93335986.59999999</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>프로티나</t>
+          <t>사피엔반도체</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>468530</t>
+          <t>452430</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>47800</v>
+        <v>25400</v>
       </c>
       <c r="F16" t="n">
-        <v>624.9677</v>
+        <v>1224.8817</v>
       </c>
       <c r="G16" t="n">
-        <v>29873454.8</v>
+        <v>31111995.5</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>468530</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>117500</v>
+        <v>48750</v>
       </c>
       <c r="F17" t="n">
-        <v>267.9088</v>
+        <v>638.1948</v>
       </c>
       <c r="G17" t="n">
-        <v>31479278.3</v>
+        <v>31111995.5</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1006,94 +1006,94 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>32050</v>
+        <v>105500</v>
       </c>
       <c r="F18" t="n">
-        <v>982.1928</v>
+        <v>283.1607</v>
       </c>
       <c r="G18" t="n">
-        <v>31479278.3</v>
+        <v>29873454.8</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>사피엔반도체</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>452430</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>25750</v>
+        <v>36200</v>
       </c>
       <c r="F19" t="n">
-        <v>1222.4962</v>
+        <v>825.2336</v>
       </c>
       <c r="G19" t="n">
-        <v>31479278.3</v>
+        <v>29873454.8</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>468530</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>108700</v>
+        <v>47800</v>
       </c>
       <c r="F20" t="n">
-        <v>285.6073</v>
+        <v>624.9677</v>
       </c>
       <c r="G20" t="n">
-        <v>31045517.4</v>
+        <v>29873454.8</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1102,86 +1102,84 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>36050</v>
+        <v>117500</v>
       </c>
       <c r="F21" t="n">
-        <v>869.3262999999999</v>
+        <v>267.9088</v>
       </c>
       <c r="G21" t="n">
-        <v>31339214.2</v>
+        <v>31479278.3</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7490</v>
+        <v>32050</v>
       </c>
       <c r="F22" t="n">
-        <v>10243.469</v>
+        <v>982.1928</v>
       </c>
       <c r="G22" t="n">
-        <v>76723582.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-15.37</v>
-      </c>
+        <v>31479278.3</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>사피엔반도체</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>452430</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>30500</v>
+        <v>25750</v>
       </c>
       <c r="F23" t="n">
-        <v>963.2346</v>
+        <v>1222.4962</v>
       </c>
       <c r="G23" t="n">
-        <v>29378655.8</v>
+        <v>31479278.3</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1200,30 +1198,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>88400</v>
+        <v>108700</v>
       </c>
       <c r="F24" t="n">
-        <v>332.3377</v>
+        <v>285.6073</v>
       </c>
       <c r="G24" t="n">
-        <v>29378655.8</v>
+        <v>31045517.4</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1232,94 +1230,96 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>9100</v>
+        <v>36050</v>
       </c>
       <c r="F25" t="n">
-        <v>2259.594</v>
+        <v>869.3262999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>20562305.7</v>
+        <v>31339214.2</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>39150</v>
+        <v>7490</v>
       </c>
       <c r="F26" t="n">
-        <v>525.2184999999999</v>
+        <v>10243.469</v>
       </c>
       <c r="G26" t="n">
-        <v>20562305.7</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>76723582.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-15.37</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>79900</v>
+        <v>30500</v>
       </c>
       <c r="F27" t="n">
-        <v>257.3505</v>
+        <v>963.2346</v>
       </c>
       <c r="G27" t="n">
-        <v>20562305.7</v>
+        <v>29378655.8</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1328,13 +1328,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>45500</v>
+        <v>88400</v>
       </c>
       <c r="F28" t="n">
-        <v>451.9188</v>
+        <v>332.3377</v>
       </c>
       <c r="G28" t="n">
-        <v>20562305.7</v>
+        <v>29378655.8</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1346,142 +1346,140 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>39050</v>
+        <v>9100</v>
       </c>
       <c r="F29" t="n">
-        <v>789.8453</v>
+        <v>2259.594</v>
       </c>
       <c r="G29" t="n">
-        <v>30843458.5</v>
+        <v>20562305.7</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>8720</v>
+        <v>39150</v>
       </c>
       <c r="F30" t="n">
-        <v>3255.4339</v>
+        <v>525.2184999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>28387383.9</v>
+        <v>20562305.7</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>16930</v>
+        <v>79900</v>
       </c>
       <c r="F31" t="n">
-        <v>4324.5003</v>
+        <v>257.3505</v>
       </c>
       <c r="G31" t="n">
-        <v>73213790.59999999</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-15.51</v>
-      </c>
+        <v>20562305.7</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>33050</v>
+        <v>45500</v>
       </c>
       <c r="F32" t="n">
-        <v>858.9224</v>
+        <v>451.9188</v>
       </c>
       <c r="G32" t="n">
-        <v>28387383.9</v>
+        <v>20562305.7</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1490,13 +1488,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>73500</v>
+        <v>39050</v>
       </c>
       <c r="F33" t="n">
-        <v>386.2229</v>
+        <v>789.8453</v>
       </c>
       <c r="G33" t="n">
-        <v>28387383.9</v>
+        <v>30843458.5</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1508,12 +1506,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1522,10 +1520,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>28400</v>
+        <v>8720</v>
       </c>
       <c r="F34" t="n">
-        <v>999.5558</v>
+        <v>3255.4339</v>
       </c>
       <c r="G34" t="n">
         <v>28387383.9</v>
@@ -1540,12 +1538,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1554,16 +1552,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>30500</v>
+        <v>16930</v>
       </c>
       <c r="F35" t="n">
-        <v>3519.9944</v>
+        <v>4324.5003</v>
       </c>
       <c r="G35" t="n">
-        <v>107359829.8</v>
+        <v>73213790.59999999</v>
       </c>
       <c r="H35" t="n">
-        <v>-24.2</v>
+        <v>-15.51</v>
       </c>
     </row>
     <row r="36">
@@ -1574,12 +1572,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1588,10 +1586,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>38850</v>
+        <v>33050</v>
       </c>
       <c r="F36" t="n">
-        <v>730.692</v>
+        <v>858.9224</v>
       </c>
       <c r="G36" t="n">
         <v>28387383.9</v>
@@ -1606,44 +1604,44 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>37600</v>
+        <v>73500</v>
       </c>
       <c r="F37" t="n">
-        <v>2516.612</v>
+        <v>386.2229</v>
       </c>
       <c r="G37" t="n">
-        <v>94624613</v>
+        <v>28387383.9</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1652,62 +1650,64 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>20400</v>
+        <v>28400</v>
       </c>
       <c r="F38" t="n">
-        <v>1577.2548</v>
+        <v>999.5558</v>
       </c>
       <c r="G38" t="n">
-        <v>32175998.7</v>
+        <v>28387383.9</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>37600</v>
+        <v>30500</v>
       </c>
       <c r="F39" t="n">
-        <v>285.2482</v>
+        <v>3519.9944</v>
       </c>
       <c r="G39" t="n">
-        <v>10725332.9</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>107359829.8</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-24.2</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1716,45 +1716,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>30100</v>
+        <v>38850</v>
       </c>
       <c r="F40" t="n">
-        <v>356.3234</v>
+        <v>730.692</v>
       </c>
       <c r="G40" t="n">
-        <v>10725332.9</v>
+        <v>28387383.9</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>36800</v>
+        <v>37600</v>
       </c>
       <c r="F41" t="n">
-        <v>874.3478</v>
+        <v>2516.612</v>
       </c>
       <c r="G41" t="n">
-        <v>32175998.7</v>
+        <v>94624613</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>46400</v>
+        <v>20400</v>
       </c>
       <c r="F42" t="n">
-        <v>693.4482</v>
+        <v>1577.2548</v>
       </c>
       <c r="G42" t="n">
         <v>32175998.7</v>
@@ -1793,17 +1793,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1812,30 +1812,30 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>9520</v>
+        <v>37600</v>
       </c>
       <c r="F43" t="n">
-        <v>1132.5399</v>
+        <v>285.2482</v>
       </c>
       <c r="G43" t="n">
-        <v>10781779.8</v>
+        <v>10725332.9</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1844,30 +1844,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>38400</v>
+        <v>30100</v>
       </c>
       <c r="F44" t="n">
-        <v>561.551</v>
+        <v>356.3234</v>
       </c>
       <c r="G44" t="n">
-        <v>21563559.7</v>
+        <v>10725332.9</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1876,30 +1876,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>79400</v>
+        <v>36800</v>
       </c>
       <c r="F45" t="n">
-        <v>135.7907</v>
+        <v>874.3478</v>
       </c>
       <c r="G45" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1908,13 +1908,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>31050</v>
+        <v>46400</v>
       </c>
       <c r="F46" t="n">
-        <v>347.2393</v>
+        <v>693.4482</v>
       </c>
       <c r="G46" t="n">
-        <v>10781779.8</v>
+        <v>32175998.7</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1926,12 +1926,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>38500</v>
+        <v>9520</v>
       </c>
       <c r="F47" t="n">
-        <v>280.0462</v>
+        <v>1132.5399</v>
       </c>
       <c r="G47" t="n">
         <v>10781779.8</v>
@@ -1958,12 +1958,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1972,30 +1972,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>50100</v>
+        <v>38400</v>
       </c>
       <c r="F48" t="n">
-        <v>645.6156</v>
+        <v>561.551</v>
       </c>
       <c r="G48" t="n">
-        <v>32345339.5</v>
+        <v>21563559.7</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2004,96 +2004,94 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>9990</v>
+        <v>79400</v>
       </c>
       <c r="F49" t="n">
-        <v>3271.9446</v>
+        <v>135.7907</v>
       </c>
       <c r="G49" t="n">
-        <v>32686726.8</v>
+        <v>10781779.8</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>32000</v>
+        <v>31050</v>
       </c>
       <c r="F50" t="n">
-        <v>2127.2811</v>
+        <v>347.2393</v>
       </c>
       <c r="G50" t="n">
-        <v>68072995.90000001</v>
-      </c>
-      <c r="H50" t="n">
-        <v>8.06</v>
-      </c>
+        <v>10781779.8</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>052710</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>19830</v>
+        <v>38500</v>
       </c>
       <c r="F51" t="n">
-        <v>2747.2455</v>
+        <v>280.0462</v>
       </c>
       <c r="G51" t="n">
-        <v>54477878.1</v>
+        <v>10781779.8</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2102,13 +2100,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>37100</v>
+        <v>50100</v>
       </c>
       <c r="F52" t="n">
-        <v>293.6813</v>
+        <v>645.6156</v>
       </c>
       <c r="G52" t="n">
-        <v>10895575.6</v>
+        <v>32345339.5</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2120,12 +2118,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2134,10 +2132,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>80200</v>
+        <v>9990</v>
       </c>
       <c r="F53" t="n">
-        <v>407.5652</v>
+        <v>3271.9446</v>
       </c>
       <c r="G53" t="n">
         <v>32686726.8</v>
@@ -2152,29 +2150,31 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>31600</v>
+        <v>32000</v>
       </c>
       <c r="F54" t="n">
-        <v>344.7967</v>
+        <v>2127.2811</v>
       </c>
       <c r="G54" t="n">
-        <v>10895575.6</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>68072995.90000001</v>
+      </c>
+      <c r="H54" t="n">
+        <v>8.06</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2184,44 +2184,44 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>052710</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>38200</v>
+        <v>19830</v>
       </c>
       <c r="F55" t="n">
-        <v>855.6735</v>
+        <v>2747.2455</v>
       </c>
       <c r="G55" t="n">
-        <v>32686726.8</v>
+        <v>54477878.1</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2230,30 +2230,30 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>87800</v>
+        <v>37100</v>
       </c>
       <c r="F56" t="n">
-        <v>384.5603</v>
+        <v>293.6813</v>
       </c>
       <c r="G56" t="n">
-        <v>33764396.5</v>
+        <v>10895575.6</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2262,126 +2262,126 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>52400</v>
+        <v>80200</v>
       </c>
       <c r="F57" t="n">
-        <v>636.0417</v>
+        <v>407.5652</v>
       </c>
       <c r="G57" t="n">
-        <v>33328583.4</v>
+        <v>32686726.8</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>10250</v>
+        <v>31600</v>
       </c>
       <c r="F58" t="n">
-        <v>3328.756</v>
+        <v>344.7967</v>
       </c>
       <c r="G58" t="n">
-        <v>34119749</v>
+        <v>10895575.6</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>10090</v>
+        <v>38200</v>
       </c>
       <c r="F59" t="n">
-        <v>3333.5276</v>
+        <v>855.6735</v>
       </c>
       <c r="G59" t="n">
-        <v>33635293.3</v>
+        <v>32686726.8</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53200</v>
+        <v>87800</v>
       </c>
       <c r="F60" t="n">
-        <v>632.2424</v>
+        <v>384.5603</v>
       </c>
       <c r="G60" t="n">
-        <v>33635293.3</v>
+        <v>33764396.5</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2390,86 +2390,84 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>35050</v>
+        <v>52400</v>
       </c>
       <c r="F61" t="n">
-        <v>941.2811</v>
+        <v>636.0417</v>
       </c>
       <c r="G61" t="n">
-        <v>32991903.3</v>
+        <v>33328583.4</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>29100</v>
+        <v>10250</v>
       </c>
       <c r="F62" t="n">
-        <v>1976.0221</v>
+        <v>3328.756</v>
       </c>
       <c r="G62" t="n">
-        <v>57502244.5</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-4.1</v>
-      </c>
+        <v>34119749</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>43700</v>
+        <v>10090</v>
       </c>
       <c r="F63" t="n">
-        <v>1509.9269</v>
+        <v>3333.5276</v>
       </c>
       <c r="G63" t="n">
-        <v>65983806.6</v>
+        <v>33635293.3</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2484,34 +2482,34 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>49500</v>
+        <v>53200</v>
       </c>
       <c r="F64" t="n">
-        <v>1333.0062</v>
+        <v>632.2424</v>
       </c>
       <c r="G64" t="n">
-        <v>65983806.6</v>
+        <v>33635293.3</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2520,94 +2518,96 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>86300</v>
+        <v>35050</v>
       </c>
       <c r="F65" t="n">
-        <v>366.4646</v>
+        <v>941.2811</v>
       </c>
       <c r="G65" t="n">
-        <v>31625898.5</v>
+        <v>32991903.3</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>8490</v>
+        <v>29100</v>
       </c>
       <c r="F66" t="n">
-        <v>3672.3539</v>
+        <v>1976.0221</v>
       </c>
       <c r="G66" t="n">
-        <v>31178284.6</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
+        <v>57502244.5</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-4.1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>45500</v>
+        <v>43700</v>
       </c>
       <c r="F67" t="n">
-        <v>685.237</v>
+        <v>1509.9269</v>
       </c>
       <c r="G67" t="n">
-        <v>31178284.6</v>
+        <v>65983806.6</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2616,20 +2616,20 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>7520</v>
+        <v>49500</v>
       </c>
       <c r="F68" t="n">
-        <v>4087.0231</v>
+        <v>1333.0062</v>
       </c>
       <c r="G68" t="n">
-        <v>30734413.9</v>
+        <v>65983806.6</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2648,94 +2648,94 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>83000</v>
+        <v>86300</v>
       </c>
       <c r="F69" t="n">
-        <v>370.2941</v>
+        <v>366.4646</v>
       </c>
       <c r="G69" t="n">
-        <v>30734413.9</v>
+        <v>31625898.5</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>47750</v>
+        <v>8490</v>
       </c>
       <c r="F70" t="n">
-        <v>643.6526</v>
+        <v>3672.3539</v>
       </c>
       <c r="G70" t="n">
-        <v>30734413.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>8080</v>
+        <v>45500</v>
       </c>
       <c r="F71" t="n">
-        <v>3746.0511</v>
+        <v>685.237</v>
       </c>
       <c r="G71" t="n">
-        <v>30268092.9</v>
+        <v>31178284.6</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2744,130 +2744,126 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>21950</v>
+        <v>7520</v>
       </c>
       <c r="F72" t="n">
-        <v>1378.9564</v>
+        <v>4087.0231</v>
       </c>
       <c r="G72" t="n">
-        <v>30268092.9</v>
+        <v>30734413.9</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>22750</v>
+        <v>83000</v>
       </c>
       <c r="F73" t="n">
-        <v>2200.9656</v>
+        <v>370.2941</v>
       </c>
       <c r="G73" t="n">
-        <v>50071968.5</v>
+        <v>30734413.9</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>33150</v>
+        <v>47750</v>
       </c>
       <c r="F74" t="n">
-        <v>921.4443</v>
+        <v>643.6526</v>
       </c>
       <c r="G74" t="n">
-        <v>30545877.8</v>
-      </c>
-      <c r="H74" t="n">
-        <v>2</v>
-      </c>
+        <v>30734413.9</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>033790</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>38050</v>
+        <v>8080</v>
       </c>
       <c r="F75" t="n">
-        <v>790.1567</v>
+        <v>3746.0511</v>
       </c>
       <c r="G75" t="n">
-        <v>30065462.5</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0.4</v>
-      </c>
+        <v>30268092.9</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2876,30 +2872,30 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>28850</v>
+        <v>21950</v>
       </c>
       <c r="F76" t="n">
-        <v>1038.0221</v>
+        <v>1378.9564</v>
       </c>
       <c r="G76" t="n">
-        <v>29946939</v>
+        <v>30268092.9</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2908,79 +2904,83 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>76400</v>
+        <v>22750</v>
       </c>
       <c r="F77" t="n">
-        <v>391.9756</v>
+        <v>2200.9656</v>
       </c>
       <c r="G77" t="n">
-        <v>29946939</v>
+        <v>50071968.5</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>21650</v>
+        <v>33150</v>
       </c>
       <c r="F78" t="n">
-        <v>1383.2304</v>
+        <v>921.4443</v>
       </c>
       <c r="G78" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H78" t="inlineStr"/>
+        <v>30545877.8</v>
+      </c>
+      <c r="H78" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>356860</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>32500</v>
+        <v>38050</v>
       </c>
       <c r="F79" t="n">
-        <v>921.4443</v>
+        <v>790.1567</v>
       </c>
       <c r="G79" t="n">
-        <v>29946939</v>
-      </c>
-      <c r="H79" t="inlineStr"/>
+        <v>30065462.5</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2990,24 +2990,24 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>356860</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>37900</v>
+        <v>28850</v>
       </c>
       <c r="F80" t="n">
-        <v>790.1567</v>
+        <v>1038.0221</v>
       </c>
       <c r="G80" t="n">
         <v>29946939</v>
@@ -3017,17 +3017,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3036,47 +3036,175 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>25300</v>
+        <v>76400</v>
       </c>
       <c r="F81" t="n">
-        <v>1186</v>
+        <v>391.9756</v>
       </c>
       <c r="G81" t="n">
-        <v>30005800</v>
+        <v>29946939</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>21650</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1383.2304</v>
+      </c>
+      <c r="G82" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>32500</v>
+      </c>
+      <c r="F83" t="n">
+        <v>921.4443</v>
+      </c>
+      <c r="G83" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>356860</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F84" t="n">
+        <v>790.1567</v>
+      </c>
+      <c r="G84" t="n">
+        <v>29946939</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>에프에스티</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>036810</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>25300</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1186</v>
+      </c>
+      <c r="G85" t="n">
+        <v>30005800</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
         <is>
           <t>아이티센글로벌</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>124500</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E82" t="n">
+      <c r="E86" t="n">
         <v>32000</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F86" t="n">
         <v>938</v>
       </c>
-      <c r="G82" t="n">
+      <c r="G86" t="n">
         <v>30016000</v>
       </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
